--- a/output/2024-10-03.xlsx
+++ b/output/2024-10-03.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="F14" t="n">
-        <v>7.49</v>
+        <v>7.42</v>
       </c>
       <c r="G14" t="n">
-        <v>161.7</v>
+        <v>174.9</v>
       </c>
       <c r="H14" t="n">
-        <v>79.3</v>
+        <v>78.2</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-215.32</v>
+        <v>-132.24</v>
       </c>
       <c r="K14" t="n">
-        <v>-69.73</v>
+        <v>62.37</v>
       </c>
       <c r="L14" t="n">
-        <v>226.33</v>
+        <v>146.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:24:42</t>
+          <t>07:23:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="F15" t="n">
-        <v>6.92</v>
+        <v>7.41</v>
       </c>
       <c r="G15" t="n">
-        <v>178</v>
+        <v>172.5</v>
       </c>
       <c r="H15" t="n">
-        <v>78.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.2</v>
+        <v>12.41</v>
       </c>
       <c r="K15" t="n">
-        <v>182.42</v>
+        <v>-16.39</v>
       </c>
       <c r="L15" t="n">
-        <v>182.56</v>
+        <v>20.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:25:56</t>
+          <t>07:25:10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.04</v>
+        <v>2.47</v>
       </c>
       <c r="F16" t="n">
-        <v>6.97</v>
+        <v>7.18</v>
       </c>
       <c r="G16" t="n">
-        <v>184.1</v>
+        <v>183.6</v>
       </c>
       <c r="H16" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-108.37</v>
+        <v>56.06</v>
       </c>
       <c r="K16" t="n">
-        <v>126.15</v>
+        <v>191.24</v>
       </c>
       <c r="L16" t="n">
-        <v>166.31</v>
+        <v>199.29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:30:28</t>
+          <t>07:29:46</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="F17" t="n">
-        <v>7.25</v>
+        <v>6.55</v>
       </c>
       <c r="G17" t="n">
-        <v>179.4</v>
+        <v>186.6</v>
       </c>
       <c r="H17" t="n">
-        <v>84.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-169.32</v>
+        <v>264.34</v>
       </c>
       <c r="K17" t="n">
-        <v>123.33</v>
+        <v>-74.84999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>209.47</v>
+        <v>274.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:32:15</t>
+          <t>07:32:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="F18" t="n">
         <v>6.71</v>
       </c>
       <c r="G18" t="n">
-        <v>185</v>
+        <v>191.7</v>
       </c>
       <c r="H18" t="n">
-        <v>85.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-41.47</v>
+        <v>-77.42</v>
       </c>
       <c r="K18" t="n">
-        <v>93.11</v>
+        <v>90.98</v>
       </c>
       <c r="L18" t="n">
-        <v>101.93</v>
+        <v>119.46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:33:59</t>
+          <t>07:33:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="F19" t="n">
-        <v>7.29</v>
+        <v>7.04</v>
       </c>
       <c r="G19" t="n">
-        <v>175.3</v>
+        <v>173.1</v>
       </c>
       <c r="H19" t="n">
-        <v>81.7</v>
+        <v>77.7</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-73.8</v>
+        <v>-84.56</v>
       </c>
       <c r="K19" t="n">
-        <v>0.78</v>
+        <v>19.64</v>
       </c>
       <c r="L19" t="n">
-        <v>73.81</v>
+        <v>86.81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:37:41</t>
+          <t>07:36:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="F20" t="n">
-        <v>6.97</v>
+        <v>7.09</v>
       </c>
       <c r="G20" t="n">
-        <v>182</v>
+        <v>174.6</v>
       </c>
       <c r="H20" t="n">
-        <v>82.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>139.96</v>
+        <v>108.87</v>
       </c>
       <c r="K20" t="n">
-        <v>-63.96</v>
+        <v>97.2</v>
       </c>
       <c r="L20" t="n">
-        <v>153.88</v>
+        <v>145.95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:39:47</t>
+          <t>07:37:26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.55</v>
+        <v>2.96</v>
       </c>
       <c r="F21" t="n">
-        <v>7.44</v>
+        <v>6.72</v>
       </c>
       <c r="G21" t="n">
-        <v>173.7</v>
+        <v>169.3</v>
       </c>
       <c r="H21" t="n">
-        <v>88.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-45.47</v>
+        <v>180.16</v>
       </c>
       <c r="K21" t="n">
-        <v>-151.14</v>
+        <v>53.76</v>
       </c>
       <c r="L21" t="n">
-        <v>157.83</v>
+        <v>188.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:41:22</t>
+          <t>07:38:47</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.86</v>
+        <v>2.37</v>
       </c>
       <c r="F22" t="n">
-        <v>7.41</v>
+        <v>6.38</v>
       </c>
       <c r="G22" t="n">
-        <v>177.8</v>
+        <v>173.1</v>
       </c>
       <c r="H22" t="n">
-        <v>76.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-120.63</v>
+        <v>369.53</v>
       </c>
       <c r="K22" t="n">
-        <v>8.109999999999999</v>
+        <v>-399.51</v>
       </c>
       <c r="L22" t="n">
-        <v>120.9</v>
+        <v>544.21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:45:15</t>
+          <t>07:43:44</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.14</v>
+        <v>2.52</v>
       </c>
       <c r="F23" t="n">
-        <v>7.25</v>
+        <v>7.06</v>
       </c>
       <c r="G23" t="n">
-        <v>165.4</v>
+        <v>185.8</v>
       </c>
       <c r="H23" t="n">
-        <v>81</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-267.36</v>
+        <v>-210.12</v>
       </c>
       <c r="K23" t="n">
-        <v>-55.61</v>
+        <v>-415.15</v>
       </c>
       <c r="L23" t="n">
-        <v>273.09</v>
+        <v>465.29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:46:51</t>
+          <t>07:45:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="F24" t="n">
-        <v>7.07</v>
+        <v>6.71</v>
       </c>
       <c r="G24" t="n">
-        <v>173.3</v>
+        <v>160.6</v>
       </c>
       <c r="H24" t="n">
-        <v>84.09999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-133.1</v>
+        <v>-108.32</v>
       </c>
       <c r="K24" t="n">
-        <v>196.23</v>
+        <v>61.88</v>
       </c>
       <c r="L24" t="n">
-        <v>237.11</v>
+        <v>124.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:48:09</t>
+          <t>07:47:16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="F25" t="n">
-        <v>6.58</v>
+        <v>7.45</v>
       </c>
       <c r="G25" t="n">
-        <v>172.5</v>
+        <v>194.5</v>
       </c>
       <c r="H25" t="n">
-        <v>78.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-116.34</v>
+        <v>-52.03</v>
       </c>
       <c r="K25" t="n">
-        <v>192.48</v>
+        <v>-137.59</v>
       </c>
       <c r="L25" t="n">
-        <v>224.9</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:53:40</t>
+          <t>07:52:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="F26" t="n">
-        <v>6.92</v>
+        <v>6.74</v>
       </c>
       <c r="G26" t="n">
-        <v>172.3</v>
+        <v>160.3</v>
       </c>
       <c r="H26" t="n">
-        <v>87.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-394.44</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>4.72</v>
+        <v>-127.65</v>
       </c>
       <c r="L26" t="n">
-        <v>394.47</v>
+        <v>143.21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:54:25</t>
+          <t>07:54:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="F27" t="n">
-        <v>6.4</v>
+        <v>7.29</v>
       </c>
       <c r="G27" t="n">
-        <v>168.5</v>
+        <v>180.1</v>
       </c>
       <c r="H27" t="n">
-        <v>89.59999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>231.21</v>
+        <v>284.76</v>
       </c>
       <c r="K27" t="n">
-        <v>363.56</v>
+        <v>-360.87</v>
       </c>
       <c r="L27" t="n">
-        <v>430.86</v>
+        <v>459.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:56:38</t>
+          <t>07:56:42</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="F28" t="n">
-        <v>6.93</v>
+        <v>6.56</v>
       </c>
       <c r="G28" t="n">
-        <v>155.3</v>
+        <v>179</v>
       </c>
       <c r="H28" t="n">
-        <v>89</v>
+        <v>83.8</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-116.21</v>
+        <v>390.91</v>
       </c>
       <c r="K28" t="n">
-        <v>-515.58</v>
+        <v>-57</v>
       </c>
       <c r="L28" t="n">
-        <v>528.52</v>
+        <v>395.04</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:07:17</t>
+          <t>08:03:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="F29" t="n">
-        <v>7.17</v>
+        <v>7.08</v>
       </c>
       <c r="G29" t="n">
-        <v>173.3</v>
+        <v>181.9</v>
       </c>
       <c r="H29" t="n">
-        <v>87.3</v>
+        <v>85.2</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-13.54</v>
+        <v>29.54</v>
       </c>
       <c r="K29" t="n">
-        <v>92.33</v>
+        <v>114.16</v>
       </c>
       <c r="L29" t="n">
-        <v>93.31999999999999</v>
+        <v>117.92</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:09:29</t>
+          <t>08:05:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="F30" t="n">
-        <v>6.43</v>
+        <v>6.92</v>
       </c>
       <c r="G30" t="n">
-        <v>185</v>
+        <v>184.2</v>
       </c>
       <c r="H30" t="n">
-        <v>86.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>12.63</v>
+        <v>-164.67</v>
       </c>
       <c r="K30" t="n">
-        <v>139.98</v>
+        <v>1.68</v>
       </c>
       <c r="L30" t="n">
-        <v>140.55</v>
+        <v>164.67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:10:34</t>
+          <t>08:07:16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.26</v>
+        <v>3.27</v>
       </c>
       <c r="F31" t="n">
-        <v>8.24</v>
+        <v>6.79</v>
       </c>
       <c r="G31" t="n">
-        <v>182</v>
+        <v>164.5</v>
       </c>
       <c r="H31" t="n">
-        <v>85</v>
+        <v>80.3</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-29.98</v>
+        <v>112.94</v>
       </c>
       <c r="K31" t="n">
-        <v>14.17</v>
+        <v>-209.33</v>
       </c>
       <c r="L31" t="n">
-        <v>33.16</v>
+        <v>237.85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:16:17</t>
+          <t>08:12:01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="F32" t="n">
-        <v>7.6</v>
+        <v>7.07</v>
       </c>
       <c r="G32" t="n">
-        <v>178.4</v>
+        <v>173</v>
       </c>
       <c r="H32" t="n">
-        <v>83.3</v>
+        <v>82</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>5.19</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-17.11</v>
+        <v>263.36</v>
       </c>
       <c r="L32" t="n">
-        <v>17.88</v>
+        <v>281.45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:17:24</t>
+          <t>08:14:06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.29</v>
+        <v>2.65</v>
       </c>
       <c r="F33" t="n">
-        <v>6.63</v>
+        <v>7.28</v>
       </c>
       <c r="G33" t="n">
-        <v>183.5</v>
+        <v>182.9</v>
       </c>
       <c r="H33" t="n">
-        <v>81.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>296.59</v>
+        <v>69.87</v>
       </c>
       <c r="K33" t="n">
-        <v>26.26</v>
+        <v>-54.52</v>
       </c>
       <c r="L33" t="n">
-        <v>297.75</v>
+        <v>88.62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:18:46</t>
+          <t>08:15:37</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.3</v>
+        <v>3.29</v>
       </c>
       <c r="F34" t="n">
-        <v>7.11</v>
+        <v>6.83</v>
       </c>
       <c r="G34" t="n">
-        <v>171</v>
+        <v>179.1</v>
       </c>
       <c r="H34" t="n">
-        <v>78.7</v>
+        <v>80</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-68.53</v>
+        <v>49.67</v>
       </c>
       <c r="K34" t="n">
-        <v>92.92</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>115.46</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:23:06</t>
+          <t>08:20:08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="F35" t="n">
-        <v>7.73</v>
+        <v>6.54</v>
       </c>
       <c r="G35" t="n">
-        <v>169.3</v>
+        <v>181.7</v>
       </c>
       <c r="H35" t="n">
-        <v>83.7</v>
+        <v>74.2</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>59.83</v>
+        <v>96.36</v>
       </c>
       <c r="K35" t="n">
-        <v>15.59</v>
+        <v>330.11</v>
       </c>
       <c r="L35" t="n">
-        <v>61.83</v>
+        <v>343.89</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:24:56</t>
+          <t>08:22:19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="F36" t="n">
-        <v>6.68</v>
+        <v>7</v>
       </c>
       <c r="G36" t="n">
-        <v>178.9</v>
+        <v>180.2</v>
       </c>
       <c r="H36" t="n">
-        <v>81.7</v>
+        <v>77.2</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-325.87</v>
+        <v>-4.97</v>
       </c>
       <c r="K36" t="n">
-        <v>95.59</v>
+        <v>154.52</v>
       </c>
       <c r="L36" t="n">
-        <v>339.6</v>
+        <v>154.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:26:55</t>
+          <t>08:23:49</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.66</v>
+        <v>2.32</v>
       </c>
       <c r="F37" t="n">
-        <v>7.06</v>
+        <v>6.77</v>
       </c>
       <c r="G37" t="n">
-        <v>190.5</v>
+        <v>183.2</v>
       </c>
       <c r="H37" t="n">
-        <v>84.2</v>
+        <v>81.7</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>122.32</v>
+        <v>407.32</v>
       </c>
       <c r="K37" t="n">
-        <v>-298.57</v>
+        <v>-184.02</v>
       </c>
       <c r="L37" t="n">
-        <v>322.65</v>
+        <v>446.96</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:31:42</t>
+          <t>08:29:20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="F38" t="n">
-        <v>6.92</v>
+        <v>7.62</v>
       </c>
       <c r="G38" t="n">
-        <v>180.2</v>
+        <v>180.9</v>
       </c>
       <c r="H38" t="n">
-        <v>82.3</v>
+        <v>86.5</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>352.56</v>
+        <v>-584.34</v>
       </c>
       <c r="K38" t="n">
-        <v>287.87</v>
+        <v>-548.6</v>
       </c>
       <c r="L38" t="n">
-        <v>455.16</v>
+        <v>801.51</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:33:40</t>
+          <t>08:30:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.08</v>
+        <v>2.64</v>
       </c>
       <c r="F39" t="n">
-        <v>7.81</v>
+        <v>7.44</v>
       </c>
       <c r="G39" t="n">
-        <v>186.1</v>
+        <v>164.9</v>
       </c>
       <c r="H39" t="n">
-        <v>83.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-90.53</v>
+        <v>-107.74</v>
       </c>
       <c r="K39" t="n">
-        <v>-304.89</v>
+        <v>-62.16</v>
       </c>
       <c r="L39" t="n">
-        <v>318.05</v>
+        <v>124.39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:35:43</t>
+          <t>08:32:41</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.69</v>
+        <v>2.93</v>
       </c>
       <c r="F40" t="n">
-        <v>6.84</v>
+        <v>6.86</v>
       </c>
       <c r="G40" t="n">
-        <v>171.3</v>
+        <v>186.3</v>
       </c>
       <c r="H40" t="n">
-        <v>83.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-216.07</v>
+        <v>27.63</v>
       </c>
       <c r="K40" t="n">
-        <v>-1007.72</v>
+        <v>-269.84</v>
       </c>
       <c r="L40" t="n">
-        <v>1030.62</v>
+        <v>271.25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:40:12</t>
+          <t>08:37:30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.71</v>
+        <v>2.46</v>
       </c>
       <c r="F41" t="n">
-        <v>6.74</v>
+        <v>6.69</v>
       </c>
       <c r="G41" t="n">
-        <v>180.8</v>
+        <v>178.6</v>
       </c>
       <c r="H41" t="n">
-        <v>79.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-175.72</v>
+        <v>31.26</v>
       </c>
       <c r="K41" t="n">
-        <v>41.31</v>
+        <v>270.43</v>
       </c>
       <c r="L41" t="n">
-        <v>180.51</v>
+        <v>272.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:41:42</t>
+          <t>08:39:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="F42" t="n">
-        <v>6.71</v>
+        <v>7.79</v>
       </c>
       <c r="G42" t="n">
-        <v>183.3</v>
+        <v>185.9</v>
       </c>
       <c r="H42" t="n">
-        <v>90.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-26.61</v>
+        <v>-427.91</v>
       </c>
       <c r="K42" t="n">
-        <v>-837.72</v>
+        <v>305.91</v>
       </c>
       <c r="L42" t="n">
-        <v>838.14</v>
+        <v>526.01</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:42:44</t>
+          <t>08:40:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="F43" t="n">
-        <v>7.51</v>
+        <v>6.49</v>
       </c>
       <c r="G43" t="n">
-        <v>178</v>
+        <v>187.2</v>
       </c>
       <c r="H43" t="n">
-        <v>81.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-205.68</v>
+        <v>172.23</v>
       </c>
       <c r="K43" t="n">
-        <v>-550.76</v>
+        <v>-675.0599999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>587.92</v>
+        <v>696.6799999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:51:30</t>
+          <t>08:49:41</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.89</v>
+        <v>2.3</v>
       </c>
       <c r="F44" t="n">
-        <v>6.55</v>
+        <v>7.06</v>
       </c>
       <c r="G44" t="n">
-        <v>189.3</v>
+        <v>162.9</v>
       </c>
       <c r="H44" t="n">
-        <v>86.3</v>
+        <v>83.2</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>52.93</v>
+        <v>-37.38</v>
       </c>
       <c r="K44" t="n">
-        <v>93.70999999999999</v>
+        <v>7.64</v>
       </c>
       <c r="L44" t="n">
-        <v>107.62</v>
+        <v>38.15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:54:05</t>
+          <t>08:50:32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="F45" t="n">
-        <v>6.83</v>
+        <v>6.56</v>
       </c>
       <c r="G45" t="n">
-        <v>181.8</v>
+        <v>174.4</v>
       </c>
       <c r="H45" t="n">
-        <v>82.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>66.48</v>
+        <v>86.42</v>
       </c>
       <c r="K45" t="n">
-        <v>-118.6</v>
+        <v>-153.46</v>
       </c>
       <c r="L45" t="n">
-        <v>135.96</v>
+        <v>176.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:56:35</t>
+          <t>08:52:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="F46" t="n">
-        <v>5.68</v>
+        <v>7.45</v>
       </c>
       <c r="G46" t="n">
-        <v>174.9</v>
+        <v>184.4</v>
       </c>
       <c r="H46" t="n">
-        <v>86.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>40.86</v>
+        <v>21.58</v>
       </c>
       <c r="K46" t="n">
-        <v>-12.75</v>
+        <v>148.55</v>
       </c>
       <c r="L46" t="n">
-        <v>42.8</v>
+        <v>150.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:59:47</t>
+          <t>08:56:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="F47" t="n">
-        <v>7.22</v>
+        <v>7.1</v>
       </c>
       <c r="G47" t="n">
-        <v>180.3</v>
+        <v>174.7</v>
       </c>
       <c r="H47" t="n">
-        <v>83.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I47" t="n">
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-135.71</v>
+        <v>-131.05</v>
       </c>
       <c r="K47" t="n">
-        <v>20.29</v>
+        <v>-140.14</v>
       </c>
       <c r="L47" t="n">
-        <v>137.22</v>
+        <v>191.87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:01:01</t>
+          <t>08:58:16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="F48" t="n">
-        <v>7.11</v>
+        <v>7.42</v>
       </c>
       <c r="G48" t="n">
-        <v>190.3</v>
+        <v>174.7</v>
       </c>
       <c r="H48" t="n">
-        <v>79.2</v>
+        <v>75.2</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>37</v>
+        <v>180.92</v>
       </c>
       <c r="K48" t="n">
-        <v>-7.34</v>
+        <v>-167.01</v>
       </c>
       <c r="L48" t="n">
-        <v>37.72</v>
+        <v>246.22</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:03:13</t>
+          <t>09:00:30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="F49" t="n">
-        <v>7.13</v>
+        <v>6.34</v>
       </c>
       <c r="G49" t="n">
-        <v>178.5</v>
+        <v>163.7</v>
       </c>
       <c r="H49" t="n">
-        <v>81.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-85.98</v>
+        <v>-185.78</v>
       </c>
       <c r="K49" t="n">
-        <v>-176.93</v>
+        <v>159.88</v>
       </c>
       <c r="L49" t="n">
-        <v>196.71</v>
+        <v>245.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:08:53</t>
+          <t>09:05:03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="F50" t="n">
-        <v>6.9</v>
+        <v>6.96</v>
       </c>
       <c r="G50" t="n">
-        <v>179.5</v>
+        <v>171.2</v>
       </c>
       <c r="H50" t="n">
-        <v>81.7</v>
+        <v>83.7</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>-74.05</v>
+        <v>302.67</v>
       </c>
       <c r="K50" t="n">
-        <v>-15.66</v>
+        <v>-243.56</v>
       </c>
       <c r="L50" t="n">
-        <v>75.69</v>
+        <v>388.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:10:13</t>
+          <t>09:06:07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
       <c r="F51" t="n">
-        <v>6.78</v>
+        <v>6.89</v>
       </c>
       <c r="G51" t="n">
-        <v>190.4</v>
+        <v>201.5</v>
       </c>
       <c r="H51" t="n">
-        <v>81.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="I51" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-70.04000000000001</v>
+        <v>-98.40000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-151.47</v>
+        <v>-328.54</v>
       </c>
       <c r="L51" t="n">
-        <v>166.88</v>
+        <v>342.96</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:11:55</t>
+          <t>09:06:55</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="F52" t="n">
-        <v>7.61</v>
+        <v>6.54</v>
       </c>
       <c r="G52" t="n">
-        <v>165.9</v>
+        <v>184.8</v>
       </c>
       <c r="H52" t="n">
-        <v>87.8</v>
+        <v>83.8</v>
       </c>
       <c r="I52" t="n">
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-290.64</v>
+        <v>43.96</v>
       </c>
       <c r="K52" t="n">
-        <v>-251.39</v>
+        <v>-175.36</v>
       </c>
       <c r="L52" t="n">
-        <v>384.28</v>
+        <v>180.79</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:16:47</t>
+          <t>09:13:23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="F53" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="G53" t="n">
-        <v>186.5</v>
+        <v>186.3</v>
       </c>
       <c r="H53" t="n">
-        <v>81.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-171.69</v>
+        <v>375.65</v>
       </c>
       <c r="K53" t="n">
-        <v>151.83</v>
+        <v>-318.06</v>
       </c>
       <c r="L53" t="n">
-        <v>229.2</v>
+        <v>492.21</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:18:37</t>
+          <t>09:14:58</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.92</v>
+        <v>2.37</v>
       </c>
       <c r="F54" t="n">
-        <v>7.44</v>
+        <v>6.64</v>
       </c>
       <c r="G54" t="n">
-        <v>189.5</v>
+        <v>187.9</v>
       </c>
       <c r="H54" t="n">
-        <v>83.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="I54" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>-203.42</v>
+        <v>6.5</v>
       </c>
       <c r="K54" t="n">
-        <v>269.6</v>
+        <v>-86.68000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>337.73</v>
+        <v>86.92</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:20:04</t>
+          <t>09:17:25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="F55" t="n">
-        <v>6.13</v>
+        <v>7.06</v>
       </c>
       <c r="G55" t="n">
-        <v>173.4</v>
+        <v>197.3</v>
       </c>
       <c r="H55" t="n">
-        <v>78.2</v>
+        <v>77.2</v>
       </c>
       <c r="I55" t="n">
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>485.66</v>
+        <v>427.4</v>
       </c>
       <c r="K55" t="n">
-        <v>322.97</v>
+        <v>135.42</v>
       </c>
       <c r="L55" t="n">
-        <v>583.24</v>
+        <v>448.34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:25:24</t>
+          <t>09:21:02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.71</v>
+        <v>2.98</v>
       </c>
       <c r="F56" t="n">
-        <v>6.53</v>
+        <v>6.89</v>
       </c>
       <c r="G56" t="n">
-        <v>191.3</v>
+        <v>177.3</v>
       </c>
       <c r="H56" t="n">
-        <v>88.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-196.85</v>
+        <v>-194.52</v>
       </c>
       <c r="K56" t="n">
-        <v>175.13</v>
+        <v>178.52</v>
       </c>
       <c r="L56" t="n">
-        <v>263.48</v>
+        <v>264.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:27:19</t>
+          <t>09:21:45</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.21</v>
+        <v>2.88</v>
       </c>
       <c r="F57" t="n">
-        <v>6.78</v>
+        <v>6.82</v>
       </c>
       <c r="G57" t="n">
-        <v>170.9</v>
+        <v>186</v>
       </c>
       <c r="H57" t="n">
-        <v>77</v>
+        <v>90.5</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>123.7</v>
+        <v>527.65</v>
       </c>
       <c r="K57" t="n">
-        <v>-114.93</v>
+        <v>-411.81</v>
       </c>
       <c r="L57" t="n">
-        <v>168.85</v>
+        <v>669.33</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:29:43</t>
+          <t>09:23:15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.74</v>
+        <v>3.21</v>
       </c>
       <c r="F58" t="n">
-        <v>6.13</v>
+        <v>6.88</v>
       </c>
       <c r="G58" t="n">
-        <v>181</v>
+        <v>177.7</v>
       </c>
       <c r="H58" t="n">
-        <v>81.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-590.38</v>
+        <v>414.89</v>
       </c>
       <c r="K58" t="n">
-        <v>-139.26</v>
+        <v>-656.61</v>
       </c>
       <c r="L58" t="n">
-        <v>606.58</v>
+        <v>776.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:39:38</t>
+          <t>09:31:33</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.87</v>
+        <v>2.47</v>
       </c>
       <c r="F59" t="n">
-        <v>6.7</v>
+        <v>7.22</v>
       </c>
       <c r="G59" t="n">
-        <v>186.7</v>
+        <v>185.6</v>
       </c>
       <c r="H59" t="n">
-        <v>84.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>15.6</v>
+        <v>152.91</v>
       </c>
       <c r="K59" t="n">
-        <v>84.97</v>
+        <v>-20.84</v>
       </c>
       <c r="L59" t="n">
-        <v>86.39</v>
+        <v>154.33</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:40:55</t>
+          <t>09:32:41</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="F60" t="n">
-        <v>7.41</v>
+        <v>7.12</v>
       </c>
       <c r="G60" t="n">
-        <v>167.4</v>
+        <v>187</v>
       </c>
       <c r="H60" t="n">
-        <v>83.8</v>
+        <v>77.7</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-131.75</v>
+        <v>312.71</v>
       </c>
       <c r="K60" t="n">
-        <v>89.83</v>
+        <v>307.91</v>
       </c>
       <c r="L60" t="n">
-        <v>159.46</v>
+        <v>438.86</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:42:24</t>
+          <t>09:34:41</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="F61" t="n">
-        <v>8.06</v>
+        <v>6.53</v>
       </c>
       <c r="G61" t="n">
-        <v>173.8</v>
+        <v>178.3</v>
       </c>
       <c r="H61" t="n">
-        <v>76.3</v>
+        <v>79.2</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-45.74</v>
+        <v>-267.43</v>
       </c>
       <c r="K61" t="n">
-        <v>275.98</v>
+        <v>17.24</v>
       </c>
       <c r="L61" t="n">
-        <v>279.74</v>
+        <v>267.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:46:46</t>
+          <t>09:38:43</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.93</v>
+        <v>2.3</v>
       </c>
       <c r="F62" t="n">
-        <v>6.55</v>
+        <v>6.47</v>
       </c>
       <c r="G62" t="n">
-        <v>167.4</v>
+        <v>171.8</v>
       </c>
       <c r="H62" t="n">
-        <v>86.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-2.76</v>
+        <v>-109.71</v>
       </c>
       <c r="K62" t="n">
-        <v>-43.82</v>
+        <v>20.97</v>
       </c>
       <c r="L62" t="n">
-        <v>43.91</v>
+        <v>111.69</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:47:51</t>
+          <t>09:39:45</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="F63" t="n">
-        <v>7.09</v>
+        <v>6.98</v>
       </c>
       <c r="G63" t="n">
-        <v>188.9</v>
+        <v>190.7</v>
       </c>
       <c r="H63" t="n">
-        <v>76.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-106.36</v>
+        <v>-94.62</v>
       </c>
       <c r="K63" t="n">
-        <v>50.07</v>
+        <v>28.81</v>
       </c>
       <c r="L63" t="n">
-        <v>117.56</v>
+        <v>98.91</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:49:37</t>
+          <t>09:41:29</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="F64" t="n">
-        <v>7.11</v>
+        <v>6.74</v>
       </c>
       <c r="G64" t="n">
-        <v>181.2</v>
+        <v>173.6</v>
       </c>
       <c r="H64" t="n">
-        <v>78.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-221.8</v>
+        <v>-91.02</v>
       </c>
       <c r="K64" t="n">
-        <v>-80.26000000000001</v>
+        <v>25.29</v>
       </c>
       <c r="L64" t="n">
-        <v>235.87</v>
+        <v>94.47</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:54:22</t>
+          <t>09:46:51</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.46</v>
+        <v>2.75</v>
       </c>
       <c r="F65" t="n">
-        <v>7.26</v>
+        <v>7.32</v>
       </c>
       <c r="G65" t="n">
-        <v>179.2</v>
+        <v>180</v>
       </c>
       <c r="H65" t="n">
-        <v>84.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="I65" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>184.45</v>
+        <v>-219.02</v>
       </c>
       <c r="K65" t="n">
-        <v>331.38</v>
+        <v>367.94</v>
       </c>
       <c r="L65" t="n">
-        <v>379.26</v>
+        <v>428.19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:56:24</t>
+          <t>09:48:26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="F66" t="n">
-        <v>7.13</v>
+        <v>6.88</v>
       </c>
       <c r="G66" t="n">
-        <v>194.5</v>
+        <v>183.8</v>
       </c>
       <c r="H66" t="n">
-        <v>81.7</v>
+        <v>88.3</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-211.68</v>
+        <v>-119.1</v>
       </c>
       <c r="K66" t="n">
-        <v>-27.38</v>
+        <v>270.53</v>
       </c>
       <c r="L66" t="n">
-        <v>213.44</v>
+        <v>295.59</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:58:04</t>
+          <t>09:50:11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="F67" t="n">
-        <v>6.59</v>
+        <v>6.99</v>
       </c>
       <c r="G67" t="n">
-        <v>168.3</v>
+        <v>185.5</v>
       </c>
       <c r="H67" t="n">
-        <v>82.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-240.63</v>
+        <v>197.31</v>
       </c>
       <c r="K67" t="n">
-        <v>255.75</v>
+        <v>-7.17</v>
       </c>
       <c r="L67" t="n">
-        <v>351.15</v>
+        <v>197.44</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:02:49</t>
+          <t>09:54:33</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="F68" t="n">
-        <v>6.94</v>
+        <v>7.02</v>
       </c>
       <c r="G68" t="n">
-        <v>185.2</v>
+        <v>166.7</v>
       </c>
       <c r="H68" t="n">
-        <v>83.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>402.92</v>
+        <v>-163.82</v>
       </c>
       <c r="K68" t="n">
-        <v>-410.48</v>
+        <v>-60.7</v>
       </c>
       <c r="L68" t="n">
-        <v>575.1900000000001</v>
+        <v>174.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:04:05</t>
+          <t>09:56:47</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.33</v>
+        <v>2.86</v>
       </c>
       <c r="F69" t="n">
-        <v>6.85</v>
+        <v>6.72</v>
       </c>
       <c r="G69" t="n">
-        <v>184.8</v>
+        <v>194.5</v>
       </c>
       <c r="H69" t="n">
-        <v>83.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>52.36</v>
+        <v>-126.26</v>
       </c>
       <c r="K69" t="n">
-        <v>452.36</v>
+        <v>-204.35</v>
       </c>
       <c r="L69" t="n">
-        <v>455.38</v>
+        <v>240.21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:06:27</t>
+          <t>09:57:58</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.66</v>
+        <v>3.33</v>
       </c>
       <c r="F70" t="n">
-        <v>7.38</v>
+        <v>6.1</v>
       </c>
       <c r="G70" t="n">
-        <v>171.2</v>
+        <v>171.9</v>
       </c>
       <c r="H70" t="n">
-        <v>77.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>321.61</v>
+        <v>-273.81</v>
       </c>
       <c r="K70" t="n">
-        <v>-197.18</v>
+        <v>-28.13</v>
       </c>
       <c r="L70" t="n">
-        <v>377.24</v>
+        <v>275.25</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:09:55</t>
+          <t>10:03:51</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="F71" t="n">
-        <v>7.19</v>
+        <v>7.23</v>
       </c>
       <c r="G71" t="n">
-        <v>169.1</v>
+        <v>175</v>
       </c>
       <c r="H71" t="n">
-        <v>78.5</v>
+        <v>82</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-30.72</v>
+        <v>419.86</v>
       </c>
       <c r="K71" t="n">
-        <v>-534.4</v>
+        <v>-168.38</v>
       </c>
       <c r="L71" t="n">
-        <v>535.28</v>
+        <v>452.36</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:11:36</t>
+          <t>10:05:12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
       <c r="F72" t="n">
-        <v>7.04</v>
+        <v>7.03</v>
       </c>
       <c r="G72" t="n">
-        <v>190.9</v>
+        <v>184.2</v>
       </c>
       <c r="H72" t="n">
-        <v>79.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>98.79000000000001</v>
+        <v>-26.19</v>
       </c>
       <c r="K72" t="n">
-        <v>-196.58</v>
+        <v>155.04</v>
       </c>
       <c r="L72" t="n">
-        <v>220</v>
+        <v>157.23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:12:23</t>
+          <t>10:06:58</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="F73" t="n">
-        <v>7.33</v>
+        <v>6.05</v>
       </c>
       <c r="G73" t="n">
-        <v>173.6</v>
+        <v>180.7</v>
       </c>
       <c r="H73" t="n">
-        <v>81.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>-47.03</v>
+        <v>414.33</v>
       </c>
       <c r="K73" t="n">
-        <v>361.49</v>
+        <v>-325.21</v>
       </c>
       <c r="L73" t="n">
-        <v>364.54</v>
+        <v>526.72</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:22:02</t>
+          <t>10:14:58</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.57</v>
+        <v>2.93</v>
       </c>
       <c r="F74" t="n">
-        <v>6.36</v>
+        <v>6.34</v>
       </c>
       <c r="G74" t="n">
-        <v>173.5</v>
+        <v>159.7</v>
       </c>
       <c r="H74" t="n">
-        <v>77.5</v>
+        <v>83.8</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>18.21</v>
+        <v>-115.98</v>
       </c>
       <c r="K74" t="n">
-        <v>44.51</v>
+        <v>12.1</v>
       </c>
       <c r="L74" t="n">
-        <v>48.09</v>
+        <v>116.61</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:24:09</t>
+          <t>10:16:41</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="F75" t="n">
-        <v>6.71</v>
+        <v>7.04</v>
       </c>
       <c r="G75" t="n">
-        <v>167.1</v>
+        <v>179.3</v>
       </c>
       <c r="H75" t="n">
-        <v>86</v>
+        <v>81.7</v>
       </c>
       <c r="I75" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-55.5</v>
+        <v>-287.1</v>
       </c>
       <c r="K75" t="n">
-        <v>8.9</v>
+        <v>7.43</v>
       </c>
       <c r="L75" t="n">
-        <v>56.21</v>
+        <v>287.19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:25:58</t>
+          <t>10:17:08</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="F76" t="n">
-        <v>6.81</v>
+        <v>7.03</v>
       </c>
       <c r="G76" t="n">
-        <v>178.5</v>
+        <v>179.5</v>
       </c>
       <c r="H76" t="n">
-        <v>88</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.09</v>
+        <v>151.28</v>
       </c>
       <c r="K76" t="n">
-        <v>-262.07</v>
+        <v>33.43</v>
       </c>
       <c r="L76" t="n">
-        <v>262.45</v>
+        <v>154.93</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:30:09</t>
+          <t>10:21:01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.89</v>
+        <v>3.38</v>
       </c>
       <c r="F77" t="n">
-        <v>7.66</v>
+        <v>5.91</v>
       </c>
       <c r="G77" t="n">
-        <v>173.3</v>
+        <v>174.6</v>
       </c>
       <c r="H77" t="n">
-        <v>86.5</v>
+        <v>82.5</v>
       </c>
       <c r="I77" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>228.49</v>
+        <v>76.73</v>
       </c>
       <c r="K77" t="n">
-        <v>-71.47</v>
+        <v>-21.96</v>
       </c>
       <c r="L77" t="n">
-        <v>239.4</v>
+        <v>79.81</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:32:19</t>
+          <t>10:23:20</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.7</v>
+        <v>3.51</v>
       </c>
       <c r="F78" t="n">
-        <v>7.06</v>
+        <v>7.25</v>
       </c>
       <c r="G78" t="n">
-        <v>169.8</v>
+        <v>172.5</v>
       </c>
       <c r="H78" t="n">
-        <v>84</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-179.3</v>
+        <v>-84.94</v>
       </c>
       <c r="K78" t="n">
-        <v>-79.3</v>
+        <v>282.64</v>
       </c>
       <c r="L78" t="n">
-        <v>196.05</v>
+        <v>295.13</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:34:19</t>
+          <t>10:24:08</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="F79" t="n">
-        <v>6.84</v>
+        <v>7.18</v>
       </c>
       <c r="G79" t="n">
-        <v>186.4</v>
+        <v>178.7</v>
       </c>
       <c r="H79" t="n">
-        <v>78.2</v>
+        <v>79.2</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-67.73</v>
+        <v>-43.11</v>
       </c>
       <c r="K79" t="n">
-        <v>87.13</v>
+        <v>-169.79</v>
       </c>
       <c r="L79" t="n">
-        <v>110.36</v>
+        <v>175.17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:38:00</t>
+          <t>10:29:01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="F80" t="n">
-        <v>7.15</v>
+        <v>6.88</v>
       </c>
       <c r="G80" t="n">
-        <v>171.8</v>
+        <v>184</v>
       </c>
       <c r="H80" t="n">
-        <v>88.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>-83.67</v>
+        <v>213.45</v>
       </c>
       <c r="K80" t="n">
-        <v>-130.61</v>
+        <v>8.19</v>
       </c>
       <c r="L80" t="n">
-        <v>155.11</v>
+        <v>213.61</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:39:12</t>
+          <t>10:30:54</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="F81" t="n">
-        <v>6.92</v>
+        <v>6.33</v>
       </c>
       <c r="G81" t="n">
-        <v>181.1</v>
+        <v>182.8</v>
       </c>
       <c r="H81" t="n">
-        <v>79.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>-52.3</v>
+        <v>137.77</v>
       </c>
       <c r="K81" t="n">
-        <v>156.32</v>
+        <v>412.62</v>
       </c>
       <c r="L81" t="n">
-        <v>164.84</v>
+        <v>435.01</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:40:32</t>
+          <t>10:31:51</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.84</v>
+        <v>2.91</v>
       </c>
       <c r="F82" t="n">
-        <v>6.68</v>
+        <v>6.61</v>
       </c>
       <c r="G82" t="n">
-        <v>183.3</v>
+        <v>185.8</v>
       </c>
       <c r="H82" t="n">
-        <v>77.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-104.89</v>
+        <v>-390.13</v>
       </c>
       <c r="K82" t="n">
-        <v>279.44</v>
+        <v>40.45</v>
       </c>
       <c r="L82" t="n">
-        <v>298.47</v>
+        <v>392.22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:46:04</t>
+          <t>10:36:06</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="F83" t="n">
-        <v>6.73</v>
+        <v>7.8</v>
       </c>
       <c r="G83" t="n">
-        <v>184.1</v>
+        <v>193</v>
       </c>
       <c r="H83" t="n">
-        <v>78</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>-342.88</v>
+        <v>289.28</v>
       </c>
       <c r="K83" t="n">
-        <v>-309.52</v>
+        <v>249.99</v>
       </c>
       <c r="L83" t="n">
-        <v>461.92</v>
+        <v>382.33</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:47:46</t>
+          <t>10:37:29</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="F84" t="n">
-        <v>6.69</v>
+        <v>7.36</v>
       </c>
       <c r="G84" t="n">
-        <v>187</v>
+        <v>176.2</v>
       </c>
       <c r="H84" t="n">
-        <v>79</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>244</v>
+        <v>288.92</v>
       </c>
       <c r="K84" t="n">
-        <v>241.85</v>
+        <v>313.06</v>
       </c>
       <c r="L84" t="n">
-        <v>343.55</v>
+        <v>426.01</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:49:40</t>
+          <t>10:39:54</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="F85" t="n">
-        <v>6.9</v>
+        <v>7.06</v>
       </c>
       <c r="G85" t="n">
-        <v>175.4</v>
+        <v>179.7</v>
       </c>
       <c r="H85" t="n">
-        <v>73.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-219.98</v>
+        <v>236.43</v>
       </c>
       <c r="K85" t="n">
-        <v>-68.5</v>
+        <v>-107.65</v>
       </c>
       <c r="L85" t="n">
-        <v>230.4</v>
+        <v>259.79</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:53:42</t>
+          <t>10:43:23</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="F86" t="n">
-        <v>6.15</v>
+        <v>6.56</v>
       </c>
       <c r="G86" t="n">
-        <v>173.7</v>
+        <v>179.2</v>
       </c>
       <c r="H86" t="n">
-        <v>80.2</v>
+        <v>83.5</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>750.09</v>
+        <v>956.3099999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>59.08</v>
+        <v>-447.71</v>
       </c>
       <c r="L86" t="n">
-        <v>752.41</v>
+        <v>1055.92</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:56:03</t>
+          <t>10:45:41</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.93</v>
+        <v>3.03</v>
       </c>
       <c r="F87" t="n">
-        <v>7.07</v>
+        <v>6.55</v>
       </c>
       <c r="G87" t="n">
-        <v>159.8</v>
+        <v>180.2</v>
       </c>
       <c r="H87" t="n">
-        <v>83.5</v>
+        <v>85.2</v>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>517.16</v>
+        <v>-239.63</v>
       </c>
       <c r="K87" t="n">
-        <v>-307.09</v>
+        <v>699.48</v>
       </c>
       <c r="L87" t="n">
-        <v>601.47</v>
+        <v>739.39</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:58:12</t>
+          <t>10:47:19</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.31</v>
+        <v>3.04</v>
       </c>
       <c r="F88" t="n">
-        <v>6.74</v>
+        <v>7</v>
       </c>
       <c r="G88" t="n">
-        <v>171.9</v>
+        <v>170.2</v>
       </c>
       <c r="H88" t="n">
-        <v>82</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-23.2</v>
+        <v>-332.52</v>
       </c>
       <c r="K88" t="n">
-        <v>8.199999999999999</v>
+        <v>-409.5</v>
       </c>
       <c r="L88" t="n">
-        <v>24.6</v>
+        <v>527.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-03.xlsx
+++ b/output/2024-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-132.24</v>
+        <v>-109.65</v>
       </c>
       <c r="K14" t="n">
-        <v>62.37</v>
+        <v>51.72</v>
       </c>
       <c r="L14" t="n">
-        <v>146.21</v>
+        <v>121.23</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>12.41</v>
+        <v>30.15</v>
       </c>
       <c r="K15" t="n">
-        <v>-16.39</v>
+        <v>-39.82</v>
       </c>
       <c r="L15" t="n">
-        <v>20.56</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>56.06</v>
+        <v>44.39</v>
       </c>
       <c r="K16" t="n">
-        <v>191.24</v>
+        <v>151.43</v>
       </c>
       <c r="L16" t="n">
-        <v>199.29</v>
+        <v>157.81</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>264.34</v>
+        <v>189.66</v>
       </c>
       <c r="K17" t="n">
-        <v>-74.84999999999999</v>
+        <v>-53.7</v>
       </c>
       <c r="L17" t="n">
-        <v>274.74</v>
+        <v>197.11</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-77.42</v>
+        <v>-84.05</v>
       </c>
       <c r="K18" t="n">
-        <v>90.98</v>
+        <v>98.77</v>
       </c>
       <c r="L18" t="n">
-        <v>119.46</v>
+        <v>129.69</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-84.56</v>
+        <v>-106.9</v>
       </c>
       <c r="K19" t="n">
-        <v>19.64</v>
+        <v>24.83</v>
       </c>
       <c r="L19" t="n">
-        <v>86.81</v>
+        <v>109.74</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>108.87</v>
+        <v>145.86</v>
       </c>
       <c r="K20" t="n">
-        <v>97.2</v>
+        <v>130.22</v>
       </c>
       <c r="L20" t="n">
-        <v>145.95</v>
+        <v>195.54</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>180.16</v>
+        <v>227.79</v>
       </c>
       <c r="K21" t="n">
-        <v>53.76</v>
+        <v>67.97</v>
       </c>
       <c r="L21" t="n">
-        <v>188.01</v>
+        <v>237.71</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>369.53</v>
+        <v>322.85</v>
       </c>
       <c r="K22" t="n">
-        <v>-399.51</v>
+        <v>-349.04</v>
       </c>
       <c r="L22" t="n">
-        <v>544.21</v>
+        <v>475.46</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-210.12</v>
+        <v>-230.2</v>
       </c>
       <c r="K23" t="n">
-        <v>-415.15</v>
+        <v>-454.84</v>
       </c>
       <c r="L23" t="n">
-        <v>465.29</v>
+        <v>509.78</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-108.32</v>
+        <v>-198.32</v>
       </c>
       <c r="K24" t="n">
-        <v>61.88</v>
+        <v>113.29</v>
       </c>
       <c r="L24" t="n">
-        <v>124.75</v>
+        <v>228.4</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-52.03</v>
+        <v>-83.68000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-137.59</v>
+        <v>-221.3</v>
       </c>
       <c r="L25" t="n">
-        <v>147.1</v>
+        <v>236.6</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-64.90000000000001</v>
+        <v>-147.81</v>
       </c>
       <c r="K26" t="n">
-        <v>-127.65</v>
+        <v>-290.74</v>
       </c>
       <c r="L26" t="n">
-        <v>143.21</v>
+        <v>326.16</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>284.76</v>
+        <v>386.33</v>
       </c>
       <c r="K27" t="n">
-        <v>-360.87</v>
+        <v>-489.58</v>
       </c>
       <c r="L27" t="n">
-        <v>459.69</v>
+        <v>623.65</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>390.91</v>
+        <v>563.88</v>
       </c>
       <c r="K28" t="n">
-        <v>-57</v>
+        <v>-82.23</v>
       </c>
       <c r="L28" t="n">
-        <v>395.04</v>
+        <v>569.85</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>29.54</v>
+        <v>26.23</v>
       </c>
       <c r="K29" t="n">
-        <v>114.16</v>
+        <v>101.38</v>
       </c>
       <c r="L29" t="n">
-        <v>117.92</v>
+        <v>104.72</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-164.67</v>
+        <v>-141.42</v>
       </c>
       <c r="K30" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="L30" t="n">
-        <v>164.67</v>
+        <v>141.43</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>112.94</v>
+        <v>114.46</v>
       </c>
       <c r="K31" t="n">
-        <v>-209.33</v>
+        <v>-212.15</v>
       </c>
       <c r="L31" t="n">
-        <v>237.85</v>
+        <v>241.06</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>99.29000000000001</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>263.36</v>
+        <v>241.57</v>
       </c>
       <c r="L32" t="n">
-        <v>281.45</v>
+        <v>258.17</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>69.87</v>
+        <v>102.79</v>
       </c>
       <c r="K33" t="n">
-        <v>-54.52</v>
+        <v>-80.2</v>
       </c>
       <c r="L33" t="n">
-        <v>88.62</v>
+        <v>130.38</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>49.67</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>73.01000000000001</v>
+        <v>124.92</v>
       </c>
       <c r="L34" t="n">
-        <v>88.3</v>
+        <v>151.09</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>96.36</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>330.11</v>
+        <v>329.13</v>
       </c>
       <c r="L35" t="n">
-        <v>343.89</v>
+        <v>342.87</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.97</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>154.52</v>
+        <v>257.98</v>
       </c>
       <c r="L36" t="n">
-        <v>154.6</v>
+        <v>258.12</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>407.32</v>
+        <v>340.95</v>
       </c>
       <c r="K37" t="n">
-        <v>-184.02</v>
+        <v>-154.03</v>
       </c>
       <c r="L37" t="n">
-        <v>446.96</v>
+        <v>374.13</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-584.34</v>
+        <v>-564.5</v>
       </c>
       <c r="K38" t="n">
-        <v>-548.6</v>
+        <v>-529.97</v>
       </c>
       <c r="L38" t="n">
-        <v>801.51</v>
+        <v>774.3</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-107.74</v>
+        <v>-201.25</v>
       </c>
       <c r="K39" t="n">
-        <v>-62.16</v>
+        <v>-116.11</v>
       </c>
       <c r="L39" t="n">
-        <v>124.39</v>
+        <v>232.34</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>27.63</v>
+        <v>36.53</v>
       </c>
       <c r="K40" t="n">
-        <v>-269.84</v>
+        <v>-356.76</v>
       </c>
       <c r="L40" t="n">
-        <v>271.25</v>
+        <v>358.63</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>31.26</v>
+        <v>47.55</v>
       </c>
       <c r="K41" t="n">
-        <v>270.43</v>
+        <v>411.3</v>
       </c>
       <c r="L41" t="n">
-        <v>272.23</v>
+        <v>414.04</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-427.91</v>
+        <v>-560.5599999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>305.91</v>
+        <v>400.74</v>
       </c>
       <c r="L42" t="n">
-        <v>526.01</v>
+        <v>689.08</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>172.23</v>
+        <v>182.55</v>
       </c>
       <c r="K43" t="n">
-        <v>-675.0599999999999</v>
+        <v>-715.5</v>
       </c>
       <c r="L43" t="n">
-        <v>696.6799999999999</v>
+        <v>738.4299999999999</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>-37.38</v>
+        <v>-63.85</v>
       </c>
       <c r="K44" t="n">
-        <v>7.64</v>
+        <v>13.04</v>
       </c>
       <c r="L44" t="n">
-        <v>38.15</v>
+        <v>65.17</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>86.42</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>-153.46</v>
+        <v>-157.15</v>
       </c>
       <c r="L45" t="n">
-        <v>176.12</v>
+        <v>180.35</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>21.58</v>
+        <v>20.39</v>
       </c>
       <c r="K46" t="n">
-        <v>148.55</v>
+        <v>140.36</v>
       </c>
       <c r="L46" t="n">
-        <v>150.11</v>
+        <v>141.83</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-131.05</v>
+        <v>-127.48</v>
       </c>
       <c r="K47" t="n">
-        <v>-140.14</v>
+        <v>-136.32</v>
       </c>
       <c r="L47" t="n">
-        <v>191.87</v>
+        <v>186.64</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>180.92</v>
+        <v>169.98</v>
       </c>
       <c r="K48" t="n">
-        <v>-167.01</v>
+        <v>-156.91</v>
       </c>
       <c r="L48" t="n">
-        <v>246.22</v>
+        <v>231.34</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-185.78</v>
+        <v>-168.13</v>
       </c>
       <c r="K49" t="n">
-        <v>159.88</v>
+        <v>144.69</v>
       </c>
       <c r="L49" t="n">
-        <v>245.1</v>
+        <v>221.81</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>302.67</v>
+        <v>316.74</v>
       </c>
       <c r="K50" t="n">
-        <v>-243.56</v>
+        <v>-254.88</v>
       </c>
       <c r="L50" t="n">
-        <v>388.5</v>
+        <v>406.56</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-98.40000000000001</v>
+        <v>-98.56999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-328.54</v>
+        <v>-329.11</v>
       </c>
       <c r="L51" t="n">
-        <v>342.96</v>
+        <v>343.56</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>43.96</v>
+        <v>53.8</v>
       </c>
       <c r="K52" t="n">
-        <v>-175.36</v>
+        <v>-214.6</v>
       </c>
       <c r="L52" t="n">
-        <v>180.79</v>
+        <v>221.25</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>375.65</v>
+        <v>382.53</v>
       </c>
       <c r="K53" t="n">
-        <v>-318.06</v>
+        <v>-323.89</v>
       </c>
       <c r="L53" t="n">
-        <v>492.21</v>
+        <v>501.23</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>6.5</v>
+        <v>14.73</v>
       </c>
       <c r="K54" t="n">
-        <v>-86.68000000000001</v>
+        <v>-196.33</v>
       </c>
       <c r="L54" t="n">
-        <v>86.92</v>
+        <v>196.89</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>427.4</v>
+        <v>443.82</v>
       </c>
       <c r="K55" t="n">
-        <v>135.42</v>
+        <v>140.62</v>
       </c>
       <c r="L55" t="n">
-        <v>448.34</v>
+        <v>465.57</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-194.52</v>
+        <v>-348.87</v>
       </c>
       <c r="K56" t="n">
-        <v>178.52</v>
+        <v>320.17</v>
       </c>
       <c r="L56" t="n">
-        <v>264.03</v>
+        <v>473.51</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>527.65</v>
+        <v>583.49</v>
       </c>
       <c r="K57" t="n">
-        <v>-411.81</v>
+        <v>-455.39</v>
       </c>
       <c r="L57" t="n">
-        <v>669.33</v>
+        <v>740.17</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>414.89</v>
+        <v>529</v>
       </c>
       <c r="K58" t="n">
-        <v>-656.61</v>
+        <v>-837.21</v>
       </c>
       <c r="L58" t="n">
-        <v>776.7</v>
+        <v>990.34</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>152.91</v>
+        <v>137.44</v>
       </c>
       <c r="K59" t="n">
-        <v>-20.84</v>
+        <v>-18.73</v>
       </c>
       <c r="L59" t="n">
-        <v>154.33</v>
+        <v>138.71</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>312.71</v>
+        <v>262.5</v>
       </c>
       <c r="K60" t="n">
-        <v>307.91</v>
+        <v>258.47</v>
       </c>
       <c r="L60" t="n">
-        <v>438.86</v>
+        <v>368.4</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-267.43</v>
+        <v>-220.39</v>
       </c>
       <c r="K61" t="n">
-        <v>17.24</v>
+        <v>14.21</v>
       </c>
       <c r="L61" t="n">
-        <v>267.99</v>
+        <v>220.85</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-109.71</v>
+        <v>-113.59</v>
       </c>
       <c r="K62" t="n">
-        <v>20.97</v>
+        <v>21.72</v>
       </c>
       <c r="L62" t="n">
-        <v>111.69</v>
+        <v>115.65</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-94.62</v>
+        <v>-113.49</v>
       </c>
       <c r="K63" t="n">
-        <v>28.81</v>
+        <v>34.56</v>
       </c>
       <c r="L63" t="n">
-        <v>98.91</v>
+        <v>118.63</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-91.02</v>
+        <v>-133.25</v>
       </c>
       <c r="K64" t="n">
-        <v>25.29</v>
+        <v>37.03</v>
       </c>
       <c r="L64" t="n">
-        <v>94.47</v>
+        <v>138.3</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-219.02</v>
+        <v>-224.06</v>
       </c>
       <c r="K65" t="n">
-        <v>367.94</v>
+        <v>376.4</v>
       </c>
       <c r="L65" t="n">
-        <v>428.19</v>
+        <v>438.04</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-119.1</v>
+        <v>-141.09</v>
       </c>
       <c r="K66" t="n">
-        <v>270.53</v>
+        <v>320.48</v>
       </c>
       <c r="L66" t="n">
-        <v>295.59</v>
+        <v>350.16</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>197.31</v>
+        <v>283.32</v>
       </c>
       <c r="K67" t="n">
-        <v>-7.17</v>
+        <v>-10.29</v>
       </c>
       <c r="L67" t="n">
-        <v>197.44</v>
+        <v>283.51</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-163.82</v>
+        <v>-256.9</v>
       </c>
       <c r="K68" t="n">
-        <v>-60.7</v>
+        <v>-95.18000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>174.7</v>
+        <v>273.96</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-126.26</v>
+        <v>-177.76</v>
       </c>
       <c r="K69" t="n">
-        <v>-204.35</v>
+        <v>-287.72</v>
       </c>
       <c r="L69" t="n">
-        <v>240.21</v>
+        <v>338.2</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-273.81</v>
+        <v>-381.33</v>
       </c>
       <c r="K70" t="n">
-        <v>-28.13</v>
+        <v>-39.18</v>
       </c>
       <c r="L70" t="n">
-        <v>275.25</v>
+        <v>383.34</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>419.86</v>
+        <v>479.87</v>
       </c>
       <c r="K71" t="n">
-        <v>-168.38</v>
+        <v>-192.44</v>
       </c>
       <c r="L71" t="n">
-        <v>452.36</v>
+        <v>517.02</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-26.19</v>
+        <v>-58.29</v>
       </c>
       <c r="K72" t="n">
-        <v>155.04</v>
+        <v>345.06</v>
       </c>
       <c r="L72" t="n">
-        <v>157.23</v>
+        <v>349.95</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>414.33</v>
+        <v>595.5</v>
       </c>
       <c r="K73" t="n">
-        <v>-325.21</v>
+        <v>-467.41</v>
       </c>
       <c r="L73" t="n">
-        <v>526.72</v>
+        <v>757.03</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-115.98</v>
+        <v>-141.87</v>
       </c>
       <c r="K74" t="n">
-        <v>12.1</v>
+        <v>14.8</v>
       </c>
       <c r="L74" t="n">
-        <v>116.61</v>
+        <v>142.64</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-287.1</v>
+        <v>-240.01</v>
       </c>
       <c r="K75" t="n">
-        <v>7.43</v>
+        <v>6.21</v>
       </c>
       <c r="L75" t="n">
-        <v>287.19</v>
+        <v>240.09</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>151.28</v>
+        <v>157</v>
       </c>
       <c r="K76" t="n">
-        <v>33.43</v>
+        <v>34.69</v>
       </c>
       <c r="L76" t="n">
-        <v>154.93</v>
+        <v>160.78</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>76.73</v>
+        <v>137.47</v>
       </c>
       <c r="K77" t="n">
-        <v>-21.96</v>
+        <v>-39.34</v>
       </c>
       <c r="L77" t="n">
-        <v>79.81</v>
+        <v>142.99</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-84.94</v>
+        <v>-88.84</v>
       </c>
       <c r="K78" t="n">
-        <v>282.64</v>
+        <v>295.6</v>
       </c>
       <c r="L78" t="n">
-        <v>295.13</v>
+        <v>308.66</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-43.11</v>
+        <v>-40.59</v>
       </c>
       <c r="K79" t="n">
-        <v>-169.79</v>
+        <v>-159.86</v>
       </c>
       <c r="L79" t="n">
-        <v>175.17</v>
+        <v>164.93</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>213.45</v>
+        <v>284.24</v>
       </c>
       <c r="K80" t="n">
-        <v>8.19</v>
+        <v>10.91</v>
       </c>
       <c r="L80" t="n">
-        <v>213.61</v>
+        <v>284.45</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>137.77</v>
+        <v>155.72</v>
       </c>
       <c r="K81" t="n">
-        <v>412.62</v>
+        <v>466.39</v>
       </c>
       <c r="L81" t="n">
-        <v>435.01</v>
+        <v>491.7</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-390.13</v>
+        <v>-394.03</v>
       </c>
       <c r="K82" t="n">
-        <v>40.45</v>
+        <v>40.86</v>
       </c>
       <c r="L82" t="n">
-        <v>392.22</v>
+        <v>396.14</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>289.28</v>
+        <v>391.52</v>
       </c>
       <c r="K83" t="n">
-        <v>249.99</v>
+        <v>338.34</v>
       </c>
       <c r="L83" t="n">
-        <v>382.33</v>
+        <v>517.46</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>288.92</v>
+        <v>310.3</v>
       </c>
       <c r="K84" t="n">
-        <v>313.06</v>
+        <v>336.22</v>
       </c>
       <c r="L84" t="n">
-        <v>426.01</v>
+        <v>457.53</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>236.43</v>
+        <v>293.96</v>
       </c>
       <c r="K85" t="n">
-        <v>-107.65</v>
+        <v>-133.84</v>
       </c>
       <c r="L85" t="n">
-        <v>259.79</v>
+        <v>322.99</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>956.3099999999999</v>
+        <v>1114.71</v>
       </c>
       <c r="K86" t="n">
-        <v>-447.71</v>
+        <v>-521.87</v>
       </c>
       <c r="L86" t="n">
-        <v>1055.92</v>
+        <v>1230.82</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-239.63</v>
+        <v>-307.45</v>
       </c>
       <c r="K87" t="n">
-        <v>699.48</v>
+        <v>897.4299999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>739.39</v>
+        <v>948.63</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-332.52</v>
+        <v>-431.04</v>
       </c>
       <c r="K88" t="n">
-        <v>-409.5</v>
+        <v>-530.83</v>
       </c>
       <c r="L88" t="n">
-        <v>527.5</v>
+        <v>683.79</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-03.xlsx
+++ b/output/2024-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-109.65</v>
+        <v>-93.12</v>
       </c>
       <c r="K14" t="n">
-        <v>51.72</v>
+        <v>43.92</v>
       </c>
       <c r="L14" t="n">
-        <v>121.23</v>
+        <v>102.96</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>30.15</v>
+        <v>25.06</v>
       </c>
       <c r="K15" t="n">
-        <v>-39.82</v>
+        <v>-33.09</v>
       </c>
       <c r="L15" t="n">
-        <v>49.95</v>
+        <v>41.51</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>44.39</v>
+        <v>35.56</v>
       </c>
       <c r="K16" t="n">
-        <v>151.43</v>
+        <v>121.33</v>
       </c>
       <c r="L16" t="n">
-        <v>157.81</v>
+        <v>126.43</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>189.66</v>
+        <v>155.99</v>
       </c>
       <c r="K17" t="n">
-        <v>-53.7</v>
+        <v>-44.17</v>
       </c>
       <c r="L17" t="n">
-        <v>197.11</v>
+        <v>162.12</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-84.05</v>
+        <v>-62.84</v>
       </c>
       <c r="K18" t="n">
-        <v>98.77</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>129.69</v>
+        <v>96.97</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-106.9</v>
+        <v>-77.31999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>24.83</v>
+        <v>17.96</v>
       </c>
       <c r="L19" t="n">
-        <v>109.74</v>
+        <v>79.38</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>145.86</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>130.22</v>
+        <v>80.53</v>
       </c>
       <c r="L20" t="n">
-        <v>195.54</v>
+        <v>120.93</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>227.79</v>
+        <v>148.59</v>
       </c>
       <c r="K21" t="n">
-        <v>67.97</v>
+        <v>44.34</v>
       </c>
       <c r="L21" t="n">
-        <v>237.71</v>
+        <v>155.07</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>322.85</v>
+        <v>194.66</v>
       </c>
       <c r="K22" t="n">
-        <v>-349.04</v>
+        <v>-210.46</v>
       </c>
       <c r="L22" t="n">
-        <v>475.46</v>
+        <v>286.68</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-230.2</v>
+        <v>-120.03</v>
       </c>
       <c r="K23" t="n">
-        <v>-454.84</v>
+        <v>-237.16</v>
       </c>
       <c r="L23" t="n">
-        <v>509.78</v>
+        <v>265.81</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-198.32</v>
+        <v>-111.59</v>
       </c>
       <c r="K24" t="n">
-        <v>113.29</v>
+        <v>63.75</v>
       </c>
       <c r="L24" t="n">
-        <v>228.4</v>
+        <v>128.51</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-83.68000000000001</v>
+        <v>-48.52</v>
       </c>
       <c r="K25" t="n">
-        <v>-221.3</v>
+        <v>-128.31</v>
       </c>
       <c r="L25" t="n">
-        <v>236.6</v>
+        <v>137.18</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-147.81</v>
+        <v>-74.73</v>
       </c>
       <c r="K26" t="n">
-        <v>-290.74</v>
+        <v>-146.98</v>
       </c>
       <c r="L26" t="n">
-        <v>326.16</v>
+        <v>164.88</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>386.33</v>
+        <v>180.34</v>
       </c>
       <c r="K27" t="n">
-        <v>-489.58</v>
+        <v>-228.54</v>
       </c>
       <c r="L27" t="n">
-        <v>623.65</v>
+        <v>291.13</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>563.88</v>
+        <v>272.73</v>
       </c>
       <c r="K28" t="n">
-        <v>-82.23</v>
+        <v>-39.77</v>
       </c>
       <c r="L28" t="n">
-        <v>569.85</v>
+        <v>275.62</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>26.23</v>
+        <v>21.9</v>
       </c>
       <c r="K29" t="n">
-        <v>101.38</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>104.72</v>
+        <v>87.44</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-141.42</v>
+        <v>-110.15</v>
       </c>
       <c r="K30" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="L30" t="n">
-        <v>141.43</v>
+        <v>110.15</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>114.46</v>
+        <v>78.62</v>
       </c>
       <c r="K31" t="n">
-        <v>-212.15</v>
+        <v>-145.73</v>
       </c>
       <c r="L31" t="n">
-        <v>241.06</v>
+        <v>165.58</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>91.06999999999999</v>
+        <v>63.52</v>
       </c>
       <c r="K32" t="n">
-        <v>241.57</v>
+        <v>168.49</v>
       </c>
       <c r="L32" t="n">
-        <v>258.17</v>
+        <v>180.06</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>102.79</v>
+        <v>69.08</v>
       </c>
       <c r="K33" t="n">
-        <v>-80.2</v>
+        <v>-53.9</v>
       </c>
       <c r="L33" t="n">
-        <v>130.38</v>
+        <v>87.62</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>84.98999999999999</v>
+        <v>55.62</v>
       </c>
       <c r="K34" t="n">
-        <v>124.92</v>
+        <v>81.75</v>
       </c>
       <c r="L34" t="n">
-        <v>151.09</v>
+        <v>98.88</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>96.06999999999999</v>
+        <v>63.58</v>
       </c>
       <c r="K35" t="n">
-        <v>329.13</v>
+        <v>217.82</v>
       </c>
       <c r="L35" t="n">
-        <v>342.87</v>
+        <v>226.91</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.300000000000001</v>
+        <v>-4.57</v>
       </c>
       <c r="K36" t="n">
-        <v>257.98</v>
+        <v>142.14</v>
       </c>
       <c r="L36" t="n">
-        <v>258.12</v>
+        <v>142.21</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>340.95</v>
+        <v>224.36</v>
       </c>
       <c r="K37" t="n">
-        <v>-154.03</v>
+        <v>-101.36</v>
       </c>
       <c r="L37" t="n">
-        <v>374.13</v>
+        <v>246.2</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-564.5</v>
+        <v>-288.94</v>
       </c>
       <c r="K38" t="n">
-        <v>-529.97</v>
+        <v>-271.26</v>
       </c>
       <c r="L38" t="n">
-        <v>774.3</v>
+        <v>396.32</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-201.25</v>
+        <v>-112.32</v>
       </c>
       <c r="K39" t="n">
-        <v>-116.11</v>
+        <v>-64.8</v>
       </c>
       <c r="L39" t="n">
-        <v>232.34</v>
+        <v>129.67</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>36.53</v>
+        <v>20.47</v>
       </c>
       <c r="K40" t="n">
-        <v>-356.76</v>
+        <v>-199.92</v>
       </c>
       <c r="L40" t="n">
-        <v>358.63</v>
+        <v>200.97</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>47.55</v>
+        <v>24.24</v>
       </c>
       <c r="K41" t="n">
-        <v>411.3</v>
+        <v>209.69</v>
       </c>
       <c r="L41" t="n">
-        <v>414.04</v>
+        <v>211.09</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-560.5599999999999</v>
+        <v>-259.97</v>
       </c>
       <c r="K42" t="n">
-        <v>400.74</v>
+        <v>185.85</v>
       </c>
       <c r="L42" t="n">
-        <v>689.08</v>
+        <v>319.57</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>182.55</v>
+        <v>97.27</v>
       </c>
       <c r="K43" t="n">
-        <v>-715.5</v>
+        <v>-381.22</v>
       </c>
       <c r="L43" t="n">
-        <v>738.4299999999999</v>
+        <v>393.44</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>-63.85</v>
+        <v>-48.85</v>
       </c>
       <c r="K44" t="n">
-        <v>13.04</v>
+        <v>9.98</v>
       </c>
       <c r="L44" t="n">
-        <v>65.17</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>88.48999999999999</v>
+        <v>60.74</v>
       </c>
       <c r="K45" t="n">
-        <v>-157.15</v>
+        <v>-107.86</v>
       </c>
       <c r="L45" t="n">
-        <v>180.35</v>
+        <v>123.79</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>20.39</v>
+        <v>15.46</v>
       </c>
       <c r="K46" t="n">
-        <v>140.36</v>
+        <v>106.45</v>
       </c>
       <c r="L46" t="n">
-        <v>141.83</v>
+        <v>107.57</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-127.48</v>
+        <v>-90.91</v>
       </c>
       <c r="K47" t="n">
-        <v>-136.32</v>
+        <v>-97.2</v>
       </c>
       <c r="L47" t="n">
-        <v>186.64</v>
+        <v>133.09</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>169.98</v>
+        <v>117.17</v>
       </c>
       <c r="K48" t="n">
-        <v>-156.91</v>
+        <v>-108.16</v>
       </c>
       <c r="L48" t="n">
-        <v>231.34</v>
+        <v>159.46</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-168.13</v>
+        <v>-117.73</v>
       </c>
       <c r="K49" t="n">
-        <v>144.69</v>
+        <v>101.32</v>
       </c>
       <c r="L49" t="n">
-        <v>221.81</v>
+        <v>155.32</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>316.74</v>
+        <v>183.07</v>
       </c>
       <c r="K50" t="n">
-        <v>-254.88</v>
+        <v>-147.31</v>
       </c>
       <c r="L50" t="n">
-        <v>406.56</v>
+        <v>234.98</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-98.56999999999999</v>
+        <v>-63.07</v>
       </c>
       <c r="K51" t="n">
-        <v>-329.11</v>
+        <v>-210.58</v>
       </c>
       <c r="L51" t="n">
-        <v>343.56</v>
+        <v>219.82</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>53.8</v>
+        <v>34.87</v>
       </c>
       <c r="K52" t="n">
-        <v>-214.6</v>
+        <v>-139.09</v>
       </c>
       <c r="L52" t="n">
-        <v>221.25</v>
+        <v>143.39</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>382.53</v>
+        <v>223.15</v>
       </c>
       <c r="K53" t="n">
-        <v>-323.89</v>
+        <v>-188.94</v>
       </c>
       <c r="L53" t="n">
-        <v>501.23</v>
+        <v>292.4</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>14.73</v>
+        <v>8.02</v>
       </c>
       <c r="K54" t="n">
-        <v>-196.33</v>
+        <v>-106.84</v>
       </c>
       <c r="L54" t="n">
-        <v>196.89</v>
+        <v>107.14</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>443.82</v>
+        <v>249.47</v>
       </c>
       <c r="K55" t="n">
-        <v>140.62</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>465.57</v>
+        <v>261.69</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-348.87</v>
+        <v>-166.84</v>
       </c>
       <c r="K56" t="n">
-        <v>320.17</v>
+        <v>153.11</v>
       </c>
       <c r="L56" t="n">
-        <v>473.51</v>
+        <v>226.45</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>583.49</v>
+        <v>307.23</v>
       </c>
       <c r="K57" t="n">
-        <v>-455.39</v>
+        <v>-239.78</v>
       </c>
       <c r="L57" t="n">
-        <v>740.17</v>
+        <v>389.73</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>529</v>
+        <v>237.06</v>
       </c>
       <c r="K58" t="n">
-        <v>-837.21</v>
+        <v>-375.17</v>
       </c>
       <c r="L58" t="n">
-        <v>990.34</v>
+        <v>443.79</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>137.44</v>
+        <v>104.22</v>
       </c>
       <c r="K59" t="n">
-        <v>-18.73</v>
+        <v>-14.2</v>
       </c>
       <c r="L59" t="n">
-        <v>138.71</v>
+        <v>105.18</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>262.5</v>
+        <v>177.79</v>
       </c>
       <c r="K60" t="n">
-        <v>258.47</v>
+        <v>175.06</v>
       </c>
       <c r="L60" t="n">
-        <v>368.4</v>
+        <v>249.51</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-220.39</v>
+        <v>-170.96</v>
       </c>
       <c r="K61" t="n">
-        <v>14.21</v>
+        <v>11.02</v>
       </c>
       <c r="L61" t="n">
-        <v>220.85</v>
+        <v>171.31</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-113.59</v>
+        <v>-88.73</v>
       </c>
       <c r="K62" t="n">
-        <v>21.72</v>
+        <v>16.96</v>
       </c>
       <c r="L62" t="n">
-        <v>115.65</v>
+        <v>90.34</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-113.49</v>
+        <v>-85.78</v>
       </c>
       <c r="K63" t="n">
-        <v>34.56</v>
+        <v>26.12</v>
       </c>
       <c r="L63" t="n">
-        <v>118.63</v>
+        <v>89.67</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-133.25</v>
+        <v>-88.61</v>
       </c>
       <c r="K64" t="n">
-        <v>37.03</v>
+        <v>24.62</v>
       </c>
       <c r="L64" t="n">
-        <v>138.3</v>
+        <v>91.97</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-224.06</v>
+        <v>-129.24</v>
       </c>
       <c r="K65" t="n">
-        <v>376.4</v>
+        <v>217.12</v>
       </c>
       <c r="L65" t="n">
-        <v>438.04</v>
+        <v>252.67</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-141.09</v>
+        <v>-81.73999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>320.48</v>
+        <v>185.67</v>
       </c>
       <c r="L66" t="n">
-        <v>350.16</v>
+        <v>202.87</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>283.32</v>
+        <v>159.9</v>
       </c>
       <c r="K67" t="n">
-        <v>-10.29</v>
+        <v>-5.81</v>
       </c>
       <c r="L67" t="n">
-        <v>283.51</v>
+        <v>160.01</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-256.9</v>
+        <v>-145.42</v>
       </c>
       <c r="K68" t="n">
-        <v>-95.18000000000001</v>
+        <v>-53.88</v>
       </c>
       <c r="L68" t="n">
-        <v>273.96</v>
+        <v>155.08</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-177.76</v>
+        <v>-97.23</v>
       </c>
       <c r="K69" t="n">
-        <v>-287.72</v>
+        <v>-157.37</v>
       </c>
       <c r="L69" t="n">
-        <v>338.2</v>
+        <v>184.99</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-381.33</v>
+        <v>-214.43</v>
       </c>
       <c r="K70" t="n">
-        <v>-39.18</v>
+        <v>-22.03</v>
       </c>
       <c r="L70" t="n">
-        <v>383.34</v>
+        <v>215.56</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>479.87</v>
+        <v>261.1</v>
       </c>
       <c r="K71" t="n">
-        <v>-192.44</v>
+        <v>-104.71</v>
       </c>
       <c r="L71" t="n">
-        <v>517.02</v>
+        <v>281.31</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-58.29</v>
+        <v>-29.06</v>
       </c>
       <c r="K72" t="n">
-        <v>345.06</v>
+        <v>172.01</v>
       </c>
       <c r="L72" t="n">
-        <v>349.95</v>
+        <v>174.45</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>595.5</v>
+        <v>272.29</v>
       </c>
       <c r="K73" t="n">
-        <v>-467.41</v>
+        <v>-213.72</v>
       </c>
       <c r="L73" t="n">
-        <v>757.03</v>
+        <v>346.15</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-141.87</v>
+        <v>-98.2</v>
       </c>
       <c r="K74" t="n">
-        <v>14.8</v>
+        <v>10.25</v>
       </c>
       <c r="L74" t="n">
-        <v>142.64</v>
+        <v>98.73</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-240.01</v>
+        <v>-177.11</v>
       </c>
       <c r="K75" t="n">
-        <v>6.21</v>
+        <v>4.58</v>
       </c>
       <c r="L75" t="n">
-        <v>240.09</v>
+        <v>177.17</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>157</v>
+        <v>112.38</v>
       </c>
       <c r="K76" t="n">
-        <v>34.69</v>
+        <v>24.83</v>
       </c>
       <c r="L76" t="n">
-        <v>160.78</v>
+        <v>115.09</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>137.47</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-39.34</v>
+        <v>-26.25</v>
       </c>
       <c r="L77" t="n">
-        <v>142.99</v>
+        <v>95.42</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-88.84</v>
+        <v>-58.71</v>
       </c>
       <c r="K78" t="n">
-        <v>295.6</v>
+        <v>195.37</v>
       </c>
       <c r="L78" t="n">
-        <v>308.66</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-40.59</v>
+        <v>-31.36</v>
       </c>
       <c r="K79" t="n">
-        <v>-159.86</v>
+        <v>-123.49</v>
       </c>
       <c r="L79" t="n">
-        <v>164.93</v>
+        <v>127.41</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>284.24</v>
+        <v>159.9</v>
       </c>
       <c r="K80" t="n">
-        <v>10.91</v>
+        <v>6.13</v>
       </c>
       <c r="L80" t="n">
-        <v>284.45</v>
+        <v>160.02</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>155.72</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>466.39</v>
+        <v>258.43</v>
       </c>
       <c r="L81" t="n">
-        <v>491.7</v>
+        <v>272.45</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-394.03</v>
+        <v>-242.67</v>
       </c>
       <c r="K82" t="n">
-        <v>40.86</v>
+        <v>25.16</v>
       </c>
       <c r="L82" t="n">
-        <v>396.14</v>
+        <v>243.97</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>391.52</v>
+        <v>196.62</v>
       </c>
       <c r="K83" t="n">
-        <v>338.34</v>
+        <v>169.91</v>
       </c>
       <c r="L83" t="n">
-        <v>517.46</v>
+        <v>259.86</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>310.3</v>
+        <v>173.01</v>
       </c>
       <c r="K84" t="n">
-        <v>336.22</v>
+        <v>187.46</v>
       </c>
       <c r="L84" t="n">
-        <v>457.53</v>
+        <v>255.09</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>293.96</v>
+        <v>165.58</v>
       </c>
       <c r="K85" t="n">
-        <v>-133.84</v>
+        <v>-75.39</v>
       </c>
       <c r="L85" t="n">
-        <v>322.99</v>
+        <v>181.93</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>1114.71</v>
+        <v>501.13</v>
       </c>
       <c r="K86" t="n">
-        <v>-521.87</v>
+        <v>-234.61</v>
       </c>
       <c r="L86" t="n">
-        <v>1230.82</v>
+        <v>553.33</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-307.45</v>
+        <v>-135.84</v>
       </c>
       <c r="K87" t="n">
-        <v>897.4299999999999</v>
+        <v>396.52</v>
       </c>
       <c r="L87" t="n">
-        <v>948.63</v>
+        <v>419.14</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-431.04</v>
+        <v>-211.31</v>
       </c>
       <c r="K88" t="n">
-        <v>-530.83</v>
+        <v>-260.23</v>
       </c>
       <c r="L88" t="n">
-        <v>683.79</v>
+        <v>335.22</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-03.xlsx
+++ b/output/2024-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-93.12</v>
+        <v>-95.81</v>
       </c>
       <c r="K14" t="n">
-        <v>43.92</v>
+        <v>45.19</v>
       </c>
       <c r="L14" t="n">
-        <v>102.96</v>
+        <v>105.93</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>25.06</v>
+        <v>26.23</v>
       </c>
       <c r="K15" t="n">
-        <v>-33.09</v>
+        <v>-34.65</v>
       </c>
       <c r="L15" t="n">
-        <v>41.51</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>35.56</v>
+        <v>36.82</v>
       </c>
       <c r="K16" t="n">
-        <v>121.33</v>
+        <v>125.63</v>
       </c>
       <c r="L16" t="n">
-        <v>126.43</v>
+        <v>130.91</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>155.99</v>
+        <v>167.37</v>
       </c>
       <c r="K17" t="n">
-        <v>-44.17</v>
+        <v>-47.39</v>
       </c>
       <c r="L17" t="n">
-        <v>162.12</v>
+        <v>173.95</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-62.84</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>73.84999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="L18" t="n">
-        <v>96.97</v>
+        <v>104.31</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-77.31999999999999</v>
+        <v>-83.36</v>
       </c>
       <c r="K19" t="n">
-        <v>17.96</v>
+        <v>19.37</v>
       </c>
       <c r="L19" t="n">
-        <v>79.38</v>
+        <v>85.56999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>90.20999999999999</v>
+        <v>102.6</v>
       </c>
       <c r="K20" t="n">
-        <v>80.53</v>
+        <v>91.59</v>
       </c>
       <c r="L20" t="n">
-        <v>120.93</v>
+        <v>137.53</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>148.59</v>
+        <v>164.94</v>
       </c>
       <c r="K21" t="n">
-        <v>44.34</v>
+        <v>49.21</v>
       </c>
       <c r="L21" t="n">
-        <v>155.07</v>
+        <v>172.12</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>194.66</v>
+        <v>220.61</v>
       </c>
       <c r="K22" t="n">
-        <v>-210.46</v>
+        <v>-238.51</v>
       </c>
       <c r="L22" t="n">
-        <v>286.68</v>
+        <v>324.89</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-120.03</v>
+        <v>-139.88</v>
       </c>
       <c r="K23" t="n">
-        <v>-237.16</v>
+        <v>-276.37</v>
       </c>
       <c r="L23" t="n">
-        <v>265.81</v>
+        <v>309.75</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-111.59</v>
+        <v>-129.44</v>
       </c>
       <c r="K24" t="n">
-        <v>63.75</v>
+        <v>73.95</v>
       </c>
       <c r="L24" t="n">
-        <v>128.51</v>
+        <v>149.07</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-48.52</v>
+        <v>-55.66</v>
       </c>
       <c r="K25" t="n">
-        <v>-128.31</v>
+        <v>-147.2</v>
       </c>
       <c r="L25" t="n">
-        <v>137.18</v>
+        <v>157.37</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-74.73</v>
+        <v>-86.83</v>
       </c>
       <c r="K26" t="n">
-        <v>-146.98</v>
+        <v>-170.79</v>
       </c>
       <c r="L26" t="n">
-        <v>164.88</v>
+        <v>191.59</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>180.34</v>
+        <v>214.22</v>
       </c>
       <c r="K27" t="n">
-        <v>-228.54</v>
+        <v>-271.48</v>
       </c>
       <c r="L27" t="n">
-        <v>291.13</v>
+        <v>345.82</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>272.73</v>
+        <v>322.06</v>
       </c>
       <c r="K28" t="n">
-        <v>-39.77</v>
+        <v>-46.96</v>
       </c>
       <c r="L28" t="n">
-        <v>275.62</v>
+        <v>325.47</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>21.9</v>
+        <v>22.85</v>
       </c>
       <c r="K29" t="n">
-        <v>84.65000000000001</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>87.44</v>
+        <v>91.23</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-110.15</v>
+        <v>-115.89</v>
       </c>
       <c r="K30" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="L30" t="n">
-        <v>110.15</v>
+        <v>115.9</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>78.62</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-145.73</v>
+        <v>-153.18</v>
       </c>
       <c r="L31" t="n">
-        <v>165.58</v>
+        <v>174.06</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>63.52</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>168.49</v>
+        <v>183.72</v>
       </c>
       <c r="L32" t="n">
-        <v>180.06</v>
+        <v>196.35</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>69.08</v>
+        <v>76.62</v>
       </c>
       <c r="K33" t="n">
-        <v>-53.9</v>
+        <v>-59.78</v>
       </c>
       <c r="L33" t="n">
-        <v>87.62</v>
+        <v>97.18000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>55.62</v>
+        <v>61.05</v>
       </c>
       <c r="K34" t="n">
-        <v>81.75</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>98.88</v>
+        <v>108.54</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>63.58</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>217.82</v>
+        <v>239.94</v>
       </c>
       <c r="L35" t="n">
-        <v>226.91</v>
+        <v>249.95</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.57</v>
+        <v>-5.19</v>
       </c>
       <c r="K36" t="n">
-        <v>142.14</v>
+        <v>161.39</v>
       </c>
       <c r="L36" t="n">
-        <v>142.21</v>
+        <v>161.47</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>224.36</v>
+        <v>251.98</v>
       </c>
       <c r="K37" t="n">
-        <v>-101.36</v>
+        <v>-113.84</v>
       </c>
       <c r="L37" t="n">
-        <v>246.2</v>
+        <v>276.5</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-288.94</v>
+        <v>-341.17</v>
       </c>
       <c r="K38" t="n">
-        <v>-271.26</v>
+        <v>-320.3</v>
       </c>
       <c r="L38" t="n">
-        <v>396.32</v>
+        <v>467.96</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-112.32</v>
+        <v>-130.11</v>
       </c>
       <c r="K39" t="n">
-        <v>-64.8</v>
+        <v>-75.06999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>129.67</v>
+        <v>150.22</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>20.47</v>
+        <v>23.47</v>
       </c>
       <c r="K40" t="n">
-        <v>-199.92</v>
+        <v>-229.22</v>
       </c>
       <c r="L40" t="n">
-        <v>200.97</v>
+        <v>230.42</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>24.24</v>
+        <v>28.09</v>
       </c>
       <c r="K41" t="n">
-        <v>209.69</v>
+        <v>242.98</v>
       </c>
       <c r="L41" t="n">
-        <v>211.09</v>
+        <v>244.6</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-259.97</v>
+        <v>-307.85</v>
       </c>
       <c r="K42" t="n">
-        <v>185.85</v>
+        <v>220.08</v>
       </c>
       <c r="L42" t="n">
-        <v>319.57</v>
+        <v>378.43</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>97.27</v>
+        <v>113.46</v>
       </c>
       <c r="K43" t="n">
-        <v>-381.22</v>
+        <v>-444.7</v>
       </c>
       <c r="L43" t="n">
-        <v>393.44</v>
+        <v>458.95</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>-48.85</v>
+        <v>-51.73</v>
       </c>
       <c r="K44" t="n">
-        <v>9.98</v>
+        <v>10.57</v>
       </c>
       <c r="L44" t="n">
-        <v>49.86</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>60.74</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>-107.86</v>
+        <v>-114.03</v>
       </c>
       <c r="L45" t="n">
-        <v>123.79</v>
+        <v>130.87</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>15.46</v>
+        <v>16.17</v>
       </c>
       <c r="K46" t="n">
-        <v>106.45</v>
+        <v>111.3</v>
       </c>
       <c r="L46" t="n">
-        <v>107.57</v>
+        <v>112.46</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-90.91</v>
+        <v>-99.44</v>
       </c>
       <c r="K47" t="n">
-        <v>-97.2</v>
+        <v>-106.33</v>
       </c>
       <c r="L47" t="n">
-        <v>133.09</v>
+        <v>145.59</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>117.17</v>
+        <v>126.85</v>
       </c>
       <c r="K48" t="n">
-        <v>-108.16</v>
+        <v>-117.09</v>
       </c>
       <c r="L48" t="n">
-        <v>159.46</v>
+        <v>172.63</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-117.73</v>
+        <v>-127.94</v>
       </c>
       <c r="K49" t="n">
-        <v>101.32</v>
+        <v>110.1</v>
       </c>
       <c r="L49" t="n">
-        <v>155.32</v>
+        <v>168.79</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>183.07</v>
+        <v>208.83</v>
       </c>
       <c r="K50" t="n">
-        <v>-147.31</v>
+        <v>-168.04</v>
       </c>
       <c r="L50" t="n">
-        <v>234.98</v>
+        <v>268.05</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-63.07</v>
+        <v>-70.44</v>
       </c>
       <c r="K51" t="n">
-        <v>-210.58</v>
+        <v>-235.19</v>
       </c>
       <c r="L51" t="n">
-        <v>219.82</v>
+        <v>245.52</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>34.87</v>
+        <v>39.09</v>
       </c>
       <c r="K52" t="n">
-        <v>-139.09</v>
+        <v>-155.93</v>
       </c>
       <c r="L52" t="n">
-        <v>143.39</v>
+        <v>160.76</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>223.15</v>
+        <v>254.08</v>
       </c>
       <c r="K53" t="n">
-        <v>-188.94</v>
+        <v>-215.12</v>
       </c>
       <c r="L53" t="n">
-        <v>292.4</v>
+        <v>332.92</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>8.02</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-106.84</v>
+        <v>-124.87</v>
       </c>
       <c r="L54" t="n">
-        <v>107.14</v>
+        <v>125.22</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>249.47</v>
+        <v>285.71</v>
       </c>
       <c r="K55" t="n">
-        <v>79.04000000000001</v>
+        <v>90.53</v>
       </c>
       <c r="L55" t="n">
-        <v>261.69</v>
+        <v>299.7</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-166.84</v>
+        <v>-195.6</v>
       </c>
       <c r="K56" t="n">
-        <v>153.11</v>
+        <v>179.52</v>
       </c>
       <c r="L56" t="n">
-        <v>226.45</v>
+        <v>265.49</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>307.23</v>
+        <v>357.97</v>
       </c>
       <c r="K57" t="n">
-        <v>-239.78</v>
+        <v>-279.38</v>
       </c>
       <c r="L57" t="n">
-        <v>389.73</v>
+        <v>454.09</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>237.06</v>
+        <v>280.07</v>
       </c>
       <c r="K58" t="n">
-        <v>-375.17</v>
+        <v>-443.24</v>
       </c>
       <c r="L58" t="n">
-        <v>443.79</v>
+        <v>524.3099999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>104.22</v>
+        <v>109.41</v>
       </c>
       <c r="K59" t="n">
-        <v>-14.2</v>
+        <v>-14.91</v>
       </c>
       <c r="L59" t="n">
-        <v>105.18</v>
+        <v>110.42</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>177.79</v>
+        <v>187.66</v>
       </c>
       <c r="K60" t="n">
-        <v>175.06</v>
+        <v>184.78</v>
       </c>
       <c r="L60" t="n">
-        <v>249.51</v>
+        <v>263.36</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-170.96</v>
+        <v>-176.96</v>
       </c>
       <c r="K61" t="n">
-        <v>11.02</v>
+        <v>11.41</v>
       </c>
       <c r="L61" t="n">
-        <v>171.31</v>
+        <v>177.33</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-88.73</v>
+        <v>-95.47</v>
       </c>
       <c r="K62" t="n">
-        <v>16.96</v>
+        <v>18.25</v>
       </c>
       <c r="L62" t="n">
-        <v>90.34</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-85.78</v>
+        <v>-92.43000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>26.12</v>
+        <v>28.15</v>
       </c>
       <c r="L63" t="n">
-        <v>89.67</v>
+        <v>96.62</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-88.61</v>
+        <v>-97.78</v>
       </c>
       <c r="K64" t="n">
-        <v>24.62</v>
+        <v>27.17</v>
       </c>
       <c r="L64" t="n">
-        <v>91.97</v>
+        <v>101.48</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-129.24</v>
+        <v>-146.74</v>
       </c>
       <c r="K65" t="n">
-        <v>217.12</v>
+        <v>246.52</v>
       </c>
       <c r="L65" t="n">
-        <v>252.67</v>
+        <v>286.89</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-81.73999999999999</v>
+        <v>-93.42</v>
       </c>
       <c r="K66" t="n">
-        <v>185.67</v>
+        <v>212.21</v>
       </c>
       <c r="L66" t="n">
-        <v>202.87</v>
+        <v>231.86</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>159.9</v>
+        <v>181.97</v>
       </c>
       <c r="K67" t="n">
-        <v>-5.81</v>
+        <v>-6.61</v>
       </c>
       <c r="L67" t="n">
-        <v>160.01</v>
+        <v>182.09</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-145.42</v>
+        <v>-165.88</v>
       </c>
       <c r="K68" t="n">
-        <v>-53.88</v>
+        <v>-61.46</v>
       </c>
       <c r="L68" t="n">
-        <v>155.08</v>
+        <v>176.9</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-97.23</v>
+        <v>-112.19</v>
       </c>
       <c r="K69" t="n">
-        <v>-157.37</v>
+        <v>-181.58</v>
       </c>
       <c r="L69" t="n">
-        <v>184.99</v>
+        <v>213.44</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-214.43</v>
+        <v>-240.77</v>
       </c>
       <c r="K70" t="n">
-        <v>-22.03</v>
+        <v>-24.74</v>
       </c>
       <c r="L70" t="n">
-        <v>215.56</v>
+        <v>242.04</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>261.1</v>
+        <v>302.11</v>
       </c>
       <c r="K71" t="n">
-        <v>-104.71</v>
+        <v>-121.15</v>
       </c>
       <c r="L71" t="n">
-        <v>281.31</v>
+        <v>325.49</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-29.06</v>
+        <v>-34.03</v>
       </c>
       <c r="K72" t="n">
-        <v>172.01</v>
+        <v>201.45</v>
       </c>
       <c r="L72" t="n">
-        <v>174.45</v>
+        <v>204.3</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>272.29</v>
+        <v>318.49</v>
       </c>
       <c r="K73" t="n">
-        <v>-213.72</v>
+        <v>-249.98</v>
       </c>
       <c r="L73" t="n">
-        <v>346.15</v>
+        <v>404.88</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-98.2</v>
+        <v>-104.08</v>
       </c>
       <c r="K74" t="n">
-        <v>10.25</v>
+        <v>10.86</v>
       </c>
       <c r="L74" t="n">
-        <v>98.73</v>
+        <v>104.64</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-177.11</v>
+        <v>-185.61</v>
       </c>
       <c r="K75" t="n">
-        <v>4.58</v>
+        <v>4.8</v>
       </c>
       <c r="L75" t="n">
-        <v>177.17</v>
+        <v>185.67</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>112.38</v>
+        <v>118.86</v>
       </c>
       <c r="K76" t="n">
-        <v>24.83</v>
+        <v>26.26</v>
       </c>
       <c r="L76" t="n">
-        <v>115.09</v>
+        <v>121.73</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>91.73999999999999</v>
+        <v>100.5</v>
       </c>
       <c r="K77" t="n">
-        <v>-26.25</v>
+        <v>-28.76</v>
       </c>
       <c r="L77" t="n">
-        <v>95.42</v>
+        <v>104.53</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-58.71</v>
+        <v>-64.48</v>
       </c>
       <c r="K78" t="n">
-        <v>195.37</v>
+        <v>214.55</v>
       </c>
       <c r="L78" t="n">
-        <v>204</v>
+        <v>224.03</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-31.36</v>
+        <v>-33.53</v>
       </c>
       <c r="K79" t="n">
-        <v>-123.49</v>
+        <v>-132.06</v>
       </c>
       <c r="L79" t="n">
-        <v>127.41</v>
+        <v>136.25</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>159.9</v>
+        <v>183.55</v>
       </c>
       <c r="K80" t="n">
-        <v>6.13</v>
+        <v>7.04</v>
       </c>
       <c r="L80" t="n">
-        <v>160.02</v>
+        <v>183.68</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>86.29000000000001</v>
+        <v>98.02</v>
       </c>
       <c r="K81" t="n">
-        <v>258.43</v>
+        <v>293.58</v>
       </c>
       <c r="L81" t="n">
-        <v>272.45</v>
+        <v>309.51</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-242.67</v>
+        <v>-273.77</v>
       </c>
       <c r="K82" t="n">
-        <v>25.16</v>
+        <v>28.39</v>
       </c>
       <c r="L82" t="n">
-        <v>243.97</v>
+        <v>275.24</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>196.62</v>
+        <v>226.91</v>
       </c>
       <c r="K83" t="n">
-        <v>169.91</v>
+        <v>196.09</v>
       </c>
       <c r="L83" t="n">
-        <v>259.86</v>
+        <v>299.9</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>173.01</v>
+        <v>198.28</v>
       </c>
       <c r="K84" t="n">
-        <v>187.46</v>
+        <v>214.84</v>
       </c>
       <c r="L84" t="n">
-        <v>255.09</v>
+        <v>292.35</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>165.58</v>
+        <v>192.24</v>
       </c>
       <c r="K85" t="n">
-        <v>-75.39</v>
+        <v>-87.53</v>
       </c>
       <c r="L85" t="n">
-        <v>181.93</v>
+        <v>211.23</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>501.13</v>
+        <v>590.28</v>
       </c>
       <c r="K86" t="n">
-        <v>-234.61</v>
+        <v>-276.35</v>
       </c>
       <c r="L86" t="n">
-        <v>553.33</v>
+        <v>651.76</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-135.84</v>
+        <v>-161.16</v>
       </c>
       <c r="K87" t="n">
-        <v>396.52</v>
+        <v>470.42</v>
       </c>
       <c r="L87" t="n">
-        <v>419.14</v>
+        <v>497.26</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-211.31</v>
+        <v>-246.04</v>
       </c>
       <c r="K88" t="n">
-        <v>-260.23</v>
+        <v>-303</v>
       </c>
       <c r="L88" t="n">
-        <v>335.22</v>
+        <v>390.32</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-03.xlsx
+++ b/output/2024-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-95.81</v>
+        <v>-59.56</v>
       </c>
       <c r="K14" t="n">
-        <v>45.19</v>
+        <v>28.09</v>
       </c>
       <c r="L14" t="n">
-        <v>105.93</v>
+        <v>65.84999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>26.23</v>
+        <v>2.03</v>
       </c>
       <c r="K15" t="n">
-        <v>-34.65</v>
+        <v>-2.68</v>
       </c>
       <c r="L15" t="n">
-        <v>43.46</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>36.82</v>
+        <v>22.99</v>
       </c>
       <c r="K16" t="n">
-        <v>125.63</v>
+        <v>78.45</v>
       </c>
       <c r="L16" t="n">
-        <v>130.91</v>
+        <v>81.75</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>167.37</v>
+        <v>114.23</v>
       </c>
       <c r="K17" t="n">
-        <v>-47.39</v>
+        <v>-32.34</v>
       </c>
       <c r="L17" t="n">
-        <v>173.95</v>
+        <v>118.72</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-67.59999999999999</v>
+        <v>-43.23</v>
       </c>
       <c r="K18" t="n">
-        <v>79.44</v>
+        <v>50.8</v>
       </c>
       <c r="L18" t="n">
-        <v>104.31</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-83.36</v>
+        <v>-55.66</v>
       </c>
       <c r="K19" t="n">
-        <v>19.37</v>
+        <v>12.93</v>
       </c>
       <c r="L19" t="n">
-        <v>85.56999999999999</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>102.6</v>
+        <v>64.95</v>
       </c>
       <c r="K20" t="n">
-        <v>91.59</v>
+        <v>57.99</v>
       </c>
       <c r="L20" t="n">
-        <v>137.53</v>
+        <v>87.06999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>164.94</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>49.21</v>
+        <v>26.93</v>
       </c>
       <c r="L21" t="n">
-        <v>172.12</v>
+        <v>94.17</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>220.61</v>
+        <v>139.67</v>
       </c>
       <c r="K22" t="n">
-        <v>-238.51</v>
+        <v>-151</v>
       </c>
       <c r="L22" t="n">
-        <v>324.89</v>
+        <v>205.69</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-139.88</v>
+        <v>-90.68000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-276.37</v>
+        <v>-179.16</v>
       </c>
       <c r="L23" t="n">
-        <v>309.75</v>
+        <v>200.8</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-129.44</v>
+        <v>-83.31</v>
       </c>
       <c r="K24" t="n">
-        <v>73.95</v>
+        <v>47.59</v>
       </c>
       <c r="L24" t="n">
-        <v>149.07</v>
+        <v>95.94</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-55.66</v>
+        <v>-35.82</v>
       </c>
       <c r="K25" t="n">
-        <v>-147.2</v>
+        <v>-94.73999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>157.37</v>
+        <v>101.28</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-86.83</v>
+        <v>-53.04</v>
       </c>
       <c r="K26" t="n">
-        <v>-170.79</v>
+        <v>-104.32</v>
       </c>
       <c r="L26" t="n">
-        <v>191.59</v>
+        <v>117.02</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>214.22</v>
+        <v>137.44</v>
       </c>
       <c r="K27" t="n">
-        <v>-271.48</v>
+        <v>-174.18</v>
       </c>
       <c r="L27" t="n">
-        <v>345.82</v>
+        <v>221.87</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>322.06</v>
+        <v>212.09</v>
       </c>
       <c r="K28" t="n">
-        <v>-46.96</v>
+        <v>-30.93</v>
       </c>
       <c r="L28" t="n">
-        <v>325.47</v>
+        <v>214.33</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>22.85</v>
+        <v>14.47</v>
       </c>
       <c r="K29" t="n">
-        <v>88.31999999999999</v>
+        <v>55.92</v>
       </c>
       <c r="L29" t="n">
-        <v>91.23</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-115.89</v>
+        <v>-72.37</v>
       </c>
       <c r="K30" t="n">
-        <v>1.18</v>
+        <v>0.74</v>
       </c>
       <c r="L30" t="n">
-        <v>115.9</v>
+        <v>72.37</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>82.65000000000001</v>
+        <v>44.83</v>
       </c>
       <c r="K31" t="n">
-        <v>-153.18</v>
+        <v>-83.09</v>
       </c>
       <c r="L31" t="n">
-        <v>174.06</v>
+        <v>94.41</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>69.26000000000001</v>
+        <v>40.54</v>
       </c>
       <c r="K32" t="n">
-        <v>183.72</v>
+        <v>107.53</v>
       </c>
       <c r="L32" t="n">
-        <v>196.35</v>
+        <v>114.92</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>76.62</v>
+        <v>46.37</v>
       </c>
       <c r="K33" t="n">
-        <v>-59.78</v>
+        <v>-36.18</v>
       </c>
       <c r="L33" t="n">
-        <v>97.18000000000001</v>
+        <v>58.81</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>61.05</v>
+        <v>32.66</v>
       </c>
       <c r="K34" t="n">
-        <v>89.73999999999999</v>
+        <v>48.01</v>
       </c>
       <c r="L34" t="n">
-        <v>108.54</v>
+        <v>58.07</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>70.04000000000001</v>
+        <v>39.72</v>
       </c>
       <c r="K35" t="n">
-        <v>239.94</v>
+        <v>136.06</v>
       </c>
       <c r="L35" t="n">
-        <v>249.95</v>
+        <v>141.74</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.19</v>
+        <v>-2.82</v>
       </c>
       <c r="K36" t="n">
-        <v>161.39</v>
+        <v>87.73</v>
       </c>
       <c r="L36" t="n">
-        <v>161.47</v>
+        <v>87.77</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>251.98</v>
+        <v>161.83</v>
       </c>
       <c r="K37" t="n">
-        <v>-113.84</v>
+        <v>-73.11</v>
       </c>
       <c r="L37" t="n">
-        <v>276.5</v>
+        <v>177.58</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-341.17</v>
+        <v>-223.22</v>
       </c>
       <c r="K38" t="n">
-        <v>-320.3</v>
+        <v>-209.56</v>
       </c>
       <c r="L38" t="n">
-        <v>467.96</v>
+        <v>306.17</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-130.11</v>
+        <v>-82.56999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>-75.06999999999999</v>
+        <v>-47.64</v>
       </c>
       <c r="L39" t="n">
-        <v>150.22</v>
+        <v>95.31999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>23.47</v>
+        <v>14.21</v>
       </c>
       <c r="K40" t="n">
-        <v>-229.22</v>
+        <v>-138.79</v>
       </c>
       <c r="L40" t="n">
-        <v>230.42</v>
+        <v>139.51</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>28.09</v>
+        <v>18.39</v>
       </c>
       <c r="K41" t="n">
-        <v>242.98</v>
+        <v>159.04</v>
       </c>
       <c r="L41" t="n">
-        <v>244.6</v>
+        <v>160.1</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-307.85</v>
+        <v>-194.09</v>
       </c>
       <c r="K42" t="n">
-        <v>220.08</v>
+        <v>138.76</v>
       </c>
       <c r="L42" t="n">
-        <v>378.43</v>
+        <v>238.59</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>113.46</v>
+        <v>70.86</v>
       </c>
       <c r="K43" t="n">
-        <v>-444.7</v>
+        <v>-277.72</v>
       </c>
       <c r="L43" t="n">
-        <v>458.95</v>
+        <v>286.62</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>-51.73</v>
+        <v>-28.1</v>
       </c>
       <c r="K44" t="n">
-        <v>10.57</v>
+        <v>5.74</v>
       </c>
       <c r="L44" t="n">
-        <v>52.8</v>
+        <v>28.68</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>64.20999999999999</v>
+        <v>37.54</v>
       </c>
       <c r="K45" t="n">
-        <v>-114.03</v>
+        <v>-66.67</v>
       </c>
       <c r="L45" t="n">
-        <v>130.87</v>
+        <v>76.51000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>16.17</v>
+        <v>9.76</v>
       </c>
       <c r="K46" t="n">
-        <v>111.3</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>112.46</v>
+        <v>67.89</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-99.44</v>
+        <v>-61.12</v>
       </c>
       <c r="K47" t="n">
-        <v>-106.33</v>
+        <v>-65.34999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>145.59</v>
+        <v>89.48</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>126.85</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-117.09</v>
+        <v>-70.86</v>
       </c>
       <c r="L48" t="n">
-        <v>172.63</v>
+        <v>104.47</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-127.94</v>
+        <v>-80.08</v>
       </c>
       <c r="K49" t="n">
-        <v>110.1</v>
+        <v>68.91</v>
       </c>
       <c r="L49" t="n">
-        <v>168.79</v>
+        <v>105.65</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>208.83</v>
+        <v>120.39</v>
       </c>
       <c r="K50" t="n">
-        <v>-168.04</v>
+        <v>-96.88</v>
       </c>
       <c r="L50" t="n">
-        <v>268.05</v>
+        <v>154.53</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-70.44</v>
+        <v>-39.76</v>
       </c>
       <c r="K51" t="n">
-        <v>-235.19</v>
+        <v>-132.76</v>
       </c>
       <c r="L51" t="n">
-        <v>245.52</v>
+        <v>138.58</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>39.09</v>
+        <v>22.75</v>
       </c>
       <c r="K52" t="n">
-        <v>-155.93</v>
+        <v>-90.77</v>
       </c>
       <c r="L52" t="n">
-        <v>160.76</v>
+        <v>93.56999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>254.08</v>
+        <v>156.25</v>
       </c>
       <c r="K53" t="n">
-        <v>-215.12</v>
+        <v>-132.29</v>
       </c>
       <c r="L53" t="n">
-        <v>332.92</v>
+        <v>204.73</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>9.369999999999999</v>
+        <v>4.76</v>
       </c>
       <c r="K54" t="n">
-        <v>-124.87</v>
+        <v>-63.42</v>
       </c>
       <c r="L54" t="n">
-        <v>125.22</v>
+        <v>63.59</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>285.71</v>
+        <v>183.55</v>
       </c>
       <c r="K55" t="n">
-        <v>90.53</v>
+        <v>58.16</v>
       </c>
       <c r="L55" t="n">
-        <v>299.7</v>
+        <v>192.54</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-195.6</v>
+        <v>-116.09</v>
       </c>
       <c r="K56" t="n">
-        <v>179.52</v>
+        <v>106.55</v>
       </c>
       <c r="L56" t="n">
-        <v>265.49</v>
+        <v>157.58</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>357.97</v>
+        <v>216.26</v>
       </c>
       <c r="K57" t="n">
-        <v>-279.38</v>
+        <v>-168.78</v>
       </c>
       <c r="L57" t="n">
-        <v>454.09</v>
+        <v>274.33</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>280.07</v>
+        <v>159.86</v>
       </c>
       <c r="K58" t="n">
-        <v>-443.24</v>
+        <v>-253</v>
       </c>
       <c r="L58" t="n">
-        <v>524.3099999999999</v>
+        <v>299.27</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>109.41</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-14.91</v>
+        <v>-9.31</v>
       </c>
       <c r="L59" t="n">
-        <v>110.42</v>
+        <v>68.95</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>187.66</v>
+        <v>107.66</v>
       </c>
       <c r="K60" t="n">
-        <v>184.78</v>
+        <v>106.01</v>
       </c>
       <c r="L60" t="n">
-        <v>263.36</v>
+        <v>151.1</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-176.96</v>
+        <v>-101.69</v>
       </c>
       <c r="K61" t="n">
-        <v>11.41</v>
+        <v>6.56</v>
       </c>
       <c r="L61" t="n">
-        <v>177.33</v>
+        <v>101.91</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-95.47</v>
+        <v>-62.76</v>
       </c>
       <c r="K62" t="n">
-        <v>18.25</v>
+        <v>12</v>
       </c>
       <c r="L62" t="n">
-        <v>97.2</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-92.43000000000001</v>
+        <v>-56.81</v>
       </c>
       <c r="K63" t="n">
-        <v>28.15</v>
+        <v>17.3</v>
       </c>
       <c r="L63" t="n">
-        <v>96.62</v>
+        <v>59.38</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-97.78</v>
+        <v>-57.81</v>
       </c>
       <c r="K64" t="n">
-        <v>27.17</v>
+        <v>16.07</v>
       </c>
       <c r="L64" t="n">
-        <v>101.48</v>
+        <v>60.01</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-146.74</v>
+        <v>-84.2</v>
       </c>
       <c r="K65" t="n">
-        <v>246.52</v>
+        <v>141.44</v>
       </c>
       <c r="L65" t="n">
-        <v>286.89</v>
+        <v>164.6</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-93.42</v>
+        <v>-50.89</v>
       </c>
       <c r="K66" t="n">
-        <v>212.21</v>
+        <v>115.6</v>
       </c>
       <c r="L66" t="n">
-        <v>231.86</v>
+        <v>126.31</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>181.97</v>
+        <v>98.91</v>
       </c>
       <c r="K67" t="n">
-        <v>-6.61</v>
+        <v>-3.59</v>
       </c>
       <c r="L67" t="n">
-        <v>182.09</v>
+        <v>98.98</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-165.88</v>
+        <v>-102.33</v>
       </c>
       <c r="K68" t="n">
-        <v>-61.46</v>
+        <v>-37.91</v>
       </c>
       <c r="L68" t="n">
-        <v>176.9</v>
+        <v>109.13</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-112.19</v>
+        <v>-68.66</v>
       </c>
       <c r="K69" t="n">
-        <v>-181.58</v>
+        <v>-111.14</v>
       </c>
       <c r="L69" t="n">
-        <v>213.44</v>
+        <v>130.64</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-240.77</v>
+        <v>-136.73</v>
       </c>
       <c r="K70" t="n">
-        <v>-24.74</v>
+        <v>-14.05</v>
       </c>
       <c r="L70" t="n">
-        <v>242.04</v>
+        <v>137.45</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>302.11</v>
+        <v>199.36</v>
       </c>
       <c r="K71" t="n">
-        <v>-121.15</v>
+        <v>-79.95</v>
       </c>
       <c r="L71" t="n">
-        <v>325.49</v>
+        <v>214.79</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-34.03</v>
+        <v>-20.98</v>
       </c>
       <c r="K72" t="n">
-        <v>201.45</v>
+        <v>124.17</v>
       </c>
       <c r="L72" t="n">
-        <v>204.3</v>
+        <v>125.93</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>318.49</v>
+        <v>179.85</v>
       </c>
       <c r="K73" t="n">
-        <v>-249.98</v>
+        <v>-141.16</v>
       </c>
       <c r="L73" t="n">
-        <v>404.88</v>
+        <v>228.63</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-104.08</v>
+        <v>-59.52</v>
       </c>
       <c r="K74" t="n">
-        <v>10.86</v>
+        <v>6.21</v>
       </c>
       <c r="L74" t="n">
-        <v>104.64</v>
+        <v>59.84</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-185.61</v>
+        <v>-107.94</v>
       </c>
       <c r="K75" t="n">
-        <v>4.8</v>
+        <v>2.79</v>
       </c>
       <c r="L75" t="n">
-        <v>185.67</v>
+        <v>107.98</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>118.86</v>
+        <v>68.77</v>
       </c>
       <c r="K76" t="n">
-        <v>26.26</v>
+        <v>15.2</v>
       </c>
       <c r="L76" t="n">
-        <v>121.73</v>
+        <v>70.43000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>100.5</v>
+        <v>52.68</v>
       </c>
       <c r="K77" t="n">
-        <v>-28.76</v>
+        <v>-15.07</v>
       </c>
       <c r="L77" t="n">
-        <v>104.53</v>
+        <v>54.79</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-64.48</v>
+        <v>-32.86</v>
       </c>
       <c r="K78" t="n">
-        <v>214.55</v>
+        <v>109.35</v>
       </c>
       <c r="L78" t="n">
-        <v>224.03</v>
+        <v>114.18</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-33.53</v>
+        <v>-20.16</v>
       </c>
       <c r="K79" t="n">
-        <v>-132.06</v>
+        <v>-79.41</v>
       </c>
       <c r="L79" t="n">
-        <v>136.25</v>
+        <v>81.93000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>183.55</v>
+        <v>105.06</v>
       </c>
       <c r="K80" t="n">
-        <v>7.04</v>
+        <v>4.03</v>
       </c>
       <c r="L80" t="n">
-        <v>183.68</v>
+        <v>105.14</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>98.02</v>
+        <v>50.74</v>
       </c>
       <c r="K81" t="n">
-        <v>293.58</v>
+        <v>151.96</v>
       </c>
       <c r="L81" t="n">
-        <v>309.51</v>
+        <v>160.21</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-273.77</v>
+        <v>-151.43</v>
       </c>
       <c r="K82" t="n">
-        <v>28.39</v>
+        <v>15.7</v>
       </c>
       <c r="L82" t="n">
-        <v>275.24</v>
+        <v>152.24</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>226.91</v>
+        <v>130.67</v>
       </c>
       <c r="K83" t="n">
-        <v>196.09</v>
+        <v>112.92</v>
       </c>
       <c r="L83" t="n">
-        <v>299.9</v>
+        <v>172.7</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>198.28</v>
+        <v>125.61</v>
       </c>
       <c r="K84" t="n">
-        <v>214.84</v>
+        <v>136.1</v>
       </c>
       <c r="L84" t="n">
-        <v>292.35</v>
+        <v>185.2</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>192.24</v>
+        <v>123.95</v>
       </c>
       <c r="K85" t="n">
-        <v>-87.53</v>
+        <v>-56.43</v>
       </c>
       <c r="L85" t="n">
-        <v>211.23</v>
+        <v>136.19</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>590.28</v>
+        <v>340.3</v>
       </c>
       <c r="K86" t="n">
-        <v>-276.35</v>
+        <v>-159.32</v>
       </c>
       <c r="L86" t="n">
-        <v>651.76</v>
+        <v>375.75</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-161.16</v>
+        <v>-94.83</v>
       </c>
       <c r="K87" t="n">
-        <v>470.42</v>
+        <v>276.79</v>
       </c>
       <c r="L87" t="n">
-        <v>497.26</v>
+        <v>292.58</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-246.04</v>
+        <v>-144.52</v>
       </c>
       <c r="K88" t="n">
-        <v>-303</v>
+        <v>-177.98</v>
       </c>
       <c r="L88" t="n">
-        <v>390.32</v>
+        <v>229.26</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-03.xlsx
+++ b/output/2024-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-59.56</v>
+        <v>-59.27</v>
       </c>
       <c r="K14" t="n">
-        <v>28.09</v>
+        <v>27.96</v>
       </c>
       <c r="L14" t="n">
-        <v>65.84999999999999</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.68</v>
+        <v>-2.65</v>
       </c>
       <c r="L15" t="n">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>22.99</v>
+        <v>22.42</v>
       </c>
       <c r="K16" t="n">
-        <v>78.45</v>
+        <v>76.5</v>
       </c>
       <c r="L16" t="n">
-        <v>81.75</v>
+        <v>79.72</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>114.23</v>
+        <v>109.45</v>
       </c>
       <c r="K17" t="n">
-        <v>-32.34</v>
+        <v>-30.99</v>
       </c>
       <c r="L17" t="n">
-        <v>118.72</v>
+        <v>113.75</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-43.23</v>
+        <v>-44.54</v>
       </c>
       <c r="K18" t="n">
-        <v>50.8</v>
+        <v>52.33</v>
       </c>
       <c r="L18" t="n">
-        <v>66.7</v>
+        <v>68.72</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-55.66</v>
+        <v>-58.88</v>
       </c>
       <c r="K19" t="n">
-        <v>12.93</v>
+        <v>13.68</v>
       </c>
       <c r="L19" t="n">
-        <v>57.14</v>
+        <v>60.45</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>64.95</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>57.99</v>
+        <v>60.87</v>
       </c>
       <c r="L20" t="n">
-        <v>87.06999999999999</v>
+        <v>91.39</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>90.23999999999999</v>
+        <v>93.25</v>
       </c>
       <c r="K21" t="n">
-        <v>26.93</v>
+        <v>27.82</v>
       </c>
       <c r="L21" t="n">
-        <v>94.17</v>
+        <v>97.31</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>139.67</v>
+        <v>132.81</v>
       </c>
       <c r="K22" t="n">
-        <v>-151</v>
+        <v>-143.59</v>
       </c>
       <c r="L22" t="n">
-        <v>205.69</v>
+        <v>195.6</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-90.68000000000001</v>
+        <v>-88.95999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-179.16</v>
+        <v>-175.77</v>
       </c>
       <c r="L23" t="n">
-        <v>200.8</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-83.31</v>
+        <v>-90.48</v>
       </c>
       <c r="K24" t="n">
-        <v>47.59</v>
+        <v>51.69</v>
       </c>
       <c r="L24" t="n">
-        <v>95.94</v>
+        <v>104.21</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-35.82</v>
+        <v>-38.34</v>
       </c>
       <c r="K25" t="n">
-        <v>-94.73999999999999</v>
+        <v>-101.38</v>
       </c>
       <c r="L25" t="n">
-        <v>101.28</v>
+        <v>108.39</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-53.04</v>
+        <v>-51.74</v>
       </c>
       <c r="K26" t="n">
-        <v>-104.32</v>
+        <v>-101.77</v>
       </c>
       <c r="L26" t="n">
-        <v>117.02</v>
+        <v>114.17</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>137.44</v>
+        <v>138.98</v>
       </c>
       <c r="K27" t="n">
-        <v>-174.18</v>
+        <v>-176.13</v>
       </c>
       <c r="L27" t="n">
-        <v>221.87</v>
+        <v>224.36</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>212.09</v>
+        <v>205.62</v>
       </c>
       <c r="K28" t="n">
-        <v>-30.93</v>
+        <v>-29.98</v>
       </c>
       <c r="L28" t="n">
-        <v>214.33</v>
+        <v>207.79</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>14.47</v>
+        <v>14.62</v>
       </c>
       <c r="K29" t="n">
-        <v>55.92</v>
+        <v>56.49</v>
       </c>
       <c r="L29" t="n">
-        <v>57.76</v>
+        <v>58.35</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-72.37</v>
+        <v>-71.58</v>
       </c>
       <c r="K30" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="L30" t="n">
-        <v>72.37</v>
+        <v>71.59</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>44.83</v>
+        <v>44.02</v>
       </c>
       <c r="K31" t="n">
-        <v>-83.09</v>
+        <v>-81.59</v>
       </c>
       <c r="L31" t="n">
-        <v>94.41</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>40.54</v>
+        <v>39.36</v>
       </c>
       <c r="K32" t="n">
-        <v>107.53</v>
+        <v>104.41</v>
       </c>
       <c r="L32" t="n">
-        <v>114.92</v>
+        <v>111.58</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>46.37</v>
+        <v>49.4</v>
       </c>
       <c r="K33" t="n">
-        <v>-36.18</v>
+        <v>-38.55</v>
       </c>
       <c r="L33" t="n">
-        <v>58.81</v>
+        <v>62.66</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>32.66</v>
+        <v>35.13</v>
       </c>
       <c r="K34" t="n">
-        <v>48.01</v>
+        <v>51.64</v>
       </c>
       <c r="L34" t="n">
-        <v>58.07</v>
+        <v>62.46</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>39.72</v>
+        <v>32.98</v>
       </c>
       <c r="K35" t="n">
-        <v>136.06</v>
+        <v>112.99</v>
       </c>
       <c r="L35" t="n">
-        <v>141.74</v>
+        <v>117.71</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.82</v>
+        <v>-2.99</v>
       </c>
       <c r="K36" t="n">
-        <v>87.73</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>87.77</v>
+        <v>93.12</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>161.83</v>
+        <v>154.78</v>
       </c>
       <c r="K37" t="n">
-        <v>-73.11</v>
+        <v>-69.93000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>177.58</v>
+        <v>169.85</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-223.22</v>
+        <v>-211</v>
       </c>
       <c r="K38" t="n">
-        <v>-209.56</v>
+        <v>-198.09</v>
       </c>
       <c r="L38" t="n">
-        <v>306.17</v>
+        <v>289.42</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-82.56999999999999</v>
+        <v>-89.7</v>
       </c>
       <c r="K39" t="n">
-        <v>-47.64</v>
+        <v>-51.75</v>
       </c>
       <c r="L39" t="n">
-        <v>95.31999999999999</v>
+        <v>103.56</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>14.21</v>
+        <v>14.55</v>
       </c>
       <c r="K40" t="n">
-        <v>-138.79</v>
+        <v>-142.09</v>
       </c>
       <c r="L40" t="n">
-        <v>139.51</v>
+        <v>142.84</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>18.39</v>
+        <v>19.24</v>
       </c>
       <c r="K41" t="n">
-        <v>159.04</v>
+        <v>166.41</v>
       </c>
       <c r="L41" t="n">
-        <v>160.1</v>
+        <v>167.52</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-194.09</v>
+        <v>-194.1</v>
       </c>
       <c r="K42" t="n">
         <v>138.76</v>
       </c>
       <c r="L42" t="n">
-        <v>238.59</v>
+        <v>238.6</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>70.86</v>
+        <v>68.83</v>
       </c>
       <c r="K43" t="n">
-        <v>-277.72</v>
+        <v>-269.77</v>
       </c>
       <c r="L43" t="n">
-        <v>286.62</v>
+        <v>278.41</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>-28.1</v>
+        <v>-27.43</v>
       </c>
       <c r="K44" t="n">
-        <v>5.74</v>
+        <v>5.6</v>
       </c>
       <c r="L44" t="n">
-        <v>28.68</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>37.54</v>
+        <v>37.45</v>
       </c>
       <c r="K45" t="n">
-        <v>-66.67</v>
+        <v>-66.51000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>76.51000000000001</v>
+        <v>76.31999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1987,10 +1987,10 @@
         <v>9.76</v>
       </c>
       <c r="K46" t="n">
-        <v>67.18000000000001</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>67.89</v>
+        <v>67.92</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-61.12</v>
+        <v>-60.78</v>
       </c>
       <c r="K47" t="n">
-        <v>-65.34999999999999</v>
+        <v>-64.98999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>89.48</v>
+        <v>88.98999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>76.76000000000001</v>
+        <v>75.14</v>
       </c>
       <c r="K48" t="n">
-        <v>-70.86</v>
+        <v>-69.36</v>
       </c>
       <c r="L48" t="n">
-        <v>104.47</v>
+        <v>102.26</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-80.08</v>
+        <v>-78.19</v>
       </c>
       <c r="K49" t="n">
-        <v>68.91</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>105.65</v>
+        <v>103.16</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>120.39</v>
+        <v>117.69</v>
       </c>
       <c r="K50" t="n">
-        <v>-96.88</v>
+        <v>-94.7</v>
       </c>
       <c r="L50" t="n">
-        <v>154.53</v>
+        <v>151.06</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-39.76</v>
+        <v>-39.03</v>
       </c>
       <c r="K51" t="n">
-        <v>-132.76</v>
+        <v>-130.33</v>
       </c>
       <c r="L51" t="n">
-        <v>138.58</v>
+        <v>136.05</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>22.75</v>
+        <v>23.45</v>
       </c>
       <c r="K52" t="n">
-        <v>-90.77</v>
+        <v>-93.53</v>
       </c>
       <c r="L52" t="n">
-        <v>93.56999999999999</v>
+        <v>96.43000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>156.25</v>
+        <v>152.02</v>
       </c>
       <c r="K53" t="n">
-        <v>-132.29</v>
+        <v>-128.72</v>
       </c>
       <c r="L53" t="n">
-        <v>204.73</v>
+        <v>199.19</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>4.76</v>
+        <v>4.65</v>
       </c>
       <c r="K54" t="n">
-        <v>-63.42</v>
+        <v>-61.95</v>
       </c>
       <c r="L54" t="n">
-        <v>63.59</v>
+        <v>62.12</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>183.55</v>
+        <v>179.5</v>
       </c>
       <c r="K55" t="n">
-        <v>58.16</v>
+        <v>56.87</v>
       </c>
       <c r="L55" t="n">
-        <v>192.54</v>
+        <v>188.29</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-116.09</v>
+        <v>-123.1</v>
       </c>
       <c r="K56" t="n">
-        <v>106.55</v>
+        <v>112.97</v>
       </c>
       <c r="L56" t="n">
-        <v>157.58</v>
+        <v>167.08</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>216.26</v>
+        <v>211.18</v>
       </c>
       <c r="K57" t="n">
-        <v>-168.78</v>
+        <v>-164.82</v>
       </c>
       <c r="L57" t="n">
-        <v>274.33</v>
+        <v>267.89</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>159.86</v>
+        <v>156.48</v>
       </c>
       <c r="K58" t="n">
-        <v>-253</v>
+        <v>-247.65</v>
       </c>
       <c r="L58" t="n">
-        <v>299.27</v>
+        <v>292.94</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>68.31999999999999</v>
+        <v>67.98</v>
       </c>
       <c r="K59" t="n">
-        <v>-9.31</v>
+        <v>-9.26</v>
       </c>
       <c r="L59" t="n">
-        <v>68.95</v>
+        <v>68.61</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>107.66</v>
+        <v>95.64</v>
       </c>
       <c r="K60" t="n">
-        <v>106.01</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>151.1</v>
+        <v>134.23</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-101.69</v>
+        <v>-97.75</v>
       </c>
       <c r="K61" t="n">
-        <v>6.56</v>
+        <v>6.3</v>
       </c>
       <c r="L61" t="n">
-        <v>101.91</v>
+        <v>97.95999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-62.76</v>
+        <v>-64.55</v>
       </c>
       <c r="K62" t="n">
-        <v>12</v>
+        <v>12.34</v>
       </c>
       <c r="L62" t="n">
-        <v>63.9</v>
+        <v>65.70999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-56.81</v>
+        <v>-59.39</v>
       </c>
       <c r="K63" t="n">
-        <v>17.3</v>
+        <v>18.08</v>
       </c>
       <c r="L63" t="n">
-        <v>59.38</v>
+        <v>62.08</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-57.81</v>
+        <v>-61.36</v>
       </c>
       <c r="K64" t="n">
-        <v>16.07</v>
+        <v>17.05</v>
       </c>
       <c r="L64" t="n">
-        <v>60.01</v>
+        <v>63.69</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-84.2</v>
+        <v>-81.72</v>
       </c>
       <c r="K65" t="n">
-        <v>141.44</v>
+        <v>137.29</v>
       </c>
       <c r="L65" t="n">
-        <v>164.6</v>
+        <v>159.77</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-50.89</v>
+        <v>-50.94</v>
       </c>
       <c r="K66" t="n">
-        <v>115.6</v>
+        <v>115.71</v>
       </c>
       <c r="L66" t="n">
-        <v>126.31</v>
+        <v>126.43</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>98.91</v>
+        <v>102.55</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.59</v>
+        <v>-3.73</v>
       </c>
       <c r="L67" t="n">
-        <v>98.98</v>
+        <v>102.62</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-102.33</v>
+        <v>-108.29</v>
       </c>
       <c r="K68" t="n">
-        <v>-37.91</v>
+        <v>-40.12</v>
       </c>
       <c r="L68" t="n">
-        <v>109.13</v>
+        <v>115.48</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-68.66</v>
+        <v>-70.98</v>
       </c>
       <c r="K69" t="n">
-        <v>-111.14</v>
+        <v>-114.88</v>
       </c>
       <c r="L69" t="n">
-        <v>130.64</v>
+        <v>135.04</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-136.73</v>
+        <v>-140.64</v>
       </c>
       <c r="K70" t="n">
-        <v>-14.05</v>
+        <v>-14.45</v>
       </c>
       <c r="L70" t="n">
-        <v>137.45</v>
+        <v>141.38</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>199.36</v>
+        <v>198.95</v>
       </c>
       <c r="K71" t="n">
-        <v>-79.95</v>
+        <v>-79.79000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>214.79</v>
+        <v>214.36</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-20.98</v>
+        <v>-23.03</v>
       </c>
       <c r="K72" t="n">
-        <v>124.17</v>
+        <v>136.33</v>
       </c>
       <c r="L72" t="n">
-        <v>125.93</v>
+        <v>138.26</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>179.85</v>
+        <v>182.06</v>
       </c>
       <c r="K73" t="n">
-        <v>-141.16</v>
+        <v>-142.9</v>
       </c>
       <c r="L73" t="n">
-        <v>228.63</v>
+        <v>231.45</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-59.52</v>
+        <v>-61.41</v>
       </c>
       <c r="K74" t="n">
-        <v>6.21</v>
+        <v>6.41</v>
       </c>
       <c r="L74" t="n">
-        <v>59.84</v>
+        <v>61.74</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-107.94</v>
+        <v>-103.37</v>
       </c>
       <c r="K75" t="n">
-        <v>2.79</v>
+        <v>2.68</v>
       </c>
       <c r="L75" t="n">
-        <v>107.98</v>
+        <v>103.4</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>68.77</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>15.2</v>
+        <v>15.26</v>
       </c>
       <c r="L76" t="n">
-        <v>70.43000000000001</v>
+        <v>70.73</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>52.68</v>
+        <v>56.84</v>
       </c>
       <c r="K77" t="n">
-        <v>-15.07</v>
+        <v>-16.27</v>
       </c>
       <c r="L77" t="n">
-        <v>54.79</v>
+        <v>59.13</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-32.86</v>
+        <v>-31.87</v>
       </c>
       <c r="K78" t="n">
-        <v>109.35</v>
+        <v>106.04</v>
       </c>
       <c r="L78" t="n">
-        <v>114.18</v>
+        <v>110.72</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-20.16</v>
+        <v>-20.09</v>
       </c>
       <c r="K79" t="n">
-        <v>-79.41</v>
+        <v>-79.14</v>
       </c>
       <c r="L79" t="n">
-        <v>81.93000000000001</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>105.06</v>
+        <v>107.77</v>
       </c>
       <c r="K80" t="n">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="L80" t="n">
-        <v>105.14</v>
+        <v>107.85</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>50.74</v>
+        <v>49.57</v>
       </c>
       <c r="K81" t="n">
-        <v>151.96</v>
+        <v>148.46</v>
       </c>
       <c r="L81" t="n">
-        <v>160.21</v>
+        <v>156.52</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-151.43</v>
+        <v>-147.5</v>
       </c>
       <c r="K82" t="n">
-        <v>15.7</v>
+        <v>15.29</v>
       </c>
       <c r="L82" t="n">
-        <v>152.24</v>
+        <v>148.29</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>130.67</v>
+        <v>131.47</v>
       </c>
       <c r="K83" t="n">
-        <v>112.92</v>
+        <v>113.62</v>
       </c>
       <c r="L83" t="n">
-        <v>172.7</v>
+        <v>173.76</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>125.61</v>
+        <v>123.32</v>
       </c>
       <c r="K84" t="n">
-        <v>136.1</v>
+        <v>133.63</v>
       </c>
       <c r="L84" t="n">
-        <v>185.2</v>
+        <v>181.84</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>123.95</v>
+        <v>126.28</v>
       </c>
       <c r="K85" t="n">
-        <v>-56.43</v>
+        <v>-57.49</v>
       </c>
       <c r="L85" t="n">
-        <v>136.19</v>
+        <v>138.75</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>340.3</v>
+        <v>325.42</v>
       </c>
       <c r="K86" t="n">
-        <v>-159.32</v>
+        <v>-152.35</v>
       </c>
       <c r="L86" t="n">
-        <v>375.75</v>
+        <v>359.32</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-94.83</v>
+        <v>-92.92</v>
       </c>
       <c r="K87" t="n">
-        <v>276.79</v>
+        <v>271.24</v>
       </c>
       <c r="L87" t="n">
-        <v>292.58</v>
+        <v>286.72</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-144.52</v>
+        <v>-144.38</v>
       </c>
       <c r="K88" t="n">
-        <v>-177.98</v>
+        <v>-177.8</v>
       </c>
       <c r="L88" t="n">
-        <v>229.26</v>
+        <v>229.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-03.xlsx
+++ b/output/2024-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-59.27</v>
+        <v>-58.94</v>
       </c>
       <c r="K14" t="n">
-        <v>27.96</v>
+        <v>27.8</v>
       </c>
       <c r="L14" t="n">
-        <v>65.53</v>
+        <v>65.17</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.65</v>
+        <v>-2.77</v>
       </c>
       <c r="L15" t="n">
-        <v>3.32</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>22.42</v>
+        <v>21.77</v>
       </c>
       <c r="K16" t="n">
-        <v>76.5</v>
+        <v>74.27</v>
       </c>
       <c r="L16" t="n">
-        <v>79.72</v>
+        <v>77.39</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>109.45</v>
+        <v>103.98</v>
       </c>
       <c r="K17" t="n">
-        <v>-30.99</v>
+        <v>-29.44</v>
       </c>
       <c r="L17" t="n">
-        <v>113.75</v>
+        <v>108.07</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-44.54</v>
+        <v>-46.03</v>
       </c>
       <c r="K18" t="n">
-        <v>52.33</v>
+        <v>54.09</v>
       </c>
       <c r="L18" t="n">
-        <v>68.72</v>
+        <v>71.02</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-58.88</v>
+        <v>-62.55</v>
       </c>
       <c r="K19" t="n">
-        <v>13.68</v>
+        <v>14.53</v>
       </c>
       <c r="L19" t="n">
-        <v>60.45</v>
+        <v>64.22</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>68.18000000000001</v>
+        <v>71.86</v>
       </c>
       <c r="K20" t="n">
-        <v>60.87</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>91.39</v>
+        <v>96.33</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>93.25</v>
+        <v>96.69</v>
       </c>
       <c r="K21" t="n">
-        <v>27.82</v>
+        <v>28.85</v>
       </c>
       <c r="L21" t="n">
-        <v>97.31</v>
+        <v>100.9</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>132.81</v>
+        <v>124.98</v>
       </c>
       <c r="K22" t="n">
-        <v>-143.59</v>
+        <v>-135.12</v>
       </c>
       <c r="L22" t="n">
-        <v>195.6</v>
+        <v>184.06</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-88.95999999999999</v>
+        <v>-87</v>
       </c>
       <c r="K23" t="n">
-        <v>-175.77</v>
+        <v>-171.89</v>
       </c>
       <c r="L23" t="n">
-        <v>197</v>
+        <v>192.65</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-90.48</v>
+        <v>-98.69</v>
       </c>
       <c r="K24" t="n">
-        <v>51.69</v>
+        <v>56.38</v>
       </c>
       <c r="L24" t="n">
-        <v>104.21</v>
+        <v>113.66</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-38.34</v>
+        <v>-41.21</v>
       </c>
       <c r="K25" t="n">
-        <v>-101.38</v>
+        <v>-108.98</v>
       </c>
       <c r="L25" t="n">
-        <v>108.39</v>
+        <v>116.51</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-51.74</v>
+        <v>-56.84</v>
       </c>
       <c r="K26" t="n">
-        <v>-101.77</v>
+        <v>-111.81</v>
       </c>
       <c r="L26" t="n">
-        <v>114.17</v>
+        <v>125.43</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>138.98</v>
+        <v>140.75</v>
       </c>
       <c r="K27" t="n">
-        <v>-176.13</v>
+        <v>-178.36</v>
       </c>
       <c r="L27" t="n">
-        <v>224.36</v>
+        <v>227.21</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>205.62</v>
+        <v>214.38</v>
       </c>
       <c r="K28" t="n">
-        <v>-29.98</v>
+        <v>-31.26</v>
       </c>
       <c r="L28" t="n">
-        <v>207.79</v>
+        <v>216.65</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>14.62</v>
+        <v>14.79</v>
       </c>
       <c r="K29" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="L29" t="n">
-        <v>58.35</v>
+        <v>59.02</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-71.58</v>
+        <v>-70.69</v>
       </c>
       <c r="K30" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="L30" t="n">
-        <v>71.59</v>
+        <v>70.69</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>44.02</v>
+        <v>43.13</v>
       </c>
       <c r="K31" t="n">
-        <v>-81.59</v>
+        <v>-79.93000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>92.70999999999999</v>
+        <v>90.83</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>39.36</v>
+        <v>38.02</v>
       </c>
       <c r="K32" t="n">
-        <v>104.41</v>
+        <v>100.84</v>
       </c>
       <c r="L32" t="n">
-        <v>111.58</v>
+        <v>107.77</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>49.4</v>
+        <v>52.87</v>
       </c>
       <c r="K33" t="n">
-        <v>-38.55</v>
+        <v>-41.26</v>
       </c>
       <c r="L33" t="n">
-        <v>62.66</v>
+        <v>67.06</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>35.13</v>
+        <v>38</v>
       </c>
       <c r="K34" t="n">
-        <v>51.64</v>
+        <v>55.85</v>
       </c>
       <c r="L34" t="n">
-        <v>62.46</v>
+        <v>67.55</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>32.98</v>
+        <v>32.85</v>
       </c>
       <c r="K35" t="n">
-        <v>112.99</v>
+        <v>112.55</v>
       </c>
       <c r="L35" t="n">
-        <v>117.71</v>
+        <v>117.24</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.99</v>
+        <v>-3.19</v>
       </c>
       <c r="K36" t="n">
-        <v>93.06999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>93.12</v>
+        <v>99.23</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>154.78</v>
+        <v>146.73</v>
       </c>
       <c r="K37" t="n">
-        <v>-69.93000000000001</v>
+        <v>-66.29000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>169.85</v>
+        <v>161.01</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-211</v>
+        <v>-197.04</v>
       </c>
       <c r="K38" t="n">
-        <v>-198.09</v>
+        <v>-184.99</v>
       </c>
       <c r="L38" t="n">
-        <v>289.42</v>
+        <v>270.27</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-89.7</v>
+        <v>-97.84999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>-51.75</v>
+        <v>-56.46</v>
       </c>
       <c r="L39" t="n">
-        <v>103.56</v>
+        <v>112.97</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>14.55</v>
+        <v>14.93</v>
       </c>
       <c r="K40" t="n">
-        <v>-142.09</v>
+        <v>-145.87</v>
       </c>
       <c r="L40" t="n">
-        <v>142.84</v>
+        <v>146.63</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>19.24</v>
+        <v>20.21</v>
       </c>
       <c r="K41" t="n">
-        <v>166.41</v>
+        <v>174.84</v>
       </c>
       <c r="L41" t="n">
-        <v>167.52</v>
+        <v>176.01</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-194.1</v>
+        <v>-194.12</v>
       </c>
       <c r="K42" t="n">
-        <v>138.76</v>
+        <v>138.77</v>
       </c>
       <c r="L42" t="n">
-        <v>238.6</v>
+        <v>238.62</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>68.83</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>-269.77</v>
+        <v>-260.69</v>
       </c>
       <c r="L43" t="n">
-        <v>278.41</v>
+        <v>269.04</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>-27.43</v>
+        <v>-30.06</v>
       </c>
       <c r="K44" t="n">
-        <v>5.6</v>
+        <v>6.14</v>
       </c>
       <c r="L44" t="n">
-        <v>28</v>
+        <v>30.68</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>37.45</v>
+        <v>37.35</v>
       </c>
       <c r="K45" t="n">
-        <v>-66.51000000000001</v>
+        <v>-66.31999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>76.31999999999999</v>
+        <v>76.11</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>9.76</v>
+        <v>9.77</v>
       </c>
       <c r="K46" t="n">
-        <v>67.20999999999999</v>
+        <v>67.25</v>
       </c>
       <c r="L46" t="n">
-        <v>67.92</v>
+        <v>67.95999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-60.78</v>
+        <v>-60.4</v>
       </c>
       <c r="K47" t="n">
-        <v>-64.98999999999999</v>
+        <v>-64.59</v>
       </c>
       <c r="L47" t="n">
-        <v>88.98999999999999</v>
+        <v>88.43000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>75.14</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-69.36</v>
+        <v>-67.65000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>102.26</v>
+        <v>99.73999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-78.19</v>
+        <v>-76.03</v>
       </c>
       <c r="K49" t="n">
-        <v>67.29000000000001</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>103.16</v>
+        <v>100.31</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>117.69</v>
+        <v>114.6</v>
       </c>
       <c r="K50" t="n">
-        <v>-94.7</v>
+        <v>-92.22</v>
       </c>
       <c r="L50" t="n">
-        <v>151.06</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-39.03</v>
+        <v>-38.2</v>
       </c>
       <c r="K51" t="n">
-        <v>-130.33</v>
+        <v>-127.55</v>
       </c>
       <c r="L51" t="n">
-        <v>136.05</v>
+        <v>133.15</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>23.45</v>
+        <v>24.24</v>
       </c>
       <c r="K52" t="n">
-        <v>-93.53</v>
+        <v>-96.7</v>
       </c>
       <c r="L52" t="n">
-        <v>96.43000000000001</v>
+        <v>99.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>152.02</v>
+        <v>147.2</v>
       </c>
       <c r="K53" t="n">
-        <v>-128.72</v>
+        <v>-124.63</v>
       </c>
       <c r="L53" t="n">
-        <v>199.19</v>
+        <v>192.87</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>4.65</v>
+        <v>5.08</v>
       </c>
       <c r="K54" t="n">
-        <v>-61.95</v>
+        <v>-67.73</v>
       </c>
       <c r="L54" t="n">
-        <v>62.12</v>
+        <v>67.92</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>179.5</v>
+        <v>174.88</v>
       </c>
       <c r="K55" t="n">
-        <v>56.87</v>
+        <v>55.41</v>
       </c>
       <c r="L55" t="n">
-        <v>188.29</v>
+        <v>183.44</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-123.1</v>
+        <v>-131.1</v>
       </c>
       <c r="K56" t="n">
-        <v>112.97</v>
+        <v>120.31</v>
       </c>
       <c r="L56" t="n">
-        <v>167.08</v>
+        <v>177.94</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>211.18</v>
+        <v>205.38</v>
       </c>
       <c r="K57" t="n">
-        <v>-164.82</v>
+        <v>-160.29</v>
       </c>
       <c r="L57" t="n">
-        <v>267.89</v>
+        <v>260.53</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>156.48</v>
+        <v>152.62</v>
       </c>
       <c r="K58" t="n">
-        <v>-247.65</v>
+        <v>-241.53</v>
       </c>
       <c r="L58" t="n">
-        <v>292.94</v>
+        <v>285.71</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>67.98</v>
+        <v>67.59</v>
       </c>
       <c r="K59" t="n">
-        <v>-9.26</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>68.61</v>
+        <v>68.22</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>95.64</v>
+        <v>90.11</v>
       </c>
       <c r="K60" t="n">
-        <v>94.18000000000001</v>
+        <v>88.72</v>
       </c>
       <c r="L60" t="n">
-        <v>134.23</v>
+        <v>126.46</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-97.75</v>
+        <v>-93.25</v>
       </c>
       <c r="K61" t="n">
-        <v>6.3</v>
+        <v>6.01</v>
       </c>
       <c r="L61" t="n">
-        <v>97.95999999999999</v>
+        <v>93.45</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-64.55</v>
+        <v>-66.59</v>
       </c>
       <c r="K62" t="n">
-        <v>12.34</v>
+        <v>12.73</v>
       </c>
       <c r="L62" t="n">
-        <v>65.70999999999999</v>
+        <v>67.79000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-59.39</v>
+        <v>-62.34</v>
       </c>
       <c r="K63" t="n">
-        <v>18.08</v>
+        <v>18.98</v>
       </c>
       <c r="L63" t="n">
-        <v>62.08</v>
+        <v>65.17</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-61.36</v>
+        <v>-65.41</v>
       </c>
       <c r="K64" t="n">
-        <v>17.05</v>
+        <v>18.18</v>
       </c>
       <c r="L64" t="n">
-        <v>63.69</v>
+        <v>67.89</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-81.72</v>
+        <v>-78.90000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>137.29</v>
+        <v>132.54</v>
       </c>
       <c r="L65" t="n">
-        <v>159.77</v>
+        <v>154.25</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-50.94</v>
+        <v>-51</v>
       </c>
       <c r="K66" t="n">
-        <v>115.71</v>
+        <v>115.83</v>
       </c>
       <c r="L66" t="n">
-        <v>126.43</v>
+        <v>126.56</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>102.55</v>
+        <v>106.71</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.73</v>
+        <v>-3.88</v>
       </c>
       <c r="L67" t="n">
-        <v>102.62</v>
+        <v>106.78</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-108.29</v>
+        <v>-115.1</v>
       </c>
       <c r="K68" t="n">
-        <v>-40.12</v>
+        <v>-42.64</v>
       </c>
       <c r="L68" t="n">
-        <v>115.48</v>
+        <v>122.74</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-70.98</v>
+        <v>-73.62</v>
       </c>
       <c r="K69" t="n">
-        <v>-114.88</v>
+        <v>-119.16</v>
       </c>
       <c r="L69" t="n">
-        <v>135.04</v>
+        <v>140.07</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-140.64</v>
+        <v>-145.02</v>
       </c>
       <c r="K70" t="n">
-        <v>-14.45</v>
+        <v>-14.9</v>
       </c>
       <c r="L70" t="n">
-        <v>141.38</v>
+        <v>145.78</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>198.95</v>
+        <v>198.5</v>
       </c>
       <c r="K71" t="n">
-        <v>-79.79000000000001</v>
+        <v>-79.59999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>214.36</v>
+        <v>213.86</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-23.03</v>
+        <v>-25.38</v>
       </c>
       <c r="K72" t="n">
-        <v>136.33</v>
+        <v>150.23</v>
       </c>
       <c r="L72" t="n">
-        <v>138.26</v>
+        <v>152.35</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>182.06</v>
+        <v>183.81</v>
       </c>
       <c r="K73" t="n">
-        <v>-142.9</v>
+        <v>-144.28</v>
       </c>
       <c r="L73" t="n">
-        <v>231.45</v>
+        <v>233.68</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-61.41</v>
+        <v>-63.58</v>
       </c>
       <c r="K74" t="n">
-        <v>6.41</v>
+        <v>6.63</v>
       </c>
       <c r="L74" t="n">
-        <v>61.74</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-103.37</v>
+        <v>-98.14</v>
       </c>
       <c r="K75" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="L75" t="n">
-        <v>103.4</v>
+        <v>98.17</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>69.06999999999999</v>
+        <v>69.41</v>
       </c>
       <c r="K76" t="n">
-        <v>15.26</v>
+        <v>15.34</v>
       </c>
       <c r="L76" t="n">
-        <v>70.73</v>
+        <v>71.08</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>56.84</v>
+        <v>61.84</v>
       </c>
       <c r="K77" t="n">
-        <v>-16.27</v>
+        <v>-17.7</v>
       </c>
       <c r="L77" t="n">
-        <v>59.13</v>
+        <v>64.31999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-31.87</v>
+        <v>-31.03</v>
       </c>
       <c r="K78" t="n">
-        <v>106.04</v>
+        <v>103.24</v>
       </c>
       <c r="L78" t="n">
-        <v>110.72</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-20.09</v>
+        <v>-20.02</v>
       </c>
       <c r="K79" t="n">
-        <v>-79.14</v>
+        <v>-78.83</v>
       </c>
       <c r="L79" t="n">
-        <v>81.65000000000001</v>
+        <v>81.33</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>107.77</v>
+        <v>110.86</v>
       </c>
       <c r="K80" t="n">
-        <v>4.13</v>
+        <v>4.25</v>
       </c>
       <c r="L80" t="n">
-        <v>107.85</v>
+        <v>110.94</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>49.57</v>
+        <v>48.23</v>
       </c>
       <c r="K81" t="n">
-        <v>148.46</v>
+        <v>144.46</v>
       </c>
       <c r="L81" t="n">
-        <v>156.52</v>
+        <v>152.3</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-147.5</v>
+        <v>-143</v>
       </c>
       <c r="K82" t="n">
-        <v>15.29</v>
+        <v>14.83</v>
       </c>
       <c r="L82" t="n">
-        <v>148.29</v>
+        <v>143.77</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>131.47</v>
+        <v>132.37</v>
       </c>
       <c r="K83" t="n">
-        <v>113.62</v>
+        <v>114.39</v>
       </c>
       <c r="L83" t="n">
-        <v>173.76</v>
+        <v>174.95</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>123.32</v>
+        <v>120.72</v>
       </c>
       <c r="K84" t="n">
-        <v>133.63</v>
+        <v>130.8</v>
       </c>
       <c r="L84" t="n">
-        <v>181.84</v>
+        <v>177.99</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>126.28</v>
+        <v>128.94</v>
       </c>
       <c r="K85" t="n">
-        <v>-57.49</v>
+        <v>-58.71</v>
       </c>
       <c r="L85" t="n">
-        <v>138.75</v>
+        <v>141.68</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>325.42</v>
+        <v>308.41</v>
       </c>
       <c r="K86" t="n">
-        <v>-152.35</v>
+        <v>-144.39</v>
       </c>
       <c r="L86" t="n">
-        <v>359.32</v>
+        <v>340.54</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-92.92</v>
+        <v>-90.75</v>
       </c>
       <c r="K87" t="n">
-        <v>271.24</v>
+        <v>264.9</v>
       </c>
       <c r="L87" t="n">
-        <v>286.72</v>
+        <v>280.01</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-144.38</v>
+        <v>-144.21</v>
       </c>
       <c r="K88" t="n">
-        <v>-177.8</v>
+        <v>-177.6</v>
       </c>
       <c r="L88" t="n">
-        <v>229.03</v>
+        <v>228.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-03.xlsx
+++ b/output/2024-10-03.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.49</v>
+        <v>2.31</v>
       </c>
       <c r="F14" t="n">
-        <v>7.42</v>
+        <v>3.74</v>
       </c>
       <c r="G14" t="n">
-        <v>174.9</v>
+        <v>182.3</v>
       </c>
       <c r="H14" t="n">
-        <v>78.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-58.94</v>
+        <v>23.88</v>
       </c>
       <c r="K14" t="n">
-        <v>27.8</v>
+        <v>47.35</v>
       </c>
       <c r="L14" t="n">
-        <v>65.17</v>
+        <v>53.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:23:00</t>
+          <t>07:23:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="F15" t="n">
-        <v>7.41</v>
+        <v>7.93</v>
       </c>
       <c r="G15" t="n">
-        <v>172.5</v>
+        <v>177.4</v>
       </c>
       <c r="H15" t="n">
-        <v>84.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1</v>
+        <v>-13.89</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.77</v>
+        <v>-74.40000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>3.47</v>
+        <v>75.69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:25:10</t>
+          <t>07:24:38</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="F16" t="n">
-        <v>7.18</v>
+        <v>2.86</v>
       </c>
       <c r="G16" t="n">
-        <v>183.6</v>
+        <v>191.7</v>
       </c>
       <c r="H16" t="n">
-        <v>76</v>
+        <v>84.5</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>21.77</v>
+        <v>-10.55</v>
       </c>
       <c r="K16" t="n">
-        <v>74.27</v>
+        <v>-28.25</v>
       </c>
       <c r="L16" t="n">
-        <v>77.39</v>
+        <v>30.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:29:46</t>
+          <t>07:29:48</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.16</v>
+        <v>2.77</v>
       </c>
       <c r="F17" t="n">
-        <v>6.55</v>
+        <v>5.48</v>
       </c>
       <c r="G17" t="n">
-        <v>186.6</v>
+        <v>172.6</v>
       </c>
       <c r="H17" t="n">
-        <v>89.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>103.98</v>
+        <v>45.91</v>
       </c>
       <c r="K17" t="n">
-        <v>-29.44</v>
+        <v>-59.65</v>
       </c>
       <c r="L17" t="n">
-        <v>108.07</v>
+        <v>75.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:32:01</t>
+          <t>07:32:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.41</v>
+        <v>2.81</v>
       </c>
       <c r="F18" t="n">
-        <v>6.71</v>
+        <v>4.79</v>
       </c>
       <c r="G18" t="n">
-        <v>191.7</v>
+        <v>182.8</v>
       </c>
       <c r="H18" t="n">
-        <v>80.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-46.03</v>
+        <v>32.15</v>
       </c>
       <c r="K18" t="n">
-        <v>54.09</v>
+        <v>52.99</v>
       </c>
       <c r="L18" t="n">
-        <v>71.02</v>
+        <v>61.98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:33:11</t>
+          <t>07:33:39</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="F19" t="n">
-        <v>7.04</v>
+        <v>5.89</v>
       </c>
       <c r="G19" t="n">
-        <v>173.1</v>
+        <v>178.8</v>
       </c>
       <c r="H19" t="n">
-        <v>77.7</v>
+        <v>80.3</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-62.55</v>
+        <v>61.95</v>
       </c>
       <c r="K19" t="n">
-        <v>14.53</v>
+        <v>39.57</v>
       </c>
       <c r="L19" t="n">
-        <v>64.22</v>
+        <v>73.51000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:36:53</t>
+          <t>07:36:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="F20" t="n">
-        <v>7.09</v>
+        <v>5.21</v>
       </c>
       <c r="G20" t="n">
-        <v>174.6</v>
+        <v>181.4</v>
       </c>
       <c r="H20" t="n">
-        <v>84.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>71.86</v>
+        <v>-68.8</v>
       </c>
       <c r="K20" t="n">
-        <v>64.15000000000001</v>
+        <v>-57.88</v>
       </c>
       <c r="L20" t="n">
-        <v>96.33</v>
+        <v>89.91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:37:26</t>
+          <t>07:37:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.96</v>
+        <v>2.29</v>
       </c>
       <c r="F21" t="n">
-        <v>6.72</v>
+        <v>4.99</v>
       </c>
       <c r="G21" t="n">
-        <v>169.3</v>
+        <v>180</v>
       </c>
       <c r="H21" t="n">
-        <v>79.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>96.69</v>
+        <v>-48.25</v>
       </c>
       <c r="K21" t="n">
-        <v>28.85</v>
+        <v>-103.45</v>
       </c>
       <c r="L21" t="n">
-        <v>100.9</v>
+        <v>114.15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:38:47</t>
+          <t>07:39:48</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="F22" t="n">
-        <v>6.38</v>
+        <v>7.93</v>
       </c>
       <c r="G22" t="n">
-        <v>173.1</v>
+        <v>162.1</v>
       </c>
       <c r="H22" t="n">
-        <v>78.8</v>
+        <v>89.8</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>124.98</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-135.12</v>
+        <v>19.47</v>
       </c>
       <c r="L22" t="n">
-        <v>184.06</v>
+        <v>86.72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:43:44</t>
+          <t>07:43:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="F23" t="n">
-        <v>7.06</v>
+        <v>6.49</v>
       </c>
       <c r="G23" t="n">
-        <v>185.8</v>
+        <v>166.5</v>
       </c>
       <c r="H23" t="n">
-        <v>80.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-87</v>
+        <v>-120.99</v>
       </c>
       <c r="K23" t="n">
-        <v>-171.89</v>
+        <v>109.27</v>
       </c>
       <c r="L23" t="n">
-        <v>192.65</v>
+        <v>163.03</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:45:19</t>
+          <t>07:46:12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>6.71</v>
+        <v>4.06</v>
       </c>
       <c r="G24" t="n">
-        <v>160.6</v>
+        <v>179.7</v>
       </c>
       <c r="H24" t="n">
-        <v>86.7</v>
+        <v>81.2</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-98.69</v>
+        <v>89.75</v>
       </c>
       <c r="K24" t="n">
-        <v>56.38</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>113.66</v>
+        <v>117.96</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:47:16</t>
+          <t>07:48:02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="F25" t="n">
-        <v>7.45</v>
+        <v>7.93</v>
       </c>
       <c r="G25" t="n">
-        <v>194.5</v>
+        <v>174.9</v>
       </c>
       <c r="H25" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-41.21</v>
+        <v>-123.4</v>
       </c>
       <c r="K25" t="n">
-        <v>-108.98</v>
+        <v>-135.41</v>
       </c>
       <c r="L25" t="n">
-        <v>116.51</v>
+        <v>183.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:52:33</t>
+          <t>07:53:39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.57</v>
+        <v>2.01</v>
       </c>
       <c r="F26" t="n">
-        <v>6.74</v>
+        <v>6.76</v>
       </c>
       <c r="G26" t="n">
-        <v>160.3</v>
+        <v>176.8</v>
       </c>
       <c r="H26" t="n">
-        <v>79.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-56.84</v>
+        <v>-210.58</v>
       </c>
       <c r="K26" t="n">
-        <v>-111.81</v>
+        <v>-59.59</v>
       </c>
       <c r="L26" t="n">
-        <v>125.43</v>
+        <v>218.84</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:54:28</t>
+          <t>07:55:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="F27" t="n">
-        <v>7.29</v>
+        <v>7.93</v>
       </c>
       <c r="G27" t="n">
-        <v>180.1</v>
+        <v>174.8</v>
       </c>
       <c r="H27" t="n">
-        <v>86.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>140.75</v>
+        <v>153.25</v>
       </c>
       <c r="K27" t="n">
-        <v>-178.36</v>
+        <v>-95.06999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>227.21</v>
+        <v>180.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:56:42</t>
+          <t>07:56:15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.43</v>
+        <v>3.03</v>
       </c>
       <c r="F28" t="n">
-        <v>6.56</v>
+        <v>7.71</v>
       </c>
       <c r="G28" t="n">
-        <v>179</v>
+        <v>175.3</v>
       </c>
       <c r="H28" t="n">
-        <v>83.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>214.38</v>
+        <v>185.72</v>
       </c>
       <c r="K28" t="n">
-        <v>-31.26</v>
+        <v>35.89</v>
       </c>
       <c r="L28" t="n">
-        <v>216.65</v>
+        <v>189.15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:03:59</t>
+          <t>08:03:24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="F29" t="n">
-        <v>7.08</v>
+        <v>7.12</v>
       </c>
       <c r="G29" t="n">
-        <v>181.9</v>
+        <v>185.4</v>
       </c>
       <c r="H29" t="n">
-        <v>85.2</v>
+        <v>81.5</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>14.79</v>
+        <v>59.78</v>
       </c>
       <c r="K29" t="n">
-        <v>57.14</v>
+        <v>1.26</v>
       </c>
       <c r="L29" t="n">
-        <v>59.02</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:05:25</t>
+          <t>08:05:18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="F30" t="n">
-        <v>6.92</v>
+        <v>7.03</v>
       </c>
       <c r="G30" t="n">
-        <v>184.2</v>
+        <v>180</v>
       </c>
       <c r="H30" t="n">
-        <v>84.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-70.69</v>
+        <v>-14.13</v>
       </c>
       <c r="K30" t="n">
-        <v>0.72</v>
+        <v>-52.39</v>
       </c>
       <c r="L30" t="n">
-        <v>70.69</v>
+        <v>54.26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:07:16</t>
+          <t>08:06:53</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.27</v>
+        <v>2.17</v>
       </c>
       <c r="F31" t="n">
-        <v>6.79</v>
+        <v>6.37</v>
       </c>
       <c r="G31" t="n">
-        <v>164.5</v>
+        <v>187</v>
       </c>
       <c r="H31" t="n">
-        <v>80.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>43.13</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>-79.93000000000001</v>
+        <v>-45.71</v>
       </c>
       <c r="L31" t="n">
-        <v>90.83</v>
+        <v>46.69</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:12:01</t>
+          <t>08:12:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="F32" t="n">
-        <v>7.07</v>
+        <v>7.89</v>
       </c>
       <c r="G32" t="n">
-        <v>173</v>
+        <v>180.8</v>
       </c>
       <c r="H32" t="n">
-        <v>82</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>38.02</v>
+        <v>23.94</v>
       </c>
       <c r="K32" t="n">
-        <v>100.84</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>107.77</v>
+        <v>100.65</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:14:06</t>
+          <t>08:14:54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="F33" t="n">
-        <v>7.28</v>
+        <v>4.48</v>
       </c>
       <c r="G33" t="n">
-        <v>182.9</v>
+        <v>172.2</v>
       </c>
       <c r="H33" t="n">
-        <v>90.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>52.87</v>
+        <v>12.6</v>
       </c>
       <c r="K33" t="n">
-        <v>-41.26</v>
+        <v>-73.95</v>
       </c>
       <c r="L33" t="n">
-        <v>67.06</v>
+        <v>75.02</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:15:37</t>
+          <t>08:16:50</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.29</v>
+        <v>2.61</v>
       </c>
       <c r="F34" t="n">
-        <v>6.83</v>
+        <v>7.85</v>
       </c>
       <c r="G34" t="n">
-        <v>179.1</v>
+        <v>180.6</v>
       </c>
       <c r="H34" t="n">
-        <v>80</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>38</v>
+        <v>69.42</v>
       </c>
       <c r="K34" t="n">
-        <v>55.85</v>
+        <v>-8.93</v>
       </c>
       <c r="L34" t="n">
-        <v>67.55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:20:08</t>
+          <t>08:22:35</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.8</v>
+        <v>2.13</v>
       </c>
       <c r="F35" t="n">
-        <v>6.54</v>
+        <v>4.09</v>
       </c>
       <c r="G35" t="n">
-        <v>181.7</v>
+        <v>188.3</v>
       </c>
       <c r="H35" t="n">
-        <v>74.2</v>
+        <v>84</v>
       </c>
       <c r="I35" t="n">
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>32.85</v>
+        <v>-66.29000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>112.55</v>
+        <v>-101.92</v>
       </c>
       <c r="L35" t="n">
-        <v>117.24</v>
+        <v>121.58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:22:19</t>
+          <t>08:24:54</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.99</v>
+        <v>2.67</v>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>5.05</v>
       </c>
       <c r="G36" t="n">
-        <v>180.2</v>
+        <v>182.4</v>
       </c>
       <c r="H36" t="n">
-        <v>77.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.19</v>
+        <v>-91.87</v>
       </c>
       <c r="K36" t="n">
-        <v>99.18000000000001</v>
+        <v>-74.15000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>99.23</v>
+        <v>118.06</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:23:49</t>
+          <t>08:26:37</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="F37" t="n">
-        <v>6.77</v>
+        <v>6.13</v>
       </c>
       <c r="G37" t="n">
-        <v>183.2</v>
+        <v>169.9</v>
       </c>
       <c r="H37" t="n">
-        <v>81.7</v>
+        <v>91.5</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>146.73</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-66.29000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>161.01</v>
+        <v>107.96</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:29:20</t>
+          <t>08:31:34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.47</v>
+        <v>2.71</v>
       </c>
       <c r="F38" t="n">
-        <v>7.62</v>
+        <v>7.59</v>
       </c>
       <c r="G38" t="n">
-        <v>180.9</v>
+        <v>178.4</v>
       </c>
       <c r="H38" t="n">
-        <v>86.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-197.04</v>
+        <v>152.75</v>
       </c>
       <c r="K38" t="n">
-        <v>-184.99</v>
+        <v>74.88</v>
       </c>
       <c r="L38" t="n">
-        <v>270.27</v>
+        <v>170.11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:30:36</t>
+          <t>08:33:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.64</v>
+        <v>2.27</v>
       </c>
       <c r="F39" t="n">
-        <v>7.44</v>
+        <v>7.43</v>
       </c>
       <c r="G39" t="n">
-        <v>164.9</v>
+        <v>188.7</v>
       </c>
       <c r="H39" t="n">
-        <v>86.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-97.84999999999999</v>
+        <v>61.14</v>
       </c>
       <c r="K39" t="n">
-        <v>-56.46</v>
+        <v>128.3</v>
       </c>
       <c r="L39" t="n">
-        <v>112.97</v>
+        <v>142.12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:32:41</t>
+          <t>08:36:11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.93</v>
+        <v>2.61</v>
       </c>
       <c r="F40" t="n">
-        <v>6.86</v>
+        <v>7.01</v>
       </c>
       <c r="G40" t="n">
-        <v>186.3</v>
+        <v>171.1</v>
       </c>
       <c r="H40" t="n">
-        <v>84.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I40" t="n">
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>14.93</v>
+        <v>-61.97</v>
       </c>
       <c r="K40" t="n">
-        <v>-145.87</v>
+        <v>-187.22</v>
       </c>
       <c r="L40" t="n">
-        <v>146.63</v>
+        <v>197.21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:37:30</t>
+          <t>08:41:30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="F41" t="n">
-        <v>6.69</v>
+        <v>5.18</v>
       </c>
       <c r="G41" t="n">
-        <v>178.6</v>
+        <v>177.8</v>
       </c>
       <c r="H41" t="n">
-        <v>76.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>20.21</v>
+        <v>108.32</v>
       </c>
       <c r="K41" t="n">
-        <v>174.84</v>
+        <v>138.46</v>
       </c>
       <c r="L41" t="n">
-        <v>176.01</v>
+        <v>175.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:39:43</t>
+          <t>08:43:42</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
       <c r="F42" t="n">
-        <v>7.79</v>
+        <v>6.71</v>
       </c>
       <c r="G42" t="n">
-        <v>185.9</v>
+        <v>179.7</v>
       </c>
       <c r="H42" t="n">
-        <v>84.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-194.12</v>
+        <v>42.83</v>
       </c>
       <c r="K42" t="n">
-        <v>138.77</v>
+        <v>227.54</v>
       </c>
       <c r="L42" t="n">
-        <v>238.62</v>
+        <v>231.54</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:40:46</t>
+          <t>08:44:54</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="F43" t="n">
-        <v>6.49</v>
+        <v>7.74</v>
       </c>
       <c r="G43" t="n">
-        <v>187.2</v>
+        <v>164</v>
       </c>
       <c r="H43" t="n">
-        <v>90.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I43" t="n">
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>66.51000000000001</v>
+        <v>36.95</v>
       </c>
       <c r="K43" t="n">
-        <v>-260.69</v>
+        <v>-295.61</v>
       </c>
       <c r="L43" t="n">
-        <v>269.04</v>
+        <v>297.91</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:49:41</t>
+          <t>08:55:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.3</v>
+        <v>2.77</v>
       </c>
       <c r="F44" t="n">
-        <v>7.06</v>
+        <v>7.03</v>
       </c>
       <c r="G44" t="n">
-        <v>162.9</v>
+        <v>182.2</v>
       </c>
       <c r="H44" t="n">
-        <v>83.2</v>
+        <v>82.7</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-30.06</v>
+        <v>-74.03</v>
       </c>
       <c r="K44" t="n">
-        <v>6.14</v>
+        <v>-41.7</v>
       </c>
       <c r="L44" t="n">
-        <v>30.68</v>
+        <v>84.95999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:50:32</t>
+          <t>08:57:28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="F45" t="n">
-        <v>6.56</v>
+        <v>7.93</v>
       </c>
       <c r="G45" t="n">
-        <v>174.4</v>
+        <v>175.9</v>
       </c>
       <c r="H45" t="n">
-        <v>78.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>37.35</v>
+        <v>-41.88</v>
       </c>
       <c r="K45" t="n">
-        <v>-66.31999999999999</v>
+        <v>53.22</v>
       </c>
       <c r="L45" t="n">
-        <v>76.11</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:52:40</t>
+          <t>08:58:31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.63</v>
+        <v>3.01</v>
       </c>
       <c r="F46" t="n">
-        <v>7.45</v>
+        <v>7.93</v>
       </c>
       <c r="G46" t="n">
-        <v>184.4</v>
+        <v>173.4</v>
       </c>
       <c r="H46" t="n">
-        <v>79.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>9.77</v>
+        <v>15.32</v>
       </c>
       <c r="K46" t="n">
-        <v>67.25</v>
+        <v>69.22</v>
       </c>
       <c r="L46" t="n">
-        <v>67.95999999999999</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:56:47</t>
+          <t>09:02:50</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="F47" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="G47" t="n">
-        <v>174.7</v>
+        <v>176</v>
       </c>
       <c r="H47" t="n">
-        <v>87.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-60.4</v>
+        <v>-102.45</v>
       </c>
       <c r="K47" t="n">
-        <v>-64.59</v>
+        <v>-24.03</v>
       </c>
       <c r="L47" t="n">
-        <v>88.43000000000001</v>
+        <v>105.23</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:58:16</t>
+          <t>09:03:56</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>7.42</v>
+        <v>7.93</v>
       </c>
       <c r="G48" t="n">
-        <v>174.7</v>
+        <v>170.3</v>
       </c>
       <c r="H48" t="n">
-        <v>75.2</v>
+        <v>78</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>73.29000000000001</v>
+        <v>101.24</v>
       </c>
       <c r="K48" t="n">
-        <v>-67.65000000000001</v>
+        <v>-38.32</v>
       </c>
       <c r="L48" t="n">
-        <v>99.73999999999999</v>
+        <v>108.24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:00:30</t>
+          <t>09:06:11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="F49" t="n">
-        <v>6.34</v>
+        <v>7.75</v>
       </c>
       <c r="G49" t="n">
-        <v>163.7</v>
+        <v>178.2</v>
       </c>
       <c r="H49" t="n">
-        <v>79.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-76.03</v>
+        <v>27.28</v>
       </c>
       <c r="K49" t="n">
-        <v>65.43000000000001</v>
+        <v>-78.38</v>
       </c>
       <c r="L49" t="n">
-        <v>100.31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:05:03</t>
+          <t>09:10:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="F50" t="n">
-        <v>6.96</v>
+        <v>7.93</v>
       </c>
       <c r="G50" t="n">
-        <v>171.2</v>
+        <v>181.1</v>
       </c>
       <c r="H50" t="n">
-        <v>83.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>114.6</v>
+        <v>-70.84</v>
       </c>
       <c r="K50" t="n">
-        <v>-92.22</v>
+        <v>-71.79000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>147.1</v>
+        <v>100.86</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:06:07</t>
+          <t>09:11:35</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="F51" t="n">
-        <v>6.89</v>
+        <v>7.87</v>
       </c>
       <c r="G51" t="n">
-        <v>201.5</v>
+        <v>176.3</v>
       </c>
       <c r="H51" t="n">
-        <v>81</v>
+        <v>76.5</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-38.2</v>
+        <v>51.36</v>
       </c>
       <c r="K51" t="n">
-        <v>-127.55</v>
+        <v>102.06</v>
       </c>
       <c r="L51" t="n">
-        <v>133.15</v>
+        <v>114.25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:06:55</t>
+          <t>09:13:43</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="F52" t="n">
-        <v>6.54</v>
+        <v>7.18</v>
       </c>
       <c r="G52" t="n">
-        <v>184.8</v>
+        <v>180.8</v>
       </c>
       <c r="H52" t="n">
-        <v>83.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>24.24</v>
+        <v>83</v>
       </c>
       <c r="K52" t="n">
-        <v>-96.7</v>
+        <v>-47.19</v>
       </c>
       <c r="L52" t="n">
-        <v>99.69</v>
+        <v>95.48</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:13:23</t>
+          <t>09:17:48</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>6.8</v>
+        <v>7.57</v>
       </c>
       <c r="G53" t="n">
-        <v>186.3</v>
+        <v>164</v>
       </c>
       <c r="H53" t="n">
-        <v>81.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I53" t="n">
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>147.2</v>
+        <v>71.47</v>
       </c>
       <c r="K53" t="n">
-        <v>-124.63</v>
+        <v>148.39</v>
       </c>
       <c r="L53" t="n">
-        <v>192.87</v>
+        <v>164.71</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:14:58</t>
+          <t>09:19:03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.37</v>
+        <v>2.61</v>
       </c>
       <c r="F54" t="n">
-        <v>6.64</v>
+        <v>7.11</v>
       </c>
       <c r="G54" t="n">
-        <v>187.9</v>
+        <v>170.8</v>
       </c>
       <c r="H54" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I54" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>5.08</v>
+        <v>-11.25</v>
       </c>
       <c r="K54" t="n">
-        <v>-67.73</v>
+        <v>-168.65</v>
       </c>
       <c r="L54" t="n">
-        <v>67.92</v>
+        <v>169.02</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:17:25</t>
+          <t>09:20:35</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="F55" t="n">
-        <v>7.06</v>
+        <v>7.93</v>
       </c>
       <c r="G55" t="n">
-        <v>197.3</v>
+        <v>185.4</v>
       </c>
       <c r="H55" t="n">
-        <v>77.2</v>
+        <v>85</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>174.88</v>
+        <v>134.71</v>
       </c>
       <c r="K55" t="n">
-        <v>55.41</v>
+        <v>-72.34</v>
       </c>
       <c r="L55" t="n">
-        <v>183.44</v>
+        <v>152.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:21:02</t>
+          <t>09:23:52</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.98</v>
+        <v>2.77</v>
       </c>
       <c r="F56" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="G56" t="n">
-        <v>177.3</v>
+        <v>181.6</v>
       </c>
       <c r="H56" t="n">
-        <v>85.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-131.1</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>120.31</v>
+        <v>234.81</v>
       </c>
       <c r="L56" t="n">
-        <v>177.94</v>
+        <v>252.27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:21:45</t>
+          <t>09:25:18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="F57" t="n">
-        <v>6.82</v>
+        <v>7.93</v>
       </c>
       <c r="G57" t="n">
-        <v>186</v>
+        <v>193.7</v>
       </c>
       <c r="H57" t="n">
-        <v>90.5</v>
+        <v>78.7</v>
       </c>
       <c r="I57" t="n">
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>205.38</v>
+        <v>190.37</v>
       </c>
       <c r="K57" t="n">
-        <v>-160.29</v>
+        <v>-90.28</v>
       </c>
       <c r="L57" t="n">
-        <v>260.53</v>
+        <v>210.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:23:15</t>
+          <t>09:27:10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.21</v>
+        <v>2.77</v>
       </c>
       <c r="F58" t="n">
-        <v>6.88</v>
+        <v>7.93</v>
       </c>
       <c r="G58" t="n">
-        <v>177.7</v>
+        <v>166.1</v>
       </c>
       <c r="H58" t="n">
-        <v>86.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>152.62</v>
+        <v>240.98</v>
       </c>
       <c r="K58" t="n">
-        <v>-241.53</v>
+        <v>-134.89</v>
       </c>
       <c r="L58" t="n">
-        <v>285.71</v>
+        <v>276.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:31:33</t>
+          <t>09:36:54</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.47</v>
+        <v>3.03</v>
       </c>
       <c r="F59" t="n">
-        <v>7.22</v>
+        <v>7.93</v>
       </c>
       <c r="G59" t="n">
-        <v>185.6</v>
+        <v>181.7</v>
       </c>
       <c r="H59" t="n">
-        <v>79.8</v>
+        <v>81.8</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>67.59</v>
+        <v>-63.44</v>
       </c>
       <c r="K59" t="n">
-        <v>-9.210000000000001</v>
+        <v>59.14</v>
       </c>
       <c r="L59" t="n">
-        <v>68.22</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:32:41</t>
+          <t>09:38:32</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.91</v>
+        <v>3.78</v>
       </c>
       <c r="F60" t="n">
-        <v>7.12</v>
+        <v>7.93</v>
       </c>
       <c r="G60" t="n">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="H60" t="n">
-        <v>77.7</v>
+        <v>84.3</v>
       </c>
       <c r="I60" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>90.11</v>
+        <v>-63.04</v>
       </c>
       <c r="K60" t="n">
-        <v>88.72</v>
+        <v>3.25</v>
       </c>
       <c r="L60" t="n">
-        <v>126.46</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:34:41</t>
+          <t>09:40:39</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.9</v>
+        <v>2.61</v>
       </c>
       <c r="F61" t="n">
-        <v>6.53</v>
+        <v>3.61</v>
       </c>
       <c r="G61" t="n">
-        <v>178.3</v>
+        <v>175</v>
       </c>
       <c r="H61" t="n">
-        <v>79.2</v>
+        <v>73.3</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-93.25</v>
+        <v>-30.47</v>
       </c>
       <c r="K61" t="n">
-        <v>6.01</v>
+        <v>-47.37</v>
       </c>
       <c r="L61" t="n">
-        <v>93.45</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:38:43</t>
+          <t>09:44:43</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.3</v>
+        <v>2.81</v>
       </c>
       <c r="F62" t="n">
-        <v>6.47</v>
+        <v>7.93</v>
       </c>
       <c r="G62" t="n">
-        <v>171.8</v>
+        <v>176.8</v>
       </c>
       <c r="H62" t="n">
-        <v>85.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-66.59</v>
+        <v>-0.46</v>
       </c>
       <c r="K62" t="n">
-        <v>12.73</v>
+        <v>93.83</v>
       </c>
       <c r="L62" t="n">
-        <v>67.79000000000001</v>
+        <v>93.83</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:39:45</t>
+          <t>09:46:57</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.58</v>
+        <v>2.87</v>
       </c>
       <c r="F63" t="n">
-        <v>6.98</v>
+        <v>6.93</v>
       </c>
       <c r="G63" t="n">
-        <v>190.7</v>
+        <v>177.8</v>
       </c>
       <c r="H63" t="n">
-        <v>82.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-62.34</v>
+        <v>-48.66</v>
       </c>
       <c r="K63" t="n">
-        <v>18.98</v>
+        <v>-45.94</v>
       </c>
       <c r="L63" t="n">
-        <v>65.17</v>
+        <v>66.92</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:41:29</t>
+          <t>09:49:28</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="F64" t="n">
-        <v>6.74</v>
+        <v>7.81</v>
       </c>
       <c r="G64" t="n">
-        <v>173.6</v>
+        <v>189.6</v>
       </c>
       <c r="H64" t="n">
-        <v>85.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-65.41</v>
+        <v>-61</v>
       </c>
       <c r="K64" t="n">
-        <v>18.18</v>
+        <v>23.87</v>
       </c>
       <c r="L64" t="n">
-        <v>67.89</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:46:51</t>
+          <t>09:53:48</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.75</v>
+        <v>3.99</v>
       </c>
       <c r="F65" t="n">
-        <v>7.32</v>
+        <v>7.93</v>
       </c>
       <c r="G65" t="n">
-        <v>180</v>
+        <v>189.2</v>
       </c>
       <c r="H65" t="n">
-        <v>80.2</v>
+        <v>83.8</v>
       </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-78.90000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>132.54</v>
+        <v>-135.57</v>
       </c>
       <c r="L65" t="n">
-        <v>154.25</v>
+        <v>135.92</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:48:26</t>
+          <t>09:54:45</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="F66" t="n">
-        <v>6.88</v>
+        <v>7.93</v>
       </c>
       <c r="G66" t="n">
-        <v>183.8</v>
+        <v>191.7</v>
       </c>
       <c r="H66" t="n">
-        <v>88.3</v>
+        <v>81.8</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-51</v>
+        <v>116.6</v>
       </c>
       <c r="K66" t="n">
-        <v>115.83</v>
+        <v>6.72</v>
       </c>
       <c r="L66" t="n">
-        <v>126.56</v>
+        <v>116.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:50:11</t>
+          <t>09:56:11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.99</v>
+        <v>3.28</v>
       </c>
       <c r="F67" t="n">
-        <v>6.99</v>
+        <v>7.93</v>
       </c>
       <c r="G67" t="n">
-        <v>185.5</v>
+        <v>171.8</v>
       </c>
       <c r="H67" t="n">
-        <v>81.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>106.71</v>
+        <v>42.71</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.88</v>
+        <v>-92.79000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>106.78</v>
+        <v>102.15</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:54:33</t>
+          <t>10:01:56</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="F68" t="n">
-        <v>7.02</v>
+        <v>7.72</v>
       </c>
       <c r="G68" t="n">
-        <v>166.7</v>
+        <v>191.5</v>
       </c>
       <c r="H68" t="n">
-        <v>79.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-115.1</v>
+        <v>209.43</v>
       </c>
       <c r="K68" t="n">
-        <v>-42.64</v>
+        <v>-73.52</v>
       </c>
       <c r="L68" t="n">
-        <v>122.74</v>
+        <v>221.96</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:56:47</t>
+          <t>10:04:33</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.86</v>
+        <v>3.04</v>
       </c>
       <c r="F69" t="n">
-        <v>6.72</v>
+        <v>7.58</v>
       </c>
       <c r="G69" t="n">
-        <v>194.5</v>
+        <v>159.7</v>
       </c>
       <c r="H69" t="n">
-        <v>85.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-73.62</v>
+        <v>-185.17</v>
       </c>
       <c r="K69" t="n">
-        <v>-119.16</v>
+        <v>-121.79</v>
       </c>
       <c r="L69" t="n">
-        <v>140.07</v>
+        <v>221.63</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:57:58</t>
+          <t>10:06:46</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.33</v>
+        <v>2.68</v>
       </c>
       <c r="F70" t="n">
-        <v>6.1</v>
+        <v>4.24</v>
       </c>
       <c r="G70" t="n">
-        <v>171.9</v>
+        <v>162.6</v>
       </c>
       <c r="H70" t="n">
-        <v>73.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-145.02</v>
+        <v>-48.64</v>
       </c>
       <c r="K70" t="n">
-        <v>-14.9</v>
+        <v>112.96</v>
       </c>
       <c r="L70" t="n">
-        <v>145.78</v>
+        <v>122.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:03:51</t>
+          <t>10:11:44</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.42</v>
+        <v>2.96</v>
       </c>
       <c r="F71" t="n">
-        <v>7.23</v>
+        <v>7.7</v>
       </c>
       <c r="G71" t="n">
-        <v>175</v>
+        <v>185.8</v>
       </c>
       <c r="H71" t="n">
-        <v>82</v>
+        <v>84.2</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>198.5</v>
+        <v>136.34</v>
       </c>
       <c r="K71" t="n">
-        <v>-79.59999999999999</v>
+        <v>-80.08</v>
       </c>
       <c r="L71" t="n">
-        <v>213.86</v>
+        <v>158.12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:05:12</t>
+          <t>10:13:36</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="F72" t="n">
-        <v>7.03</v>
+        <v>7.93</v>
       </c>
       <c r="G72" t="n">
-        <v>184.2</v>
+        <v>174.7</v>
       </c>
       <c r="H72" t="n">
-        <v>86.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>-25.38</v>
+        <v>54.71</v>
       </c>
       <c r="K72" t="n">
-        <v>150.23</v>
+        <v>-323.4</v>
       </c>
       <c r="L72" t="n">
-        <v>152.35</v>
+        <v>327.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:06:58</t>
+          <t>10:14:44</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.32</v>
+        <v>2.86</v>
       </c>
       <c r="F73" t="n">
-        <v>6.05</v>
+        <v>7.17</v>
       </c>
       <c r="G73" t="n">
-        <v>180.7</v>
+        <v>180.3</v>
       </c>
       <c r="H73" t="n">
-        <v>80.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>183.81</v>
+        <v>-213.89</v>
       </c>
       <c r="K73" t="n">
-        <v>-144.28</v>
+        <v>-98.61</v>
       </c>
       <c r="L73" t="n">
-        <v>233.68</v>
+        <v>235.53</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:14:58</t>
+          <t>10:26:36</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="F74" t="n">
-        <v>6.34</v>
+        <v>7.24</v>
       </c>
       <c r="G74" t="n">
-        <v>159.7</v>
+        <v>168.9</v>
       </c>
       <c r="H74" t="n">
-        <v>83.8</v>
+        <v>87.2</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-63.58</v>
+        <v>31</v>
       </c>
       <c r="K74" t="n">
-        <v>6.63</v>
+        <v>42.42</v>
       </c>
       <c r="L74" t="n">
-        <v>63.92</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:16:41</t>
+          <t>10:27:43</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="F75" t="n">
-        <v>7.04</v>
+        <v>7.93</v>
       </c>
       <c r="G75" t="n">
-        <v>179.3</v>
+        <v>183.4</v>
       </c>
       <c r="H75" t="n">
-        <v>81.7</v>
+        <v>86</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>-98.14</v>
+        <v>-69.09</v>
       </c>
       <c r="K75" t="n">
-        <v>2.54</v>
+        <v>14.58</v>
       </c>
       <c r="L75" t="n">
-        <v>98.17</v>
+        <v>70.61</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:17:08</t>
+          <t>10:28:52</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.86</v>
+        <v>3.22</v>
       </c>
       <c r="F76" t="n">
-        <v>7.03</v>
+        <v>7.93</v>
       </c>
       <c r="G76" t="n">
-        <v>179.5</v>
+        <v>172.6</v>
       </c>
       <c r="H76" t="n">
-        <v>85.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>69.41</v>
+        <v>-0.78</v>
       </c>
       <c r="K76" t="n">
-        <v>15.34</v>
+        <v>-59.06</v>
       </c>
       <c r="L76" t="n">
-        <v>71.08</v>
+        <v>59.06</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:21:01</t>
+          <t>10:34:47</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.38</v>
+        <v>2.38</v>
       </c>
       <c r="F77" t="n">
-        <v>5.91</v>
+        <v>7.26</v>
       </c>
       <c r="G77" t="n">
-        <v>174.6</v>
+        <v>177.9</v>
       </c>
       <c r="H77" t="n">
-        <v>82.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>61.84</v>
+        <v>53.35</v>
       </c>
       <c r="K77" t="n">
-        <v>-17.7</v>
+        <v>-52.14</v>
       </c>
       <c r="L77" t="n">
-        <v>64.31999999999999</v>
+        <v>74.59</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:23:20</t>
+          <t>10:36:21</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.51</v>
+        <v>3.12</v>
       </c>
       <c r="F78" t="n">
-        <v>7.25</v>
+        <v>7.93</v>
       </c>
       <c r="G78" t="n">
-        <v>172.5</v>
+        <v>169.4</v>
       </c>
       <c r="H78" t="n">
-        <v>85.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-31.03</v>
+        <v>-78.01000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>103.24</v>
+        <v>-56.92</v>
       </c>
       <c r="L78" t="n">
-        <v>107.8</v>
+        <v>96.56999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:24:08</t>
+          <t>10:37:36</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="F79" t="n">
-        <v>7.18</v>
+        <v>7.93</v>
       </c>
       <c r="G79" t="n">
-        <v>178.7</v>
+        <v>171.8</v>
       </c>
       <c r="H79" t="n">
-        <v>79.2</v>
+        <v>77.5</v>
       </c>
       <c r="I79" t="n">
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-20.02</v>
+        <v>58.43</v>
       </c>
       <c r="K79" t="n">
-        <v>-78.83</v>
+        <v>57.31</v>
       </c>
       <c r="L79" t="n">
-        <v>81.33</v>
+        <v>81.84999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:29:01</t>
+          <t>10:42:47</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.76</v>
+        <v>2.93</v>
       </c>
       <c r="F80" t="n">
-        <v>6.88</v>
+        <v>7.93</v>
       </c>
       <c r="G80" t="n">
-        <v>184</v>
+        <v>188.7</v>
       </c>
       <c r="H80" t="n">
-        <v>85.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>110.86</v>
+        <v>-50.36</v>
       </c>
       <c r="K80" t="n">
-        <v>4.25</v>
+        <v>-86.54000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>110.94</v>
+        <v>100.13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:30:54</t>
+          <t>10:45:43</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.23</v>
+        <v>3.09</v>
       </c>
       <c r="F81" t="n">
-        <v>6.33</v>
+        <v>7.93</v>
       </c>
       <c r="G81" t="n">
-        <v>182.8</v>
+        <v>177.3</v>
       </c>
       <c r="H81" t="n">
-        <v>80.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>48.23</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>144.46</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>152.3</v>
+        <v>112.79</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:31:51</t>
+          <t>10:46:21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.91</v>
+        <v>2.79</v>
       </c>
       <c r="F82" t="n">
-        <v>6.61</v>
+        <v>5.03</v>
       </c>
       <c r="G82" t="n">
-        <v>185.8</v>
+        <v>189.9</v>
       </c>
       <c r="H82" t="n">
-        <v>85.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-143</v>
+        <v>-44.29</v>
       </c>
       <c r="K82" t="n">
-        <v>14.83</v>
+        <v>-75.94</v>
       </c>
       <c r="L82" t="n">
-        <v>143.77</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:36:06</t>
+          <t>10:50:36</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="F83" t="n">
-        <v>7.8</v>
+        <v>7.93</v>
       </c>
       <c r="G83" t="n">
-        <v>193</v>
+        <v>167.4</v>
       </c>
       <c r="H83" t="n">
-        <v>81.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="I83" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>132.37</v>
+        <v>-137.1</v>
       </c>
       <c r="K83" t="n">
-        <v>114.39</v>
+        <v>-74.95</v>
       </c>
       <c r="L83" t="n">
-        <v>174.95</v>
+        <v>156.25</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:37:29</t>
+          <t>10:51:22</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.65</v>
+        <v>3.21</v>
       </c>
       <c r="F84" t="n">
-        <v>7.36</v>
+        <v>7.93</v>
       </c>
       <c r="G84" t="n">
-        <v>176.2</v>
+        <v>163.5</v>
       </c>
       <c r="H84" t="n">
-        <v>78.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>120.72</v>
+        <v>148.93</v>
       </c>
       <c r="K84" t="n">
-        <v>130.8</v>
+        <v>104.44</v>
       </c>
       <c r="L84" t="n">
-        <v>177.99</v>
+        <v>181.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:39:54</t>
+          <t>10:52:22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.55</v>
+        <v>3.01</v>
       </c>
       <c r="F85" t="n">
-        <v>7.06</v>
+        <v>7.93</v>
       </c>
       <c r="G85" t="n">
-        <v>179.7</v>
+        <v>185.2</v>
       </c>
       <c r="H85" t="n">
-        <v>87.3</v>
+        <v>81.3</v>
       </c>
       <c r="I85" t="n">
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>128.94</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>-58.71</v>
+        <v>-48.21</v>
       </c>
       <c r="L85" t="n">
-        <v>141.68</v>
+        <v>104.05</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:43:23</t>
+          <t>10:57:55</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="F86" t="n">
-        <v>6.56</v>
+        <v>7.93</v>
       </c>
       <c r="G86" t="n">
-        <v>179.2</v>
+        <v>180.6</v>
       </c>
       <c r="H86" t="n">
-        <v>83.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>308.41</v>
+        <v>-35.06</v>
       </c>
       <c r="K86" t="n">
-        <v>-144.39</v>
+        <v>163.01</v>
       </c>
       <c r="L86" t="n">
-        <v>340.54</v>
+        <v>166.74</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:45:41</t>
+          <t>10:58:54</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="F87" t="n">
-        <v>6.55</v>
+        <v>7.93</v>
       </c>
       <c r="G87" t="n">
-        <v>180.2</v>
+        <v>181</v>
       </c>
       <c r="H87" t="n">
-        <v>85.2</v>
+        <v>89.5</v>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>-90.75</v>
+        <v>61.13</v>
       </c>
       <c r="K87" t="n">
-        <v>264.9</v>
+        <v>-241.54</v>
       </c>
       <c r="L87" t="n">
-        <v>280.01</v>
+        <v>249.16</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:47:19</t>
+          <t>11:00:18</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="F88" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="G88" t="n">
-        <v>170.2</v>
+        <v>197.1</v>
       </c>
       <c r="H88" t="n">
-        <v>83.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I88" t="n">
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-144.21</v>
+        <v>-109.34</v>
       </c>
       <c r="K88" t="n">
-        <v>-177.6</v>
+        <v>-196.48</v>
       </c>
       <c r="L88" t="n">
-        <v>228.77</v>
+        <v>224.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-03.xlsx
+++ b/output/2024-10-03.xlsx
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.89</v>
+        <v>-13.61</v>
       </c>
       <c r="K15" t="n">
-        <v>-74.40000000000001</v>
+        <v>-72.89</v>
       </c>
       <c r="L15" t="n">
-        <v>75.69</v>
+        <v>74.14</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.55</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-28.25</v>
+        <v>-26.45</v>
       </c>
       <c r="L16" t="n">
-        <v>30.16</v>
+        <v>28.23</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>45.91</v>
+        <v>47.68</v>
       </c>
       <c r="K17" t="n">
-        <v>-59.65</v>
+        <v>-61.94</v>
       </c>
       <c r="L17" t="n">
-        <v>75.27</v>
+        <v>78.17</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>32.15</v>
+        <v>31.49</v>
       </c>
       <c r="K18" t="n">
-        <v>52.99</v>
+        <v>51.9</v>
       </c>
       <c r="L18" t="n">
-        <v>61.98</v>
+        <v>60.71</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>61.95</v>
+        <v>64.33</v>
       </c>
       <c r="K19" t="n">
-        <v>39.57</v>
+        <v>41.1</v>
       </c>
       <c r="L19" t="n">
-        <v>73.51000000000001</v>
+        <v>76.34</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-68.8</v>
+        <v>-72.7</v>
       </c>
       <c r="K20" t="n">
-        <v>-57.88</v>
+        <v>-61.15</v>
       </c>
       <c r="L20" t="n">
-        <v>89.91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-48.25</v>
+        <v>-50.98</v>
       </c>
       <c r="K21" t="n">
-        <v>-103.45</v>
+        <v>-109.31</v>
       </c>
       <c r="L21" t="n">
-        <v>114.15</v>
+        <v>120.61</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>84.51000000000001</v>
+        <v>80.98</v>
       </c>
       <c r="K22" t="n">
-        <v>19.47</v>
+        <v>18.66</v>
       </c>
       <c r="L22" t="n">
-        <v>86.72</v>
+        <v>83.11</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-120.99</v>
+        <v>-127.84</v>
       </c>
       <c r="K23" t="n">
-        <v>109.27</v>
+        <v>115.45</v>
       </c>
       <c r="L23" t="n">
-        <v>163.03</v>
+        <v>172.26</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>89.75</v>
+        <v>87.92</v>
       </c>
       <c r="K24" t="n">
-        <v>76.54000000000001</v>
+        <v>74.98</v>
       </c>
       <c r="L24" t="n">
-        <v>117.96</v>
+        <v>115.55</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-123.4</v>
+        <v>-130.38</v>
       </c>
       <c r="K25" t="n">
-        <v>-135.41</v>
+        <v>-143.08</v>
       </c>
       <c r="L25" t="n">
-        <v>183.2</v>
+        <v>193.57</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-210.58</v>
+        <v>-214.7</v>
       </c>
       <c r="K26" t="n">
-        <v>-59.59</v>
+        <v>-60.76</v>
       </c>
       <c r="L26" t="n">
-        <v>218.84</v>
+        <v>223.14</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>153.25</v>
+        <v>159.14</v>
       </c>
       <c r="K27" t="n">
-        <v>-95.06999999999999</v>
+        <v>-98.73</v>
       </c>
       <c r="L27" t="n">
-        <v>180.35</v>
+        <v>187.28</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>185.72</v>
+        <v>181.93</v>
       </c>
       <c r="K28" t="n">
-        <v>35.89</v>
+        <v>35.16</v>
       </c>
       <c r="L28" t="n">
-        <v>189.15</v>
+        <v>185.29</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>59.78</v>
+        <v>60.96</v>
       </c>
       <c r="K29" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="L29" t="n">
-        <v>59.8</v>
+        <v>60.97</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.13</v>
+        <v>-13.84</v>
       </c>
       <c r="K30" t="n">
-        <v>-52.39</v>
+        <v>-51.32</v>
       </c>
       <c r="L30" t="n">
-        <v>54.26</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.539999999999999</v>
+        <v>-9.15</v>
       </c>
       <c r="K31" t="n">
-        <v>-45.71</v>
+        <v>-43.8</v>
       </c>
       <c r="L31" t="n">
-        <v>46.69</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>23.94</v>
+        <v>22.94</v>
       </c>
       <c r="K32" t="n">
-        <v>97.76000000000001</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>100.65</v>
+        <v>96.45</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>12.6</v>
+        <v>13.09</v>
       </c>
       <c r="K33" t="n">
-        <v>-73.95</v>
+        <v>-76.79000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>75.02</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>69.42</v>
+        <v>70.78</v>
       </c>
       <c r="K34" t="n">
-        <v>-8.93</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>70</v>
+        <v>71.37</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-66.29000000000001</v>
+        <v>-67.59</v>
       </c>
       <c r="K35" t="n">
-        <v>-101.92</v>
+        <v>-103.92</v>
       </c>
       <c r="L35" t="n">
-        <v>121.58</v>
+        <v>123.96</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-91.87</v>
+        <v>-97.06999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-74.15000000000001</v>
+        <v>-78.34999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>118.06</v>
+        <v>124.74</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>69.76000000000001</v>
+        <v>68.33</v>
       </c>
       <c r="K37" t="n">
-        <v>82.40000000000001</v>
+        <v>80.72</v>
       </c>
       <c r="L37" t="n">
-        <v>107.96</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>152.75</v>
+        <v>146.38</v>
       </c>
       <c r="K38" t="n">
-        <v>74.88</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>170.11</v>
+        <v>163.02</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>61.14</v>
+        <v>59.9</v>
       </c>
       <c r="K39" t="n">
-        <v>128.3</v>
+        <v>125.68</v>
       </c>
       <c r="L39" t="n">
-        <v>142.12</v>
+        <v>139.22</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-61.97</v>
+        <v>-64.34999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-187.22</v>
+        <v>-194.42</v>
       </c>
       <c r="L40" t="n">
-        <v>197.21</v>
+        <v>204.79</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>108.32</v>
+        <v>103.81</v>
       </c>
       <c r="K41" t="n">
-        <v>138.46</v>
+        <v>132.69</v>
       </c>
       <c r="L41" t="n">
-        <v>175.8</v>
+        <v>168.47</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>42.83</v>
+        <v>41.05</v>
       </c>
       <c r="K42" t="n">
-        <v>227.54</v>
+        <v>218.06</v>
       </c>
       <c r="L42" t="n">
-        <v>231.54</v>
+        <v>221.89</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>36.95</v>
+        <v>37.68</v>
       </c>
       <c r="K43" t="n">
-        <v>-295.61</v>
+        <v>-301.41</v>
       </c>
       <c r="L43" t="n">
-        <v>297.91</v>
+        <v>303.75</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-74.03</v>
+        <v>-75.48</v>
       </c>
       <c r="K44" t="n">
-        <v>-41.7</v>
+        <v>-42.52</v>
       </c>
       <c r="L44" t="n">
-        <v>84.95999999999999</v>
+        <v>86.63</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-41.88</v>
+        <v>-43.49</v>
       </c>
       <c r="K45" t="n">
-        <v>53.22</v>
+        <v>55.27</v>
       </c>
       <c r="L45" t="n">
-        <v>67.72</v>
+        <v>70.33</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>15.32</v>
+        <v>15.01</v>
       </c>
       <c r="K46" t="n">
-        <v>69.22</v>
+        <v>67.81</v>
       </c>
       <c r="L46" t="n">
-        <v>70.90000000000001</v>
+        <v>69.45</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-102.45</v>
+        <v>-104.46</v>
       </c>
       <c r="K47" t="n">
-        <v>-24.03</v>
+        <v>-24.5</v>
       </c>
       <c r="L47" t="n">
-        <v>105.23</v>
+        <v>107.29</v>
       </c>
     </row>
     <row r="48">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>27.28</v>
+        <v>28.83</v>
       </c>
       <c r="K49" t="n">
-        <v>-78.38</v>
+        <v>-82.81999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>83</v>
+        <v>87.69</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-70.84</v>
+        <v>-67.89</v>
       </c>
       <c r="K50" t="n">
-        <v>-71.79000000000001</v>
+        <v>-68.8</v>
       </c>
       <c r="L50" t="n">
-        <v>100.86</v>
+        <v>96.66</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>51.36</v>
+        <v>54.25</v>
       </c>
       <c r="K51" t="n">
-        <v>102.06</v>
+        <v>107.81</v>
       </c>
       <c r="L51" t="n">
-        <v>114.25</v>
+        <v>120.69</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>83</v>
+        <v>81.31</v>
       </c>
       <c r="K52" t="n">
-        <v>-47.19</v>
+        <v>-46.23</v>
       </c>
       <c r="L52" t="n">
-        <v>95.48</v>
+        <v>93.53</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>71.47</v>
+        <v>72.88</v>
       </c>
       <c r="K53" t="n">
-        <v>148.39</v>
+        <v>151.3</v>
       </c>
       <c r="L53" t="n">
-        <v>164.71</v>
+        <v>167.94</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>-11.25</v>
+        <v>-10.53</v>
       </c>
       <c r="K54" t="n">
-        <v>-168.65</v>
+        <v>-157.88</v>
       </c>
       <c r="L54" t="n">
-        <v>169.02</v>
+        <v>158.23</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>134.71</v>
+        <v>134.72</v>
       </c>
       <c r="K55" t="n">
-        <v>-72.34</v>
+        <v>-72.34999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>152.9</v>
+        <v>152.91</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>92.20999999999999</v>
+        <v>90.33</v>
       </c>
       <c r="K56" t="n">
-        <v>234.81</v>
+        <v>230.02</v>
       </c>
       <c r="L56" t="n">
-        <v>252.27</v>
+        <v>247.12</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>190.37</v>
+        <v>194.1</v>
       </c>
       <c r="K57" t="n">
-        <v>-90.28</v>
+        <v>-92.05</v>
       </c>
       <c r="L57" t="n">
-        <v>210.7</v>
+        <v>214.83</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>240.98</v>
+        <v>225.6</v>
       </c>
       <c r="K58" t="n">
-        <v>-134.89</v>
+        <v>-126.28</v>
       </c>
       <c r="L58" t="n">
-        <v>276.17</v>
+        <v>258.54</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-63.44</v>
+        <v>-67.03</v>
       </c>
       <c r="K59" t="n">
-        <v>59.14</v>
+        <v>62.49</v>
       </c>
       <c r="L59" t="n">
-        <v>86.73</v>
+        <v>91.64</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-63.04</v>
+        <v>-60.26</v>
       </c>
       <c r="K60" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="L60" t="n">
-        <v>63.13</v>
+        <v>60.34</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-30.47</v>
+        <v>-28.52</v>
       </c>
       <c r="K61" t="n">
-        <v>-47.37</v>
+        <v>-44.35</v>
       </c>
       <c r="L61" t="n">
-        <v>56.33</v>
+        <v>52.73</v>
       </c>
     </row>
     <row r="62">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-48.66</v>
+        <v>-46.63</v>
       </c>
       <c r="K63" t="n">
-        <v>-45.94</v>
+        <v>-44.03</v>
       </c>
       <c r="L63" t="n">
-        <v>66.92</v>
+        <v>64.13</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-61</v>
+        <v>-57.11</v>
       </c>
       <c r="K64" t="n">
-        <v>23.87</v>
+        <v>22.35</v>
       </c>
       <c r="L64" t="n">
-        <v>65.51000000000001</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.06</v>
       </c>
       <c r="K65" t="n">
-        <v>-135.57</v>
+        <v>-140.61</v>
       </c>
       <c r="L65" t="n">
-        <v>135.92</v>
+        <v>140.97</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>116.6</v>
+        <v>123.2</v>
       </c>
       <c r="K66" t="n">
-        <v>6.72</v>
+        <v>7.1</v>
       </c>
       <c r="L66" t="n">
-        <v>116.8</v>
+        <v>123.41</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>42.71</v>
+        <v>40.93</v>
       </c>
       <c r="K67" t="n">
-        <v>-92.79000000000001</v>
+        <v>-88.92</v>
       </c>
       <c r="L67" t="n">
-        <v>102.15</v>
+        <v>97.89</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>209.43</v>
+        <v>221.28</v>
       </c>
       <c r="K68" t="n">
-        <v>-73.52</v>
+        <v>-77.68000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>221.96</v>
+        <v>234.52</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-185.17</v>
+        <v>-188.8</v>
       </c>
       <c r="K69" t="n">
-        <v>-121.79</v>
+        <v>-124.17</v>
       </c>
       <c r="L69" t="n">
-        <v>221.63</v>
+        <v>225.98</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-48.64</v>
+        <v>-50.52</v>
       </c>
       <c r="K70" t="n">
-        <v>112.96</v>
+        <v>117.31</v>
       </c>
       <c r="L70" t="n">
-        <v>122.99</v>
+        <v>127.72</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>136.34</v>
+        <v>130.66</v>
       </c>
       <c r="K71" t="n">
-        <v>-80.08</v>
+        <v>-76.75</v>
       </c>
       <c r="L71" t="n">
-        <v>158.12</v>
+        <v>151.53</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>54.71</v>
+        <v>56.81</v>
       </c>
       <c r="K72" t="n">
-        <v>-323.4</v>
+        <v>-335.84</v>
       </c>
       <c r="L72" t="n">
-        <v>327.99</v>
+        <v>340.61</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-213.89</v>
+        <v>-204.98</v>
       </c>
       <c r="K73" t="n">
-        <v>-98.61</v>
+        <v>-94.51000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>235.53</v>
+        <v>225.71</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>31</v>
+        <v>32.2</v>
       </c>
       <c r="K74" t="n">
-        <v>42.42</v>
+        <v>44.05</v>
       </c>
       <c r="L74" t="n">
-        <v>52.54</v>
+        <v>54.56</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>-69.09</v>
+        <v>-66.20999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>14.58</v>
+        <v>13.98</v>
       </c>
       <c r="L75" t="n">
-        <v>70.61</v>
+        <v>67.67</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.78</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-59.06</v>
+        <v>-61.33</v>
       </c>
       <c r="L76" t="n">
-        <v>59.06</v>
+        <v>61.34</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>53.35</v>
+        <v>52.26</v>
       </c>
       <c r="K77" t="n">
-        <v>-52.14</v>
+        <v>-51.07</v>
       </c>
       <c r="L77" t="n">
-        <v>74.59</v>
+        <v>73.06999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-78.01000000000001</v>
+        <v>-79.54000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>-56.92</v>
+        <v>-58.04</v>
       </c>
       <c r="L78" t="n">
-        <v>96.56999999999999</v>
+        <v>98.45999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>58.43</v>
+        <v>59.58</v>
       </c>
       <c r="K79" t="n">
-        <v>57.31</v>
+        <v>58.44</v>
       </c>
       <c r="L79" t="n">
-        <v>81.84999999999999</v>
+        <v>83.45</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-50.36</v>
+        <v>-49.34</v>
       </c>
       <c r="K80" t="n">
-        <v>-86.54000000000001</v>
+        <v>-84.77</v>
       </c>
       <c r="L80" t="n">
-        <v>100.13</v>
+        <v>98.08</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>70.04000000000001</v>
+        <v>68.61</v>
       </c>
       <c r="K81" t="n">
-        <v>88.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>112.79</v>
+        <v>110.48</v>
       </c>
     </row>
     <row r="82">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-137.1</v>
+        <v>-131.41</v>
       </c>
       <c r="K83" t="n">
-        <v>-74.95</v>
+        <v>-71.84</v>
       </c>
       <c r="L83" t="n">
-        <v>156.25</v>
+        <v>149.77</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>148.93</v>
+        <v>145.89</v>
       </c>
       <c r="K84" t="n">
-        <v>104.44</v>
+        <v>102.3</v>
       </c>
       <c r="L84" t="n">
-        <v>181.9</v>
+        <v>178.19</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>92.20999999999999</v>
+        <v>97.42</v>
       </c>
       <c r="K85" t="n">
-        <v>-48.21</v>
+        <v>-50.94</v>
       </c>
       <c r="L85" t="n">
-        <v>104.05</v>
+        <v>109.94</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-35.06</v>
+        <v>-36.41</v>
       </c>
       <c r="K86" t="n">
-        <v>163.01</v>
+        <v>169.28</v>
       </c>
       <c r="L86" t="n">
-        <v>166.74</v>
+        <v>173.15</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>61.13</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>-241.54</v>
+        <v>-255.21</v>
       </c>
       <c r="L87" t="n">
-        <v>249.16</v>
+        <v>263.26</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-109.34</v>
+        <v>-115.52</v>
       </c>
       <c r="K88" t="n">
-        <v>-196.48</v>
+        <v>-207.61</v>
       </c>
       <c r="L88" t="n">
-        <v>224.86</v>
+        <v>237.58</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-03.xlsx
+++ b/output/2024-10-03.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="F14" t="n">
-        <v>3.74</v>
+        <v>5.65</v>
       </c>
       <c r="G14" t="n">
-        <v>182.3</v>
+        <v>170.2</v>
       </c>
       <c r="H14" t="n">
-        <v>77.59999999999999</v>
+        <v>28.9</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>23.88</v>
+        <v>29.5</v>
       </c>
       <c r="K14" t="n">
-        <v>47.35</v>
+        <v>-22.28</v>
       </c>
       <c r="L14" t="n">
-        <v>53.04</v>
+        <v>36.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:23:02</t>
+          <t>07:23:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -670,31 +670,31 @@
         <v>2.49</v>
       </c>
       <c r="F15" t="n">
-        <v>7.93</v>
+        <v>5.14</v>
       </c>
       <c r="G15" t="n">
-        <v>177.4</v>
+        <v>184.3</v>
       </c>
       <c r="H15" t="n">
-        <v>82.59999999999999</v>
+        <v>46.2</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.61</v>
+        <v>-20.11</v>
       </c>
       <c r="K15" t="n">
-        <v>-72.89</v>
+        <v>-19.19</v>
       </c>
       <c r="L15" t="n">
-        <v>74.14</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:24:38</t>
+          <t>07:25:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.56</v>
+        <v>1.7</v>
       </c>
       <c r="F16" t="n">
-        <v>2.86</v>
+        <v>3.46</v>
       </c>
       <c r="G16" t="n">
-        <v>191.7</v>
+        <v>183.1</v>
       </c>
       <c r="H16" t="n">
-        <v>84.5</v>
+        <v>35.1</v>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.869999999999999</v>
+        <v>-40.06</v>
       </c>
       <c r="K16" t="n">
-        <v>-26.45</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>28.23</v>
+        <v>41.22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:29:48</t>
+          <t>07:29:24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="F17" t="n">
-        <v>5.48</v>
+        <v>4.73</v>
       </c>
       <c r="G17" t="n">
-        <v>172.6</v>
+        <v>175.3</v>
       </c>
       <c r="H17" t="n">
-        <v>91.7</v>
+        <v>44.8</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>47.68</v>
+        <v>33.27</v>
       </c>
       <c r="K17" t="n">
-        <v>-61.94</v>
+        <v>-51.35</v>
       </c>
       <c r="L17" t="n">
-        <v>78.17</v>
+        <v>61.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:32:13</t>
+          <t>07:30:09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.81</v>
+        <v>2.51</v>
       </c>
       <c r="F18" t="n">
-        <v>4.79</v>
+        <v>7.93</v>
       </c>
       <c r="G18" t="n">
-        <v>182.8</v>
+        <v>159.6</v>
       </c>
       <c r="H18" t="n">
-        <v>80.40000000000001</v>
+        <v>55</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J18" t="n">
-        <v>31.49</v>
+        <v>31.18</v>
       </c>
       <c r="K18" t="n">
-        <v>51.9</v>
+        <v>34.72</v>
       </c>
       <c r="L18" t="n">
-        <v>60.71</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:33:39</t>
+          <t>07:30:58</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.15</v>
+        <v>2.57</v>
       </c>
       <c r="F19" t="n">
-        <v>5.89</v>
+        <v>7.19</v>
       </c>
       <c r="G19" t="n">
-        <v>178.8</v>
+        <v>169.1</v>
       </c>
       <c r="H19" t="n">
-        <v>80.3</v>
+        <v>57.4</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J19" t="n">
-        <v>64.33</v>
+        <v>15.95</v>
       </c>
       <c r="K19" t="n">
-        <v>41.1</v>
+        <v>-69.23</v>
       </c>
       <c r="L19" t="n">
-        <v>76.34</v>
+        <v>71.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:36:24</t>
+          <t>07:36:50</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="F20" t="n">
-        <v>5.21</v>
+        <v>6.49</v>
       </c>
       <c r="G20" t="n">
-        <v>181.4</v>
+        <v>198</v>
       </c>
       <c r="H20" t="n">
-        <v>84.3</v>
+        <v>39.3</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J20" t="n">
-        <v>-72.7</v>
+        <v>-77.59999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-61.15</v>
+        <v>18.66</v>
       </c>
       <c r="L20" t="n">
-        <v>95</v>
+        <v>79.81999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:37:52</t>
+          <t>07:38:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="F21" t="n">
-        <v>4.99</v>
+        <v>7.93</v>
       </c>
       <c r="G21" t="n">
-        <v>180</v>
+        <v>183.3</v>
       </c>
       <c r="H21" t="n">
-        <v>85.40000000000001</v>
+        <v>36.8</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>-50.98</v>
+        <v>-4.93</v>
       </c>
       <c r="K21" t="n">
-        <v>-109.31</v>
+        <v>-38.91</v>
       </c>
       <c r="L21" t="n">
-        <v>120.61</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:39:48</t>
+          <t>07:41:05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="F22" t="n">
-        <v>7.93</v>
+        <v>5.09</v>
       </c>
       <c r="G22" t="n">
-        <v>162.1</v>
+        <v>186.6</v>
       </c>
       <c r="H22" t="n">
-        <v>89.8</v>
+        <v>45.9</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>80.98</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>18.66</v>
+        <v>-10.07</v>
       </c>
       <c r="L22" t="n">
-        <v>83.11</v>
+        <v>79.88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:43:36</t>
+          <t>07:46:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="F23" t="n">
-        <v>6.49</v>
+        <v>5.71</v>
       </c>
       <c r="G23" t="n">
-        <v>166.5</v>
+        <v>173.8</v>
       </c>
       <c r="H23" t="n">
-        <v>79.5</v>
+        <v>46.2</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J23" t="n">
-        <v>-127.84</v>
+        <v>14.99</v>
       </c>
       <c r="K23" t="n">
-        <v>115.45</v>
+        <v>-229.7</v>
       </c>
       <c r="L23" t="n">
-        <v>172.26</v>
+        <v>230.18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:46:12</t>
+          <t>07:48:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="F24" t="n">
-        <v>4.06</v>
+        <v>4.82</v>
       </c>
       <c r="G24" t="n">
         <v>179.7</v>
       </c>
       <c r="H24" t="n">
-        <v>81.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>87.92</v>
+        <v>6.56</v>
       </c>
       <c r="K24" t="n">
-        <v>74.98</v>
+        <v>-118.65</v>
       </c>
       <c r="L24" t="n">
-        <v>115.55</v>
+        <v>118.83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:48:02</t>
+          <t>07:50:38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="F25" t="n">
         <v>7.93</v>
       </c>
       <c r="G25" t="n">
-        <v>174.9</v>
+        <v>196.7</v>
       </c>
       <c r="H25" t="n">
-        <v>82</v>
+        <v>69.2</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>-130.38</v>
+        <v>112.89</v>
       </c>
       <c r="K25" t="n">
-        <v>-143.08</v>
+        <v>-76.84</v>
       </c>
       <c r="L25" t="n">
-        <v>193.57</v>
+        <v>136.56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:53:39</t>
+          <t>07:55:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.01</v>
+        <v>2.31</v>
       </c>
       <c r="F26" t="n">
-        <v>6.76</v>
+        <v>3.7</v>
       </c>
       <c r="G26" t="n">
-        <v>176.8</v>
+        <v>176.7</v>
       </c>
       <c r="H26" t="n">
-        <v>81.90000000000001</v>
+        <v>49.8</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-214.7</v>
+        <v>168.43</v>
       </c>
       <c r="K26" t="n">
-        <v>-60.76</v>
+        <v>40.61</v>
       </c>
       <c r="L26" t="n">
-        <v>223.14</v>
+        <v>173.26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:55:27</t>
+          <t>07:56:54</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="F27" t="n">
-        <v>7.93</v>
+        <v>7.33</v>
       </c>
       <c r="G27" t="n">
-        <v>174.8</v>
+        <v>183.7</v>
       </c>
       <c r="H27" t="n">
-        <v>79.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>159.14</v>
+        <v>-159.77</v>
       </c>
       <c r="K27" t="n">
-        <v>-98.73</v>
+        <v>96.48</v>
       </c>
       <c r="L27" t="n">
-        <v>187.28</v>
+        <v>186.64</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:56:15</t>
+          <t>07:58:02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.03</v>
+        <v>2.27</v>
       </c>
       <c r="F28" t="n">
-        <v>7.71</v>
+        <v>2.78</v>
       </c>
       <c r="G28" t="n">
-        <v>175.3</v>
+        <v>169.6</v>
       </c>
       <c r="H28" t="n">
-        <v>80.40000000000001</v>
+        <v>41.2</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J28" t="n">
-        <v>181.93</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>35.16</v>
+        <v>-126.59</v>
       </c>
       <c r="L28" t="n">
-        <v>185.29</v>
+        <v>150.33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:03:24</t>
+          <t>08:08:44</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="F29" t="n">
-        <v>7.12</v>
+        <v>7.93</v>
       </c>
       <c r="G29" t="n">
-        <v>185.4</v>
+        <v>192.4</v>
       </c>
       <c r="H29" t="n">
-        <v>81.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>60.96</v>
+        <v>-44.05</v>
       </c>
       <c r="K29" t="n">
-        <v>1.28</v>
+        <v>-2.51</v>
       </c>
       <c r="L29" t="n">
-        <v>60.97</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:05:18</t>
+          <t>08:10:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="F30" t="n">
-        <v>7.03</v>
+        <v>4.82</v>
       </c>
       <c r="G30" t="n">
-        <v>180</v>
+        <v>178.3</v>
       </c>
       <c r="H30" t="n">
-        <v>85.40000000000001</v>
+        <v>45.2</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J30" t="n">
-        <v>-13.84</v>
+        <v>36.16</v>
       </c>
       <c r="K30" t="n">
-        <v>-51.32</v>
+        <v>14.99</v>
       </c>
       <c r="L30" t="n">
-        <v>53.15</v>
+        <v>39.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:06:53</t>
+          <t>08:11:55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="F31" t="n">
-        <v>6.37</v>
+        <v>6.03</v>
       </c>
       <c r="G31" t="n">
-        <v>187</v>
+        <v>181.9</v>
       </c>
       <c r="H31" t="n">
-        <v>76.90000000000001</v>
+        <v>22</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.15</v>
+        <v>-25.8</v>
       </c>
       <c r="K31" t="n">
-        <v>-43.8</v>
+        <v>-40.13</v>
       </c>
       <c r="L31" t="n">
-        <v>44.75</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:12:39</t>
+          <t>08:15:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="F32" t="n">
-        <v>7.89</v>
+        <v>5.03</v>
       </c>
       <c r="G32" t="n">
-        <v>180.8</v>
+        <v>182.4</v>
       </c>
       <c r="H32" t="n">
-        <v>89.90000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>22.94</v>
+        <v>-54.34</v>
       </c>
       <c r="K32" t="n">
-        <v>93.68000000000001</v>
+        <v>27.3</v>
       </c>
       <c r="L32" t="n">
-        <v>96.45</v>
+        <v>60.81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:14:54</t>
+          <t>08:16:11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="F33" t="n">
-        <v>4.48</v>
+        <v>7.69</v>
       </c>
       <c r="G33" t="n">
-        <v>172.2</v>
+        <v>181.3</v>
       </c>
       <c r="H33" t="n">
-        <v>81.40000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J33" t="n">
-        <v>13.09</v>
+        <v>42.12</v>
       </c>
       <c r="K33" t="n">
-        <v>-76.79000000000001</v>
+        <v>-46.4</v>
       </c>
       <c r="L33" t="n">
-        <v>77.90000000000001</v>
+        <v>62.66</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:16:50</t>
+          <t>08:17:36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.61</v>
+        <v>3.08</v>
       </c>
       <c r="F34" t="n">
-        <v>7.85</v>
+        <v>7.93</v>
       </c>
       <c r="G34" t="n">
-        <v>180.6</v>
+        <v>153.2</v>
       </c>
       <c r="H34" t="n">
-        <v>83.40000000000001</v>
+        <v>15.9</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>70.78</v>
+        <v>45.14</v>
       </c>
       <c r="K34" t="n">
-        <v>-9.109999999999999</v>
+        <v>30.89</v>
       </c>
       <c r="L34" t="n">
-        <v>71.37</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:22:35</t>
+          <t>08:22:55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.13</v>
+        <v>2.76</v>
       </c>
       <c r="F35" t="n">
-        <v>4.09</v>
+        <v>5.72</v>
       </c>
       <c r="G35" t="n">
-        <v>188.3</v>
+        <v>176.7</v>
       </c>
       <c r="H35" t="n">
-        <v>84</v>
+        <v>69.8</v>
       </c>
       <c r="I35" t="n">
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-67.59</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-103.92</v>
+        <v>2.91</v>
       </c>
       <c r="L35" t="n">
-        <v>123.96</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:24:54</t>
+          <t>08:24:51</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.67</v>
+        <v>2.93</v>
       </c>
       <c r="F36" t="n">
-        <v>5.05</v>
+        <v>6.9</v>
       </c>
       <c r="G36" t="n">
-        <v>182.4</v>
+        <v>180.5</v>
       </c>
       <c r="H36" t="n">
-        <v>82.40000000000001</v>
+        <v>44.5</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-97.06999999999999</v>
+        <v>-138.23</v>
       </c>
       <c r="K36" t="n">
-        <v>-78.34999999999999</v>
+        <v>48.74</v>
       </c>
       <c r="L36" t="n">
-        <v>124.74</v>
+        <v>146.57</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:26:37</t>
+          <t>08:26:45</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="F37" t="n">
-        <v>6.13</v>
+        <v>7.93</v>
       </c>
       <c r="G37" t="n">
-        <v>169.9</v>
+        <v>168.6</v>
       </c>
       <c r="H37" t="n">
-        <v>91.5</v>
+        <v>22.7</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>68.33</v>
+        <v>63.48</v>
       </c>
       <c r="K37" t="n">
-        <v>80.72</v>
+        <v>7.61</v>
       </c>
       <c r="L37" t="n">
-        <v>105.76</v>
+        <v>63.93</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:31:34</t>
+          <t>08:30:57</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.71</v>
+        <v>2.35</v>
       </c>
       <c r="F38" t="n">
-        <v>7.59</v>
+        <v>7.02</v>
       </c>
       <c r="G38" t="n">
-        <v>178.4</v>
+        <v>175.2</v>
       </c>
       <c r="H38" t="n">
-        <v>74.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J38" t="n">
-        <v>146.38</v>
+        <v>22.13</v>
       </c>
       <c r="K38" t="n">
-        <v>71.76000000000001</v>
+        <v>102.23</v>
       </c>
       <c r="L38" t="n">
-        <v>163.02</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:33:47</t>
+          <t>08:32:54</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.27</v>
+        <v>2.9</v>
       </c>
       <c r="F39" t="n">
-        <v>7.43</v>
+        <v>7.93</v>
       </c>
       <c r="G39" t="n">
-        <v>188.7</v>
+        <v>182</v>
       </c>
       <c r="H39" t="n">
-        <v>82.2</v>
+        <v>87.7</v>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>59.9</v>
+        <v>188.8</v>
       </c>
       <c r="K39" t="n">
-        <v>125.68</v>
+        <v>-11.38</v>
       </c>
       <c r="L39" t="n">
-        <v>139.22</v>
+        <v>189.14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:36:11</t>
+          <t>08:34:50</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="F40" t="n">
-        <v>7.01</v>
+        <v>7.93</v>
       </c>
       <c r="G40" t="n">
-        <v>171.1</v>
+        <v>188.1</v>
       </c>
       <c r="H40" t="n">
-        <v>79.40000000000001</v>
+        <v>39.7</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>-64.34999999999999</v>
+        <v>-131.26</v>
       </c>
       <c r="K40" t="n">
-        <v>-194.42</v>
+        <v>15.07</v>
       </c>
       <c r="L40" t="n">
-        <v>204.79</v>
+        <v>132.12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:41:30</t>
+          <t>08:39:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.68</v>
+        <v>2.31</v>
       </c>
       <c r="F41" t="n">
-        <v>5.18</v>
+        <v>6.65</v>
       </c>
       <c r="G41" t="n">
-        <v>177.8</v>
+        <v>180</v>
       </c>
       <c r="H41" t="n">
-        <v>85.59999999999999</v>
+        <v>56.2</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>103.81</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>132.69</v>
+        <v>189.04</v>
       </c>
       <c r="L41" t="n">
-        <v>168.47</v>
+        <v>201.35</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:43:42</t>
+          <t>08:40:56</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.14</v>
+        <v>2.57</v>
       </c>
       <c r="F42" t="n">
-        <v>6.71</v>
+        <v>6.92</v>
       </c>
       <c r="G42" t="n">
-        <v>179.7</v>
+        <v>186.8</v>
       </c>
       <c r="H42" t="n">
-        <v>85.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="I42" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J42" t="n">
-        <v>41.05</v>
+        <v>163.25</v>
       </c>
       <c r="K42" t="n">
-        <v>218.06</v>
+        <v>23.63</v>
       </c>
       <c r="L42" t="n">
-        <v>221.89</v>
+        <v>164.95</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:44:54</t>
+          <t>08:43:05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="F43" t="n">
-        <v>7.74</v>
+        <v>5.33</v>
       </c>
       <c r="G43" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="H43" t="n">
-        <v>75.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>37.68</v>
+        <v>82.52</v>
       </c>
       <c r="K43" t="n">
-        <v>-301.41</v>
+        <v>-97.36</v>
       </c>
       <c r="L43" t="n">
-        <v>303.75</v>
+        <v>127.63</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:55:00</t>
+          <t>08:53:01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="F44" t="n">
-        <v>7.03</v>
+        <v>7.93</v>
       </c>
       <c r="G44" t="n">
-        <v>182.2</v>
+        <v>192.4</v>
       </c>
       <c r="H44" t="n">
-        <v>82.7</v>
+        <v>69.8</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>-75.48</v>
+        <v>-3.95</v>
       </c>
       <c r="K44" t="n">
-        <v>-42.52</v>
+        <v>42.05</v>
       </c>
       <c r="L44" t="n">
-        <v>86.63</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:57:28</t>
+          <t>08:54:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.61</v>
+        <v>3.09</v>
       </c>
       <c r="F45" t="n">
         <v>7.93</v>
       </c>
       <c r="G45" t="n">
-        <v>175.9</v>
+        <v>176.7</v>
       </c>
       <c r="H45" t="n">
-        <v>78.09999999999999</v>
+        <v>31.5</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>-43.49</v>
+        <v>-42.28</v>
       </c>
       <c r="K45" t="n">
-        <v>55.27</v>
+        <v>-32.35</v>
       </c>
       <c r="L45" t="n">
-        <v>70.33</v>
+        <v>53.24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:58:31</t>
+          <t>08:56:31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="F46" t="n">
         <v>7.93</v>
       </c>
       <c r="G46" t="n">
-        <v>173.4</v>
+        <v>178.6</v>
       </c>
       <c r="H46" t="n">
-        <v>87.5</v>
+        <v>47.5</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>15.01</v>
+        <v>-15.02</v>
       </c>
       <c r="K46" t="n">
-        <v>67.81</v>
+        <v>-43.69</v>
       </c>
       <c r="L46" t="n">
-        <v>69.45</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:02:50</t>
+          <t>09:00:59</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="F47" t="n">
-        <v>7.9</v>
+        <v>7.93</v>
       </c>
       <c r="G47" t="n">
-        <v>176</v>
+        <v>175.1</v>
       </c>
       <c r="H47" t="n">
-        <v>78.7</v>
+        <v>33.4</v>
       </c>
       <c r="I47" t="n">
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-104.46</v>
+        <v>-6.93</v>
       </c>
       <c r="K47" t="n">
-        <v>-24.5</v>
+        <v>-50.64</v>
       </c>
       <c r="L47" t="n">
-        <v>107.29</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:03:56</t>
+          <t>09:02:45</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="F48" t="n">
-        <v>7.93</v>
+        <v>7.87</v>
       </c>
       <c r="G48" t="n">
-        <v>170.3</v>
+        <v>165.9</v>
       </c>
       <c r="H48" t="n">
-        <v>78</v>
+        <v>43.7</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J48" t="n">
-        <v>101.24</v>
+        <v>-3.33</v>
       </c>
       <c r="K48" t="n">
-        <v>-38.32</v>
+        <v>6.23</v>
       </c>
       <c r="L48" t="n">
-        <v>108.24</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:06:11</t>
+          <t>09:03:18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.34</v>
+        <v>2.79</v>
       </c>
       <c r="F49" t="n">
-        <v>7.75</v>
+        <v>7.93</v>
       </c>
       <c r="G49" t="n">
-        <v>178.2</v>
+        <v>184</v>
       </c>
       <c r="H49" t="n">
-        <v>87.3</v>
+        <v>57.3</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>28.83</v>
+        <v>-63.64</v>
       </c>
       <c r="K49" t="n">
-        <v>-82.81999999999999</v>
+        <v>14.58</v>
       </c>
       <c r="L49" t="n">
-        <v>87.69</v>
+        <v>65.29000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:10:00</t>
+          <t>09:08:03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="F50" t="n">
-        <v>7.93</v>
+        <v>5.92</v>
       </c>
       <c r="G50" t="n">
-        <v>181.1</v>
+        <v>168.8</v>
       </c>
       <c r="H50" t="n">
-        <v>78.40000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>-67.89</v>
+        <v>98.42</v>
       </c>
       <c r="K50" t="n">
-        <v>-68.8</v>
+        <v>-6.23</v>
       </c>
       <c r="L50" t="n">
-        <v>96.66</v>
+        <v>98.62</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:11:35</t>
+          <t>09:09:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.4</v>
+        <v>2.41</v>
       </c>
       <c r="F51" t="n">
-        <v>7.87</v>
+        <v>7.93</v>
       </c>
       <c r="G51" t="n">
-        <v>176.3</v>
+        <v>184.5</v>
       </c>
       <c r="H51" t="n">
-        <v>76.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J51" t="n">
-        <v>54.25</v>
+        <v>-82.48999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>107.81</v>
+        <v>-5.59</v>
       </c>
       <c r="L51" t="n">
-        <v>120.69</v>
+        <v>82.68000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:13:43</t>
+          <t>09:11:37</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="F52" t="n">
-        <v>7.18</v>
+        <v>7.65</v>
       </c>
       <c r="G52" t="n">
-        <v>180.8</v>
+        <v>171.3</v>
       </c>
       <c r="H52" t="n">
-        <v>79.59999999999999</v>
+        <v>59.3</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>81.31</v>
+        <v>55.53</v>
       </c>
       <c r="K52" t="n">
-        <v>-46.23</v>
+        <v>-7.54</v>
       </c>
       <c r="L52" t="n">
-        <v>93.53</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:17:48</t>
+          <t>09:16:44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="F53" t="n">
-        <v>7.57</v>
+        <v>7.93</v>
       </c>
       <c r="G53" t="n">
-        <v>164</v>
+        <v>165.8</v>
       </c>
       <c r="H53" t="n">
-        <v>78.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>72.88</v>
+        <v>-24.83</v>
       </c>
       <c r="K53" t="n">
-        <v>151.3</v>
+        <v>-149.18</v>
       </c>
       <c r="L53" t="n">
-        <v>167.94</v>
+        <v>151.24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:19:03</t>
+          <t>09:18:59</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="F54" t="n">
-        <v>7.11</v>
+        <v>4.29</v>
       </c>
       <c r="G54" t="n">
-        <v>170.8</v>
+        <v>182.5</v>
       </c>
       <c r="H54" t="n">
-        <v>82</v>
+        <v>49.3</v>
       </c>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>-10.53</v>
+        <v>-68.20999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-157.88</v>
+        <v>-74.67</v>
       </c>
       <c r="L54" t="n">
-        <v>158.23</v>
+        <v>101.14</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:20:35</t>
+          <t>09:21:49</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="F55" t="n">
         <v>7.93</v>
       </c>
       <c r="G55" t="n">
-        <v>185.4</v>
+        <v>167.8</v>
       </c>
       <c r="H55" t="n">
-        <v>85</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>134.72</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>-72.34999999999999</v>
+        <v>-205.29</v>
       </c>
       <c r="L55" t="n">
-        <v>152.91</v>
+        <v>219.37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:23:52</t>
+          <t>09:26:11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="F56" t="n">
-        <v>6.9</v>
+        <v>7.93</v>
       </c>
       <c r="G56" t="n">
-        <v>181.6</v>
+        <v>183.9</v>
       </c>
       <c r="H56" t="n">
-        <v>84.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>90.33</v>
+        <v>-164.54</v>
       </c>
       <c r="K56" t="n">
-        <v>230.02</v>
+        <v>-62.56</v>
       </c>
       <c r="L56" t="n">
-        <v>247.12</v>
+        <v>176.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:25:18</t>
+          <t>09:28:17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="F57" t="n">
-        <v>7.93</v>
+        <v>7.3</v>
       </c>
       <c r="G57" t="n">
-        <v>193.7</v>
+        <v>157.8</v>
       </c>
       <c r="H57" t="n">
-        <v>78.7</v>
+        <v>33.2</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>194.1</v>
+        <v>153.4</v>
       </c>
       <c r="K57" t="n">
-        <v>-92.05</v>
+        <v>-44.81</v>
       </c>
       <c r="L57" t="n">
-        <v>214.83</v>
+        <v>159.81</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:27:10</t>
+          <t>09:30:04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="F58" t="n">
-        <v>7.93</v>
+        <v>7.31</v>
       </c>
       <c r="G58" t="n">
-        <v>166.1</v>
+        <v>182.1</v>
       </c>
       <c r="H58" t="n">
-        <v>77.3</v>
+        <v>95.7</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J58" t="n">
-        <v>225.6</v>
+        <v>268.93</v>
       </c>
       <c r="K58" t="n">
-        <v>-126.28</v>
+        <v>-98.31</v>
       </c>
       <c r="L58" t="n">
-        <v>258.54</v>
+        <v>286.34</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:36:54</t>
+          <t>09:42:39</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.03</v>
+        <v>3.57</v>
       </c>
       <c r="F59" t="n">
         <v>7.93</v>
       </c>
       <c r="G59" t="n">
-        <v>181.7</v>
+        <v>174.2</v>
       </c>
       <c r="H59" t="n">
-        <v>81.8</v>
+        <v>50</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>-67.03</v>
+        <v>56.86</v>
       </c>
       <c r="K59" t="n">
-        <v>62.49</v>
+        <v>15.43</v>
       </c>
       <c r="L59" t="n">
-        <v>91.64</v>
+        <v>58.92</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:38:32</t>
+          <t>09:43:56</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.78</v>
+        <v>2.9</v>
       </c>
       <c r="F60" t="n">
-        <v>7.93</v>
+        <v>6.42</v>
       </c>
       <c r="G60" t="n">
-        <v>166</v>
+        <v>176.2</v>
       </c>
       <c r="H60" t="n">
-        <v>84.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J60" t="n">
-        <v>-60.26</v>
+        <v>-34.31</v>
       </c>
       <c r="K60" t="n">
-        <v>3.11</v>
+        <v>40.14</v>
       </c>
       <c r="L60" t="n">
-        <v>60.34</v>
+        <v>52.81</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:40:39</t>
+          <t>09:44:56</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.61</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>3.61</v>
+        <v>7.49</v>
       </c>
       <c r="G61" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="H61" t="n">
-        <v>73.3</v>
+        <v>98.7</v>
       </c>
       <c r="I61" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-28.52</v>
+        <v>2.96</v>
       </c>
       <c r="K61" t="n">
-        <v>-44.35</v>
+        <v>46.73</v>
       </c>
       <c r="L61" t="n">
-        <v>52.73</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:44:43</t>
+          <t>09:49:52</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.81</v>
+        <v>3.09</v>
       </c>
       <c r="F62" t="n">
-        <v>7.93</v>
+        <v>7.7</v>
       </c>
       <c r="G62" t="n">
-        <v>176.8</v>
+        <v>173.5</v>
       </c>
       <c r="H62" t="n">
-        <v>78.40000000000001</v>
+        <v>31.1</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.46</v>
+        <v>84.42</v>
       </c>
       <c r="K62" t="n">
-        <v>93.83</v>
+        <v>35.04</v>
       </c>
       <c r="L62" t="n">
-        <v>93.83</v>
+        <v>91.41</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:46:57</t>
+          <t>09:50:39</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.87</v>
+        <v>3.09</v>
       </c>
       <c r="F63" t="n">
-        <v>6.93</v>
+        <v>7.93</v>
       </c>
       <c r="G63" t="n">
-        <v>177.8</v>
+        <v>169.7</v>
       </c>
       <c r="H63" t="n">
-        <v>81.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-46.63</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-44.03</v>
+        <v>-6.91</v>
       </c>
       <c r="L63" t="n">
-        <v>64.13</v>
+        <v>70.41</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:49:28</t>
+          <t>09:52:44</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.73</v>
+        <v>2.38</v>
       </c>
       <c r="F64" t="n">
-        <v>7.81</v>
+        <v>5.54</v>
       </c>
       <c r="G64" t="n">
-        <v>189.6</v>
+        <v>173.1</v>
       </c>
       <c r="H64" t="n">
-        <v>81</v>
+        <v>53.5</v>
       </c>
       <c r="I64" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-57.11</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>22.35</v>
+        <v>-11.11</v>
       </c>
       <c r="L64" t="n">
-        <v>61.32</v>
+        <v>67.52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:53:48</t>
+          <t>09:57:22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.99</v>
+        <v>2.92</v>
       </c>
       <c r="F65" t="n">
         <v>7.93</v>
       </c>
       <c r="G65" t="n">
-        <v>189.2</v>
+        <v>185.3</v>
       </c>
       <c r="H65" t="n">
-        <v>83.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.06</v>
+        <v>24.37</v>
       </c>
       <c r="K65" t="n">
-        <v>-140.61</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>140.97</v>
+        <v>70.73</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:54:45</t>
+          <t>09:59:17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="F66" t="n">
-        <v>7.93</v>
+        <v>6.68</v>
       </c>
       <c r="G66" t="n">
-        <v>191.7</v>
+        <v>184.5</v>
       </c>
       <c r="H66" t="n">
-        <v>81.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>123.2</v>
+        <v>-32.45</v>
       </c>
       <c r="K66" t="n">
-        <v>7.1</v>
+        <v>-49.69</v>
       </c>
       <c r="L66" t="n">
-        <v>123.41</v>
+        <v>59.35</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:56:11</t>
+          <t>10:00:22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="F67" t="n">
-        <v>7.93</v>
+        <v>6.91</v>
       </c>
       <c r="G67" t="n">
-        <v>171.8</v>
+        <v>178.8</v>
       </c>
       <c r="H67" t="n">
-        <v>82.40000000000001</v>
+        <v>39.1</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>40.93</v>
+        <v>10.91</v>
       </c>
       <c r="K67" t="n">
-        <v>-88.92</v>
+        <v>-101.16</v>
       </c>
       <c r="L67" t="n">
-        <v>97.89</v>
+        <v>101.75</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:01:56</t>
+          <t>10:04:37</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="F68" t="n">
-        <v>7.72</v>
+        <v>7.93</v>
       </c>
       <c r="G68" t="n">
-        <v>191.5</v>
+        <v>194.8</v>
       </c>
       <c r="H68" t="n">
-        <v>82.5</v>
+        <v>53.4</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J68" t="n">
-        <v>221.28</v>
+        <v>-87.58</v>
       </c>
       <c r="K68" t="n">
-        <v>-77.68000000000001</v>
+        <v>-92.93000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>234.52</v>
+        <v>127.69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:04:33</t>
+          <t>10:06:45</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.04</v>
+        <v>3.9</v>
       </c>
       <c r="F69" t="n">
-        <v>7.58</v>
+        <v>7.93</v>
       </c>
       <c r="G69" t="n">
-        <v>159.7</v>
+        <v>176.2</v>
       </c>
       <c r="H69" t="n">
-        <v>79.40000000000001</v>
+        <v>55.3</v>
       </c>
       <c r="I69" t="n">
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-188.8</v>
+        <v>137.65</v>
       </c>
       <c r="K69" t="n">
-        <v>-124.17</v>
+        <v>-124.71</v>
       </c>
       <c r="L69" t="n">
-        <v>225.98</v>
+        <v>185.74</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:06:46</t>
+          <t>10:09:15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="F70" t="n">
-        <v>4.24</v>
+        <v>7.93</v>
       </c>
       <c r="G70" t="n">
-        <v>162.6</v>
+        <v>166.9</v>
       </c>
       <c r="H70" t="n">
-        <v>87.3</v>
+        <v>59</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-50.52</v>
+        <v>84.16</v>
       </c>
       <c r="K70" t="n">
-        <v>117.31</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>127.72</v>
+        <v>122.13</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:11:44</t>
+          <t>10:14:33</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3022,31 +3022,31 @@
         <v>2.96</v>
       </c>
       <c r="F71" t="n">
-        <v>7.7</v>
+        <v>7.93</v>
       </c>
       <c r="G71" t="n">
-        <v>185.8</v>
+        <v>168.5</v>
       </c>
       <c r="H71" t="n">
-        <v>84.2</v>
+        <v>77</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>130.66</v>
+        <v>152.48</v>
       </c>
       <c r="K71" t="n">
-        <v>-76.75</v>
+        <v>72.31</v>
       </c>
       <c r="L71" t="n">
-        <v>151.53</v>
+        <v>168.75</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:13:36</t>
+          <t>10:16:09</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="F72" t="n">
-        <v>7.93</v>
+        <v>6.66</v>
       </c>
       <c r="G72" t="n">
-        <v>174.7</v>
+        <v>168.9</v>
       </c>
       <c r="H72" t="n">
-        <v>81.5</v>
+        <v>61.5</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>56.81</v>
+        <v>-158.38</v>
       </c>
       <c r="K72" t="n">
-        <v>-335.84</v>
+        <v>90.25</v>
       </c>
       <c r="L72" t="n">
-        <v>340.61</v>
+        <v>182.29</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:14:44</t>
+          <t>10:17:26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="F73" t="n">
-        <v>7.17</v>
+        <v>7.93</v>
       </c>
       <c r="G73" t="n">
-        <v>180.3</v>
+        <v>172.5</v>
       </c>
       <c r="H73" t="n">
-        <v>90.90000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J73" t="n">
-        <v>-204.98</v>
+        <v>148.24</v>
       </c>
       <c r="K73" t="n">
-        <v>-94.51000000000001</v>
+        <v>13.99</v>
       </c>
       <c r="L73" t="n">
-        <v>225.71</v>
+        <v>148.9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:26:36</t>
+          <t>10:30:23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="F74" t="n">
-        <v>7.24</v>
+        <v>7.93</v>
       </c>
       <c r="G74" t="n">
-        <v>168.9</v>
+        <v>175.2</v>
       </c>
       <c r="H74" t="n">
-        <v>87.2</v>
+        <v>76.7</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>32.2</v>
+        <v>-30.53</v>
       </c>
       <c r="K74" t="n">
-        <v>44.05</v>
+        <v>-20.7</v>
       </c>
       <c r="L74" t="n">
-        <v>54.56</v>
+        <v>36.88</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:27:43</t>
+          <t>10:31:48</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="F75" t="n">
-        <v>7.93</v>
+        <v>4.95</v>
       </c>
       <c r="G75" t="n">
-        <v>183.4</v>
+        <v>179.6</v>
       </c>
       <c r="H75" t="n">
-        <v>86</v>
+        <v>71.8</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-66.20999999999999</v>
+        <v>1.75</v>
       </c>
       <c r="K75" t="n">
-        <v>13.98</v>
+        <v>-53.11</v>
       </c>
       <c r="L75" t="n">
-        <v>67.67</v>
+        <v>53.13</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:28:52</t>
+          <t>10:33:37</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.22</v>
+        <v>2.75</v>
       </c>
       <c r="F76" t="n">
-        <v>7.93</v>
+        <v>7.03</v>
       </c>
       <c r="G76" t="n">
-        <v>172.6</v>
+        <v>181.2</v>
       </c>
       <c r="H76" t="n">
-        <v>91.09999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.8100000000000001</v>
+        <v>12.94</v>
       </c>
       <c r="K76" t="n">
-        <v>-61.33</v>
+        <v>37.64</v>
       </c>
       <c r="L76" t="n">
-        <v>61.34</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:34:47</t>
+          <t>10:37:59</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="F77" t="n">
-        <v>7.26</v>
+        <v>7.19</v>
       </c>
       <c r="G77" t="n">
-        <v>177.9</v>
+        <v>175.8</v>
       </c>
       <c r="H77" t="n">
-        <v>79.40000000000001</v>
+        <v>53.4</v>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J77" t="n">
-        <v>52.26</v>
+        <v>-53.78</v>
       </c>
       <c r="K77" t="n">
-        <v>-51.07</v>
+        <v>-25.95</v>
       </c>
       <c r="L77" t="n">
-        <v>73.06999999999999</v>
+        <v>59.71</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:36:21</t>
+          <t>10:39:13</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="F78" t="n">
-        <v>7.93</v>
+        <v>6.91</v>
       </c>
       <c r="G78" t="n">
-        <v>169.4</v>
+        <v>166.9</v>
       </c>
       <c r="H78" t="n">
-        <v>89.3</v>
+        <v>58.1</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J78" t="n">
-        <v>-79.54000000000001</v>
+        <v>-27.96</v>
       </c>
       <c r="K78" t="n">
-        <v>-58.04</v>
+        <v>-43.4</v>
       </c>
       <c r="L78" t="n">
-        <v>98.45999999999999</v>
+        <v>51.62</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:37:36</t>
+          <t>10:40:28</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="F79" t="n">
-        <v>7.93</v>
+        <v>7.78</v>
       </c>
       <c r="G79" t="n">
-        <v>171.8</v>
+        <v>188.4</v>
       </c>
       <c r="H79" t="n">
-        <v>77.5</v>
+        <v>45.4</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>59.58</v>
+        <v>-12.46</v>
       </c>
       <c r="K79" t="n">
-        <v>58.44</v>
+        <v>57.68</v>
       </c>
       <c r="L79" t="n">
-        <v>83.45</v>
+        <v>59.01</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:42:47</t>
+          <t>10:45:22</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.93</v>
+        <v>3.06</v>
       </c>
       <c r="F80" t="n">
         <v>7.93</v>
       </c>
       <c r="G80" t="n">
-        <v>188.7</v>
+        <v>167.8</v>
       </c>
       <c r="H80" t="n">
-        <v>82.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>-49.34</v>
+        <v>42.34</v>
       </c>
       <c r="K80" t="n">
-        <v>-84.77</v>
+        <v>-80.11</v>
       </c>
       <c r="L80" t="n">
-        <v>98.08</v>
+        <v>90.61</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:45:43</t>
+          <t>10:46:51</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="F81" t="n">
         <v>7.93</v>
       </c>
       <c r="G81" t="n">
-        <v>177.3</v>
+        <v>163.7</v>
       </c>
       <c r="H81" t="n">
-        <v>89.5</v>
+        <v>28.8</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J81" t="n">
-        <v>68.61</v>
+        <v>-54.56</v>
       </c>
       <c r="K81" t="n">
-        <v>86.59999999999999</v>
+        <v>-17</v>
       </c>
       <c r="L81" t="n">
-        <v>110.48</v>
+        <v>57.15</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:46:21</t>
+          <t>10:48:20</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.79</v>
+        <v>3.05</v>
       </c>
       <c r="F82" t="n">
-        <v>5.03</v>
+        <v>6.95</v>
       </c>
       <c r="G82" t="n">
-        <v>189.9</v>
+        <v>183.5</v>
       </c>
       <c r="H82" t="n">
-        <v>83.5</v>
+        <v>42</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-44.29</v>
+        <v>-26.2</v>
       </c>
       <c r="K82" t="n">
-        <v>-75.94</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>87.92</v>
+        <v>94.55</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:50:36</t>
+          <t>10:54:14</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.38</v>
+        <v>4.17</v>
       </c>
       <c r="F83" t="n">
         <v>7.93</v>
       </c>
       <c r="G83" t="n">
-        <v>167.4</v>
+        <v>193.3</v>
       </c>
       <c r="H83" t="n">
-        <v>86</v>
+        <v>43.1</v>
       </c>
       <c r="I83" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J83" t="n">
-        <v>-131.41</v>
+        <v>-169.92</v>
       </c>
       <c r="K83" t="n">
-        <v>-71.84</v>
+        <v>-157.76</v>
       </c>
       <c r="L83" t="n">
-        <v>149.77</v>
+        <v>231.86</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:51:22</t>
+          <t>10:55:37</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.21</v>
+        <v>2.66</v>
       </c>
       <c r="F84" t="n">
         <v>7.93</v>
       </c>
       <c r="G84" t="n">
-        <v>163.5</v>
+        <v>176.2</v>
       </c>
       <c r="H84" t="n">
-        <v>87.7</v>
+        <v>71.8</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J84" t="n">
-        <v>145.89</v>
+        <v>75.62</v>
       </c>
       <c r="K84" t="n">
-        <v>102.3</v>
+        <v>-49.05</v>
       </c>
       <c r="L84" t="n">
-        <v>178.19</v>
+        <v>90.13</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:52:22</t>
+          <t>10:56:28</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="F85" t="n">
         <v>7.93</v>
       </c>
       <c r="G85" t="n">
-        <v>185.2</v>
+        <v>179.4</v>
       </c>
       <c r="H85" t="n">
-        <v>81.3</v>
+        <v>43.2</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>97.42</v>
+        <v>152.71</v>
       </c>
       <c r="K85" t="n">
-        <v>-50.94</v>
+        <v>-0.17</v>
       </c>
       <c r="L85" t="n">
-        <v>109.94</v>
+        <v>152.71</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:57:55</t>
+          <t>11:02:22</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="F86" t="n">
         <v>7.93</v>
       </c>
       <c r="G86" t="n">
-        <v>180.6</v>
+        <v>157.8</v>
       </c>
       <c r="H86" t="n">
-        <v>78.90000000000001</v>
+        <v>43.4</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J86" t="n">
-        <v>-36.41</v>
+        <v>-98.90000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>169.28</v>
+        <v>121.12</v>
       </c>
       <c r="L86" t="n">
-        <v>173.15</v>
+        <v>156.37</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:58:54</t>
+          <t>11:03:04</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="F87" t="n">
         <v>7.93</v>
       </c>
       <c r="G87" t="n">
-        <v>181</v>
+        <v>184.4</v>
       </c>
       <c r="H87" t="n">
-        <v>89.5</v>
+        <v>78.7</v>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>64.59999999999999</v>
+        <v>179.88</v>
       </c>
       <c r="K87" t="n">
-        <v>-255.21</v>
+        <v>-25.68</v>
       </c>
       <c r="L87" t="n">
-        <v>263.26</v>
+        <v>181.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:00:18</t>
+          <t>11:05:31</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="F88" t="n">
-        <v>7.3</v>
+        <v>7.71</v>
       </c>
       <c r="G88" t="n">
-        <v>197.1</v>
+        <v>170.2</v>
       </c>
       <c r="H88" t="n">
-        <v>79.09999999999999</v>
+        <v>45.9</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-115.52</v>
+        <v>198.28</v>
       </c>
       <c r="K88" t="n">
-        <v>-207.61</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>237.58</v>
+        <v>209.94</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-03.xlsx
+++ b/output/2024-10-03.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.27</v>
+        <v>1.94</v>
       </c>
       <c r="F14" t="n">
-        <v>5.65</v>
+        <v>4.87</v>
       </c>
       <c r="G14" t="n">
-        <v>170.2</v>
+        <v>168.5</v>
       </c>
       <c r="H14" t="n">
-        <v>28.9</v>
+        <v>44.1</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>29.5</v>
+        <v>-8.23</v>
       </c>
       <c r="K14" t="n">
-        <v>-22.28</v>
+        <v>37.79</v>
       </c>
       <c r="L14" t="n">
-        <v>36.97</v>
+        <v>38.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:23:11</t>
+          <t>07:23:54</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.49</v>
+        <v>2.71</v>
       </c>
       <c r="F15" t="n">
-        <v>5.14</v>
+        <v>6.83</v>
       </c>
       <c r="G15" t="n">
-        <v>184.3</v>
+        <v>169.2</v>
       </c>
       <c r="H15" t="n">
-        <v>46.2</v>
+        <v>31.1</v>
       </c>
       <c r="I15" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>-20.11</v>
+        <v>-63.32</v>
       </c>
       <c r="K15" t="n">
-        <v>-19.19</v>
+        <v>-29.55</v>
       </c>
       <c r="L15" t="n">
-        <v>27.8</v>
+        <v>69.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:25:03</t>
+          <t>07:24:39</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7</v>
+        <v>2.44</v>
       </c>
       <c r="F16" t="n">
-        <v>3.46</v>
+        <v>4.9</v>
       </c>
       <c r="G16" t="n">
-        <v>183.1</v>
+        <v>193.2</v>
       </c>
       <c r="H16" t="n">
-        <v>35.1</v>
+        <v>58.5</v>
       </c>
       <c r="I16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>-40.06</v>
+        <v>-45.42</v>
       </c>
       <c r="K16" t="n">
-        <v>9.720000000000001</v>
+        <v>34.42</v>
       </c>
       <c r="L16" t="n">
-        <v>41.22</v>
+        <v>56.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:29:24</t>
+          <t>07:29:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="F17" t="n">
-        <v>4.73</v>
+        <v>5.88</v>
       </c>
       <c r="G17" t="n">
-        <v>175.3</v>
+        <v>179.6</v>
       </c>
       <c r="H17" t="n">
-        <v>44.8</v>
+        <v>54.4</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>33.27</v>
+        <v>35.62</v>
       </c>
       <c r="K17" t="n">
-        <v>-51.35</v>
+        <v>-62.58</v>
       </c>
       <c r="L17" t="n">
-        <v>61.19</v>
+        <v>72.01000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:30:09</t>
+          <t>07:30:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.51</v>
+        <v>2.14</v>
       </c>
       <c r="F18" t="n">
-        <v>7.93</v>
+        <v>5.62</v>
       </c>
       <c r="G18" t="n">
-        <v>159.6</v>
+        <v>183.8</v>
       </c>
       <c r="H18" t="n">
-        <v>55</v>
+        <v>68.8</v>
       </c>
       <c r="I18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J18" t="n">
-        <v>31.18</v>
+        <v>44.42</v>
       </c>
       <c r="K18" t="n">
-        <v>34.72</v>
+        <v>-49.3</v>
       </c>
       <c r="L18" t="n">
-        <v>46.67</v>
+        <v>66.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:30:58</t>
+          <t>07:32:48</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.57</v>
+        <v>2.31</v>
       </c>
       <c r="F19" t="n">
-        <v>7.19</v>
+        <v>2.82</v>
       </c>
       <c r="G19" t="n">
-        <v>169.1</v>
+        <v>159.1</v>
       </c>
       <c r="H19" t="n">
-        <v>57.4</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>15.95</v>
+        <v>-56.78</v>
       </c>
       <c r="K19" t="n">
-        <v>-69.23</v>
+        <v>-16.95</v>
       </c>
       <c r="L19" t="n">
-        <v>71.05</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:36:50</t>
+          <t>07:37:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="F20" t="n">
-        <v>6.49</v>
+        <v>6.22</v>
       </c>
       <c r="G20" t="n">
-        <v>198</v>
+        <v>179.4</v>
       </c>
       <c r="H20" t="n">
-        <v>39.3</v>
+        <v>98.8</v>
       </c>
       <c r="I20" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>-77.59999999999999</v>
+        <v>93.92</v>
       </c>
       <c r="K20" t="n">
-        <v>18.66</v>
+        <v>29.59</v>
       </c>
       <c r="L20" t="n">
-        <v>79.81999999999999</v>
+        <v>98.48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:38:45</t>
+          <t>07:38:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="F21" t="n">
-        <v>7.93</v>
+        <v>5.81</v>
       </c>
       <c r="G21" t="n">
-        <v>183.3</v>
+        <v>186.3</v>
       </c>
       <c r="H21" t="n">
-        <v>36.8</v>
+        <v>44.7</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.93</v>
+        <v>-43.98</v>
       </c>
       <c r="K21" t="n">
-        <v>-38.91</v>
+        <v>-95.06</v>
       </c>
       <c r="L21" t="n">
-        <v>39.22</v>
+        <v>104.74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:41:05</t>
+          <t>07:40:35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="F22" t="n">
-        <v>5.09</v>
+        <v>5.2</v>
       </c>
       <c r="G22" t="n">
-        <v>186.6</v>
+        <v>180.3</v>
       </c>
       <c r="H22" t="n">
-        <v>45.9</v>
+        <v>28.6</v>
       </c>
       <c r="I22" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>79.23999999999999</v>
+        <v>-86.89</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.07</v>
+        <v>-40.84</v>
       </c>
       <c r="L22" t="n">
-        <v>79.88</v>
+        <v>96.01000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:46:52</t>
+          <t>07:45:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
       <c r="F23" t="n">
-        <v>5.71</v>
+        <v>7.93</v>
       </c>
       <c r="G23" t="n">
-        <v>173.8</v>
+        <v>168.8</v>
       </c>
       <c r="H23" t="n">
-        <v>46.2</v>
+        <v>44.8</v>
       </c>
       <c r="I23" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>14.99</v>
+        <v>-75.18000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-229.7</v>
+        <v>195.38</v>
       </c>
       <c r="L23" t="n">
-        <v>230.18</v>
+        <v>209.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:48:52</t>
+          <t>07:46:48</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="F24" t="n">
-        <v>4.82</v>
+        <v>7.93</v>
       </c>
       <c r="G24" t="n">
-        <v>179.7</v>
+        <v>177.1</v>
       </c>
       <c r="H24" t="n">
-        <v>72.09999999999999</v>
+        <v>56.5</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>6.56</v>
+        <v>71.14</v>
       </c>
       <c r="K24" t="n">
-        <v>-118.65</v>
+        <v>-180.8</v>
       </c>
       <c r="L24" t="n">
-        <v>118.83</v>
+        <v>194.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:50:38</t>
+          <t>07:48:14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.65</v>
+        <v>2.46</v>
       </c>
       <c r="F25" t="n">
-        <v>7.93</v>
+        <v>7.33</v>
       </c>
       <c r="G25" t="n">
-        <v>196.7</v>
+        <v>180.6</v>
       </c>
       <c r="H25" t="n">
-        <v>69.2</v>
+        <v>88.3</v>
       </c>
       <c r="I25" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>112.89</v>
+        <v>173.79</v>
       </c>
       <c r="K25" t="n">
-        <v>-76.84</v>
+        <v>40.37</v>
       </c>
       <c r="L25" t="n">
-        <v>136.56</v>
+        <v>178.42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:55:30</t>
+          <t>07:51:32</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="F26" t="n">
-        <v>3.7</v>
+        <v>7.93</v>
       </c>
       <c r="G26" t="n">
-        <v>176.7</v>
+        <v>167.1</v>
       </c>
       <c r="H26" t="n">
-        <v>49.8</v>
+        <v>55.5</v>
       </c>
       <c r="I26" t="n">
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>168.43</v>
+        <v>-164.47</v>
       </c>
       <c r="K26" t="n">
-        <v>40.61</v>
+        <v>104.27</v>
       </c>
       <c r="L26" t="n">
-        <v>173.26</v>
+        <v>194.74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:56:54</t>
+          <t>07:53:39</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
       <c r="F27" t="n">
-        <v>7.33</v>
+        <v>6.46</v>
       </c>
       <c r="G27" t="n">
-        <v>183.7</v>
+        <v>186.7</v>
       </c>
       <c r="H27" t="n">
-        <v>86.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-159.77</v>
+        <v>159.3</v>
       </c>
       <c r="K27" t="n">
-        <v>96.48</v>
+        <v>67.3</v>
       </c>
       <c r="L27" t="n">
-        <v>186.64</v>
+        <v>172.93</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:58:02</t>
+          <t>07:56:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="F28" t="n">
-        <v>2.78</v>
+        <v>4.4</v>
       </c>
       <c r="G28" t="n">
-        <v>169.6</v>
+        <v>183.3</v>
       </c>
       <c r="H28" t="n">
-        <v>41.2</v>
+        <v>49.2</v>
       </c>
       <c r="I28" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>81.09999999999999</v>
+        <v>-131.48</v>
       </c>
       <c r="K28" t="n">
-        <v>-126.59</v>
+        <v>-75.05</v>
       </c>
       <c r="L28" t="n">
-        <v>150.33</v>
+        <v>151.39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:08:44</t>
+          <t>08:08:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="F29" t="n">
         <v>7.93</v>
       </c>
       <c r="G29" t="n">
-        <v>192.4</v>
+        <v>180.7</v>
       </c>
       <c r="H29" t="n">
-        <v>81.90000000000001</v>
+        <v>54.3</v>
       </c>
       <c r="I29" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-44.05</v>
+        <v>22.34</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.51</v>
+        <v>26.53</v>
       </c>
       <c r="L29" t="n">
-        <v>44.12</v>
+        <v>34.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:10:36</t>
+          <t>08:11:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="F30" t="n">
-        <v>4.82</v>
+        <v>7.06</v>
       </c>
       <c r="G30" t="n">
-        <v>178.3</v>
+        <v>187.1</v>
       </c>
       <c r="H30" t="n">
-        <v>45.2</v>
+        <v>61</v>
       </c>
       <c r="I30" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>36.16</v>
+        <v>2.01</v>
       </c>
       <c r="K30" t="n">
-        <v>14.99</v>
+        <v>-46.1</v>
       </c>
       <c r="L30" t="n">
-        <v>39.14</v>
+        <v>46.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:11:55</t>
+          <t>08:12:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="F31" t="n">
-        <v>6.03</v>
+        <v>6.45</v>
       </c>
       <c r="G31" t="n">
-        <v>181.9</v>
+        <v>165.9</v>
       </c>
       <c r="H31" t="n">
-        <v>22</v>
+        <v>65.2</v>
       </c>
       <c r="I31" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-25.8</v>
+        <v>13.09</v>
       </c>
       <c r="K31" t="n">
-        <v>-40.13</v>
+        <v>40.82</v>
       </c>
       <c r="L31" t="n">
-        <v>47.71</v>
+        <v>42.87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:15:04</t>
+          <t>08:16:53</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="F32" t="n">
-        <v>5.03</v>
+        <v>7.93</v>
       </c>
       <c r="G32" t="n">
-        <v>182.4</v>
+        <v>177.6</v>
       </c>
       <c r="H32" t="n">
-        <v>11.2</v>
+        <v>55.7</v>
       </c>
       <c r="I32" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-54.34</v>
+        <v>-38.87</v>
       </c>
       <c r="K32" t="n">
-        <v>27.3</v>
+        <v>61.53</v>
       </c>
       <c r="L32" t="n">
-        <v>60.81</v>
+        <v>72.78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:16:11</t>
+          <t>08:18:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="F33" t="n">
-        <v>7.69</v>
+        <v>4.64</v>
       </c>
       <c r="G33" t="n">
-        <v>181.3</v>
+        <v>166.8</v>
       </c>
       <c r="H33" t="n">
-        <v>57.2</v>
+        <v>59.5</v>
       </c>
       <c r="I33" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>42.12</v>
+        <v>53.12</v>
       </c>
       <c r="K33" t="n">
-        <v>-46.4</v>
+        <v>55.49</v>
       </c>
       <c r="L33" t="n">
-        <v>62.66</v>
+        <v>76.81999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:17:36</t>
+          <t>08:19:35</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.08</v>
+        <v>2.58</v>
       </c>
       <c r="F34" t="n">
-        <v>7.93</v>
+        <v>6.87</v>
       </c>
       <c r="G34" t="n">
-        <v>153.2</v>
+        <v>176.9</v>
       </c>
       <c r="H34" t="n">
-        <v>15.9</v>
+        <v>55.8</v>
       </c>
       <c r="I34" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>45.14</v>
+        <v>-63.73</v>
       </c>
       <c r="K34" t="n">
-        <v>30.89</v>
+        <v>-3.65</v>
       </c>
       <c r="L34" t="n">
-        <v>54.7</v>
+        <v>63.83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:22:55</t>
+          <t>08:24:01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>5.72</v>
+        <v>7.67</v>
       </c>
       <c r="G35" t="n">
-        <v>176.7</v>
+        <v>164.5</v>
       </c>
       <c r="H35" t="n">
-        <v>69.8</v>
+        <v>61.9</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>83.84999999999999</v>
+        <v>-75.48999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>2.91</v>
+        <v>25.87</v>
       </c>
       <c r="L35" t="n">
-        <v>83.90000000000001</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:24:51</t>
+          <t>08:25:52</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F36" t="n">
-        <v>6.9</v>
+        <v>7.93</v>
       </c>
       <c r="G36" t="n">
-        <v>180.5</v>
+        <v>175.5</v>
       </c>
       <c r="H36" t="n">
-        <v>44.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-138.23</v>
+        <v>91.97</v>
       </c>
       <c r="K36" t="n">
-        <v>48.74</v>
+        <v>73.36</v>
       </c>
       <c r="L36" t="n">
-        <v>146.57</v>
+        <v>117.65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:26:45</t>
+          <t>08:27:12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.61</v>
+        <v>3.79</v>
       </c>
       <c r="F37" t="n">
-        <v>7.93</v>
+        <v>5.76</v>
       </c>
       <c r="G37" t="n">
-        <v>168.6</v>
+        <v>183</v>
       </c>
       <c r="H37" t="n">
-        <v>22.7</v>
+        <v>48</v>
       </c>
       <c r="I37" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>63.48</v>
+        <v>-118.35</v>
       </c>
       <c r="K37" t="n">
-        <v>7.61</v>
+        <v>82.97</v>
       </c>
       <c r="L37" t="n">
-        <v>63.93</v>
+        <v>144.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:30:57</t>
+          <t>08:32:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="F38" t="n">
-        <v>7.02</v>
+        <v>6.98</v>
       </c>
       <c r="G38" t="n">
-        <v>175.2</v>
+        <v>187.8</v>
       </c>
       <c r="H38" t="n">
-        <v>77.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>22.13</v>
+        <v>-173.32</v>
       </c>
       <c r="K38" t="n">
-        <v>102.23</v>
+        <v>38.41</v>
       </c>
       <c r="L38" t="n">
-        <v>104.6</v>
+        <v>177.52</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:32:54</t>
+          <t>08:33:58</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="F39" t="n">
-        <v>7.93</v>
+        <v>5.26</v>
       </c>
       <c r="G39" t="n">
-        <v>182</v>
+        <v>186.6</v>
       </c>
       <c r="H39" t="n">
-        <v>87.7</v>
+        <v>45.9</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>188.8</v>
+        <v>171.55</v>
       </c>
       <c r="K39" t="n">
-        <v>-11.38</v>
+        <v>2.4</v>
       </c>
       <c r="L39" t="n">
-        <v>189.14</v>
+        <v>171.57</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:34:50</t>
+          <t>08:35:08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="F40" t="n">
-        <v>7.93</v>
+        <v>6.39</v>
       </c>
       <c r="G40" t="n">
-        <v>188.1</v>
+        <v>172.8</v>
       </c>
       <c r="H40" t="n">
-        <v>39.7</v>
+        <v>83.5</v>
       </c>
       <c r="I40" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>-131.26</v>
+        <v>17.46</v>
       </c>
       <c r="K40" t="n">
-        <v>15.07</v>
+        <v>-173.29</v>
       </c>
       <c r="L40" t="n">
-        <v>132.12</v>
+        <v>174.17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:39:20</t>
+          <t>08:39:42</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.31</v>
+        <v>3.74</v>
       </c>
       <c r="F41" t="n">
-        <v>6.65</v>
+        <v>7.93</v>
       </c>
       <c r="G41" t="n">
-        <v>180</v>
+        <v>174.9</v>
       </c>
       <c r="H41" t="n">
-        <v>56.2</v>
+        <v>85.3</v>
       </c>
       <c r="I41" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>69.31999999999999</v>
+        <v>167.46</v>
       </c>
       <c r="K41" t="n">
-        <v>189.04</v>
+        <v>-258.86</v>
       </c>
       <c r="L41" t="n">
-        <v>201.35</v>
+        <v>308.31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:40:56</t>
+          <t>08:42:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="F42" t="n">
-        <v>6.92</v>
+        <v>7.93</v>
       </c>
       <c r="G42" t="n">
-        <v>186.8</v>
+        <v>167.8</v>
       </c>
       <c r="H42" t="n">
-        <v>66.2</v>
+        <v>47.9</v>
       </c>
       <c r="I42" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>163.25</v>
+        <v>164.94</v>
       </c>
       <c r="K42" t="n">
-        <v>23.63</v>
+        <v>-189.93</v>
       </c>
       <c r="L42" t="n">
-        <v>164.95</v>
+        <v>251.55</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:43:05</t>
+          <t>08:42:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="F43" t="n">
-        <v>5.33</v>
+        <v>5.81</v>
       </c>
       <c r="G43" t="n">
-        <v>173</v>
+        <v>194.1</v>
       </c>
       <c r="H43" t="n">
-        <v>80.7</v>
+        <v>55.8</v>
       </c>
       <c r="I43" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>82.52</v>
+        <v>186.2</v>
       </c>
       <c r="K43" t="n">
-        <v>-97.36</v>
+        <v>12.26</v>
       </c>
       <c r="L43" t="n">
-        <v>127.63</v>
+        <v>186.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:53:01</t>
+          <t>08:55:38</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="F44" t="n">
-        <v>7.93</v>
+        <v>7.6</v>
       </c>
       <c r="G44" t="n">
-        <v>192.4</v>
+        <v>183.7</v>
       </c>
       <c r="H44" t="n">
-        <v>69.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.95</v>
+        <v>-50.15</v>
       </c>
       <c r="K44" t="n">
-        <v>42.05</v>
+        <v>39.67</v>
       </c>
       <c r="L44" t="n">
-        <v>42.24</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:54:36</t>
+          <t>08:56:50</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.09</v>
+        <v>2.45</v>
       </c>
       <c r="F45" t="n">
-        <v>7.93</v>
+        <v>3.55</v>
       </c>
       <c r="G45" t="n">
-        <v>176.7</v>
+        <v>172.2</v>
       </c>
       <c r="H45" t="n">
-        <v>31.5</v>
+        <v>38.2</v>
       </c>
       <c r="I45" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-42.28</v>
+        <v>-45.97</v>
       </c>
       <c r="K45" t="n">
-        <v>-32.35</v>
+        <v>15</v>
       </c>
       <c r="L45" t="n">
-        <v>53.24</v>
+        <v>48.35</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:56:31</t>
+          <t>08:58:54</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="F46" t="n">
-        <v>7.93</v>
+        <v>5.63</v>
       </c>
       <c r="G46" t="n">
-        <v>178.6</v>
+        <v>192.4</v>
       </c>
       <c r="H46" t="n">
-        <v>47.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.02</v>
+        <v>-60.59</v>
       </c>
       <c r="K46" t="n">
-        <v>-43.69</v>
+        <v>8.66</v>
       </c>
       <c r="L46" t="n">
-        <v>46.2</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:00:59</t>
+          <t>09:04:13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.53</v>
+        <v>2.97</v>
       </c>
       <c r="F47" t="n">
-        <v>7.93</v>
+        <v>5.59</v>
       </c>
       <c r="G47" t="n">
-        <v>175.1</v>
+        <v>190.2</v>
       </c>
       <c r="H47" t="n">
-        <v>33.4</v>
+        <v>60</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-6.93</v>
+        <v>62.51</v>
       </c>
       <c r="K47" t="n">
-        <v>-50.64</v>
+        <v>21.58</v>
       </c>
       <c r="L47" t="n">
-        <v>51.11</v>
+        <v>66.13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:02:45</t>
+          <t>09:06:15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="F48" t="n">
-        <v>7.87</v>
+        <v>4.89</v>
       </c>
       <c r="G48" t="n">
-        <v>165.9</v>
+        <v>190.1</v>
       </c>
       <c r="H48" t="n">
-        <v>43.7</v>
+        <v>68.8</v>
       </c>
       <c r="I48" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.33</v>
+        <v>-46.26</v>
       </c>
       <c r="K48" t="n">
-        <v>6.23</v>
+        <v>85.13</v>
       </c>
       <c r="L48" t="n">
-        <v>7.06</v>
+        <v>96.89</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:03:18</t>
+          <t>09:07:54</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.79</v>
+        <v>2.99</v>
       </c>
       <c r="F49" t="n">
-        <v>7.93</v>
+        <v>5.7</v>
       </c>
       <c r="G49" t="n">
-        <v>184</v>
+        <v>182.4</v>
       </c>
       <c r="H49" t="n">
-        <v>57.3</v>
+        <v>11.2</v>
       </c>
       <c r="I49" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-63.64</v>
+        <v>-67.62</v>
       </c>
       <c r="K49" t="n">
-        <v>14.58</v>
+        <v>48.72</v>
       </c>
       <c r="L49" t="n">
-        <v>65.29000000000001</v>
+        <v>83.34</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:08:03</t>
+          <t>09:13:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.42</v>
+        <v>2.77</v>
       </c>
       <c r="F50" t="n">
-        <v>5.92</v>
+        <v>7.93</v>
       </c>
       <c r="G50" t="n">
-        <v>168.8</v>
+        <v>177.2</v>
       </c>
       <c r="H50" t="n">
-        <v>60.7</v>
+        <v>50.3</v>
       </c>
       <c r="I50" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>98.42</v>
+        <v>4.75</v>
       </c>
       <c r="K50" t="n">
-        <v>-6.23</v>
+        <v>-106.83</v>
       </c>
       <c r="L50" t="n">
-        <v>98.62</v>
+        <v>106.94</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:09:46</t>
+          <t>09:13:41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="F51" t="n">
-        <v>7.93</v>
+        <v>7.17</v>
       </c>
       <c r="G51" t="n">
-        <v>184.5</v>
+        <v>160.7</v>
       </c>
       <c r="H51" t="n">
-        <v>70.90000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="I51" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-82.48999999999999</v>
+        <v>13.66</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.59</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>82.68000000000001</v>
+        <v>97.39</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:11:37</t>
+          <t>09:15:20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="F52" t="n">
-        <v>7.65</v>
+        <v>7.93</v>
       </c>
       <c r="G52" t="n">
-        <v>171.3</v>
+        <v>183.8</v>
       </c>
       <c r="H52" t="n">
-        <v>59.3</v>
+        <v>39.7</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>55.53</v>
+        <v>-35.7</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.54</v>
+        <v>-112.97</v>
       </c>
       <c r="L52" t="n">
-        <v>56.04</v>
+        <v>118.48</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:16:44</t>
+          <t>09:20:13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="F53" t="n">
         <v>7.93</v>
       </c>
       <c r="G53" t="n">
-        <v>165.8</v>
+        <v>172.1</v>
       </c>
       <c r="H53" t="n">
-        <v>75.3</v>
+        <v>48.9</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-24.83</v>
+        <v>-158.98</v>
       </c>
       <c r="K53" t="n">
-        <v>-149.18</v>
+        <v>11.44</v>
       </c>
       <c r="L53" t="n">
-        <v>151.24</v>
+        <v>159.39</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:18:59</t>
+          <t>09:22:39</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="F54" t="n">
-        <v>4.29</v>
+        <v>6.27</v>
       </c>
       <c r="G54" t="n">
-        <v>182.5</v>
+        <v>170.8</v>
       </c>
       <c r="H54" t="n">
-        <v>49.3</v>
+        <v>79.5</v>
       </c>
       <c r="I54" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-68.20999999999999</v>
+        <v>-64.8</v>
       </c>
       <c r="K54" t="n">
-        <v>-74.67</v>
+        <v>208.93</v>
       </c>
       <c r="L54" t="n">
-        <v>101.14</v>
+        <v>218.75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:21:49</t>
+          <t>09:24:31</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.72</v>
+        <v>2.78</v>
       </c>
       <c r="F55" t="n">
         <v>7.93</v>
       </c>
       <c r="G55" t="n">
-        <v>167.8</v>
+        <v>175.2</v>
       </c>
       <c r="H55" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>77.31999999999999</v>
+        <v>25.62</v>
       </c>
       <c r="K55" t="n">
-        <v>-205.29</v>
+        <v>151.19</v>
       </c>
       <c r="L55" t="n">
-        <v>219.37</v>
+        <v>153.35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:26:11</t>
+          <t>09:28:41</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.58</v>
+        <v>3.06</v>
       </c>
       <c r="F56" t="n">
         <v>7.93</v>
       </c>
       <c r="G56" t="n">
-        <v>183.9</v>
+        <v>189.4</v>
       </c>
       <c r="H56" t="n">
-        <v>65.90000000000001</v>
+        <v>34.5</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-164.54</v>
+        <v>158.85</v>
       </c>
       <c r="K56" t="n">
-        <v>-62.56</v>
+        <v>-152.56</v>
       </c>
       <c r="L56" t="n">
-        <v>176.03</v>
+        <v>220.24</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:28:17</t>
+          <t>09:29:11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="F57" t="n">
-        <v>7.3</v>
+        <v>6.29</v>
       </c>
       <c r="G57" t="n">
-        <v>157.8</v>
+        <v>188.1</v>
       </c>
       <c r="H57" t="n">
-        <v>33.2</v>
+        <v>39.7</v>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>153.4</v>
+        <v>-238.41</v>
       </c>
       <c r="K57" t="n">
-        <v>-44.81</v>
+        <v>71.73</v>
       </c>
       <c r="L57" t="n">
-        <v>159.81</v>
+        <v>248.97</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:30:04</t>
+          <t>09:31:23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="F58" t="n">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="G58" t="n">
-        <v>182.1</v>
+        <v>176.8</v>
       </c>
       <c r="H58" t="n">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J58" t="n">
-        <v>268.93</v>
+        <v>55.85</v>
       </c>
       <c r="K58" t="n">
-        <v>-98.31</v>
+        <v>230.03</v>
       </c>
       <c r="L58" t="n">
-        <v>286.34</v>
+        <v>236.71</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:42:39</t>
+          <t>09:41:11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="F59" t="n">
-        <v>7.93</v>
+        <v>7.68</v>
       </c>
       <c r="G59" t="n">
-        <v>174.2</v>
+        <v>175.8</v>
       </c>
       <c r="H59" t="n">
-        <v>50</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>56.86</v>
+        <v>35.4</v>
       </c>
       <c r="K59" t="n">
-        <v>15.43</v>
+        <v>-23.16</v>
       </c>
       <c r="L59" t="n">
-        <v>58.92</v>
+        <v>42.31</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:43:56</t>
+          <t>09:43:35</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="F60" t="n">
-        <v>6.42</v>
+        <v>7.93</v>
       </c>
       <c r="G60" t="n">
-        <v>176.2</v>
+        <v>173</v>
       </c>
       <c r="H60" t="n">
-        <v>66.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="I60" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-34.31</v>
+        <v>29.68</v>
       </c>
       <c r="K60" t="n">
-        <v>40.14</v>
+        <v>-27.76</v>
       </c>
       <c r="L60" t="n">
-        <v>52.81</v>
+        <v>40.64</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:44:56</t>
+          <t>09:45:40</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="F61" t="n">
-        <v>7.49</v>
+        <v>7.93</v>
       </c>
       <c r="G61" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H61" t="n">
-        <v>98.7</v>
+        <v>95.2</v>
       </c>
       <c r="I61" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>2.96</v>
+        <v>58.03</v>
       </c>
       <c r="K61" t="n">
-        <v>46.73</v>
+        <v>33</v>
       </c>
       <c r="L61" t="n">
-        <v>46.83</v>
+        <v>66.76000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:49:52</t>
+          <t>09:49:09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.09</v>
+        <v>2.76</v>
       </c>
       <c r="F62" t="n">
-        <v>7.7</v>
+        <v>7.93</v>
       </c>
       <c r="G62" t="n">
-        <v>173.5</v>
+        <v>176.7</v>
       </c>
       <c r="H62" t="n">
-        <v>31.1</v>
+        <v>31.5</v>
       </c>
       <c r="I62" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>84.42</v>
+        <v>-75.26000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>35.04</v>
+        <v>-34.23</v>
       </c>
       <c r="L62" t="n">
-        <v>91.41</v>
+        <v>82.68000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:50:39</t>
+          <t>09:50:55</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="F63" t="n">
         <v>7.93</v>
       </c>
       <c r="G63" t="n">
-        <v>169.7</v>
+        <v>180.9</v>
       </c>
       <c r="H63" t="n">
-        <v>69.09999999999999</v>
+        <v>60.7</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>70.06999999999999</v>
+        <v>23.17</v>
       </c>
       <c r="K63" t="n">
-        <v>-6.91</v>
+        <v>63.6</v>
       </c>
       <c r="L63" t="n">
-        <v>70.41</v>
+        <v>67.69</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:52:44</t>
+          <t>09:53:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,28 +2725,28 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="F64" t="n">
-        <v>5.54</v>
+        <v>7.93</v>
       </c>
       <c r="G64" t="n">
-        <v>173.1</v>
+        <v>172.9</v>
       </c>
       <c r="H64" t="n">
-        <v>53.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>66.59999999999999</v>
+        <v>-49.75</v>
       </c>
       <c r="K64" t="n">
-        <v>-11.11</v>
+        <v>-32.82</v>
       </c>
       <c r="L64" t="n">
-        <v>67.52</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="65">
@@ -2767,28 +2767,28 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="F65" t="n">
-        <v>7.93</v>
+        <v>7.6</v>
       </c>
       <c r="G65" t="n">
-        <v>185.3</v>
+        <v>163.5</v>
       </c>
       <c r="H65" t="n">
-        <v>74.59999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>24.37</v>
+        <v>24.98</v>
       </c>
       <c r="K65" t="n">
-        <v>66.40000000000001</v>
+        <v>-77.68000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>70.73</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="F66" t="n">
-        <v>6.68</v>
+        <v>7.93</v>
       </c>
       <c r="G66" t="n">
-        <v>184.5</v>
+        <v>177.5</v>
       </c>
       <c r="H66" t="n">
-        <v>94.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J66" t="n">
-        <v>-32.45</v>
+        <v>-113.1</v>
       </c>
       <c r="K66" t="n">
-        <v>-49.69</v>
+        <v>-48.88</v>
       </c>
       <c r="L66" t="n">
-        <v>59.35</v>
+        <v>123.21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:00:22</t>
+          <t>10:01:50</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="F67" t="n">
-        <v>6.91</v>
+        <v>5.4</v>
       </c>
       <c r="G67" t="n">
-        <v>178.8</v>
+        <v>178.6</v>
       </c>
       <c r="H67" t="n">
-        <v>39.1</v>
+        <v>50.6</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J67" t="n">
-        <v>10.91</v>
+        <v>54.72</v>
       </c>
       <c r="K67" t="n">
-        <v>-101.16</v>
+        <v>-72.58</v>
       </c>
       <c r="L67" t="n">
-        <v>101.75</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:04:37</t>
+          <t>10:06:05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.42</v>
+        <v>2.99</v>
       </c>
       <c r="F68" t="n">
         <v>7.93</v>
       </c>
       <c r="G68" t="n">
-        <v>194.8</v>
+        <v>163.4</v>
       </c>
       <c r="H68" t="n">
-        <v>53.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-87.58</v>
+        <v>-58.38</v>
       </c>
       <c r="K68" t="n">
-        <v>-92.93000000000001</v>
+        <v>-169.8</v>
       </c>
       <c r="L68" t="n">
-        <v>127.69</v>
+        <v>179.55</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:06:45</t>
+          <t>10:07:18</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.9</v>
+        <v>3.21</v>
       </c>
       <c r="F69" t="n">
         <v>7.93</v>
       </c>
       <c r="G69" t="n">
-        <v>176.2</v>
+        <v>178.1</v>
       </c>
       <c r="H69" t="n">
-        <v>55.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>137.65</v>
+        <v>-85.48999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>-124.71</v>
+        <v>-433.04</v>
       </c>
       <c r="L69" t="n">
-        <v>185.74</v>
+        <v>441.4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:09:15</t>
+          <t>10:09:51</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="F70" t="n">
         <v>7.93</v>
       </c>
       <c r="G70" t="n">
-        <v>166.9</v>
+        <v>177</v>
       </c>
       <c r="H70" t="n">
-        <v>59</v>
+        <v>49.3</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>84.16</v>
+        <v>113.97</v>
       </c>
       <c r="K70" t="n">
-        <v>88.51000000000001</v>
+        <v>-174.07</v>
       </c>
       <c r="L70" t="n">
-        <v>122.13</v>
+        <v>208.06</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:14:33</t>
+          <t>10:14:40</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.96</v>
+        <v>3.11</v>
       </c>
       <c r="F71" t="n">
-        <v>7.93</v>
+        <v>7.42</v>
       </c>
       <c r="G71" t="n">
-        <v>168.5</v>
+        <v>179.6</v>
       </c>
       <c r="H71" t="n">
-        <v>77</v>
+        <v>46.8</v>
       </c>
       <c r="I71" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>152.48</v>
+        <v>113.94</v>
       </c>
       <c r="K71" t="n">
-        <v>72.31</v>
+        <v>-54.77</v>
       </c>
       <c r="L71" t="n">
-        <v>168.75</v>
+        <v>126.42</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:16:09</t>
+          <t>10:16:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.84</v>
+        <v>2.91</v>
       </c>
       <c r="F72" t="n">
-        <v>6.66</v>
+        <v>7.93</v>
       </c>
       <c r="G72" t="n">
-        <v>168.9</v>
+        <v>176.3</v>
       </c>
       <c r="H72" t="n">
-        <v>61.5</v>
+        <v>58.7</v>
       </c>
       <c r="I72" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-158.38</v>
+        <v>-149.44</v>
       </c>
       <c r="K72" t="n">
-        <v>90.25</v>
+        <v>-146.1</v>
       </c>
       <c r="L72" t="n">
-        <v>182.29</v>
+        <v>208.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:17:26</t>
+          <t>10:17:28</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="F73" t="n">
         <v>7.93</v>
       </c>
       <c r="G73" t="n">
-        <v>172.5</v>
+        <v>176.6</v>
       </c>
       <c r="H73" t="n">
-        <v>4.8</v>
+        <v>63.1</v>
       </c>
       <c r="I73" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>148.24</v>
+        <v>165.62</v>
       </c>
       <c r="K73" t="n">
-        <v>13.99</v>
+        <v>180.34</v>
       </c>
       <c r="L73" t="n">
-        <v>148.9</v>
+        <v>244.86</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:30:23</t>
+          <t>10:29:37</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="F74" t="n">
-        <v>7.93</v>
+        <v>5.12</v>
       </c>
       <c r="G74" t="n">
-        <v>175.2</v>
+        <v>174.3</v>
       </c>
       <c r="H74" t="n">
-        <v>76.7</v>
+        <v>100</v>
       </c>
       <c r="I74" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>-30.53</v>
+        <v>12.89</v>
       </c>
       <c r="K74" t="n">
-        <v>-20.7</v>
+        <v>46.81</v>
       </c>
       <c r="L74" t="n">
-        <v>36.88</v>
+        <v>48.56</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:31:48</t>
+          <t>10:31:46</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="F75" t="n">
-        <v>4.95</v>
+        <v>7.52</v>
       </c>
       <c r="G75" t="n">
-        <v>179.6</v>
+        <v>172.1</v>
       </c>
       <c r="H75" t="n">
-        <v>71.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>1.75</v>
+        <v>41.64</v>
       </c>
       <c r="K75" t="n">
-        <v>-53.11</v>
+        <v>19.9</v>
       </c>
       <c r="L75" t="n">
-        <v>53.13</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:33:37</t>
+          <t>10:33:51</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="F76" t="n">
-        <v>7.03</v>
+        <v>7.93</v>
       </c>
       <c r="G76" t="n">
-        <v>181.2</v>
+        <v>174.8</v>
       </c>
       <c r="H76" t="n">
-        <v>57.4</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>12.94</v>
+        <v>48.33</v>
       </c>
       <c r="K76" t="n">
-        <v>37.64</v>
+        <v>41.53</v>
       </c>
       <c r="L76" t="n">
-        <v>39.8</v>
+        <v>63.72</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:37:59</t>
+          <t>10:38:45</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="F77" t="n">
-        <v>7.19</v>
+        <v>7.6</v>
       </c>
       <c r="G77" t="n">
-        <v>175.8</v>
+        <v>178.2</v>
       </c>
       <c r="H77" t="n">
-        <v>53.4</v>
+        <v>60.1</v>
       </c>
       <c r="I77" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-53.78</v>
+        <v>30.75</v>
       </c>
       <c r="K77" t="n">
-        <v>-25.95</v>
+        <v>76.31</v>
       </c>
       <c r="L77" t="n">
-        <v>59.71</v>
+        <v>82.27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:39:13</t>
+          <t>10:39:59</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.55</v>
+        <v>3.02</v>
       </c>
       <c r="F78" t="n">
-        <v>6.91</v>
+        <v>7.93</v>
       </c>
       <c r="G78" t="n">
-        <v>166.9</v>
+        <v>186.8</v>
       </c>
       <c r="H78" t="n">
-        <v>58.1</v>
+        <v>38.6</v>
       </c>
       <c r="I78" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>-27.96</v>
+        <v>-14.33</v>
       </c>
       <c r="K78" t="n">
-        <v>-43.4</v>
+        <v>84.61</v>
       </c>
       <c r="L78" t="n">
-        <v>51.62</v>
+        <v>85.81999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:40:28</t>
+          <t>10:41:25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="F79" t="n">
-        <v>7.78</v>
+        <v>6.55</v>
       </c>
       <c r="G79" t="n">
-        <v>188.4</v>
+        <v>177.3</v>
       </c>
       <c r="H79" t="n">
-        <v>45.4</v>
+        <v>54.3</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-12.46</v>
+        <v>53.16</v>
       </c>
       <c r="K79" t="n">
-        <v>57.68</v>
+        <v>-66.66</v>
       </c>
       <c r="L79" t="n">
-        <v>59.01</v>
+        <v>85.27</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:45:22</t>
+          <t>10:44:46</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.06</v>
+        <v>2.65</v>
       </c>
       <c r="F80" t="n">
         <v>7.93</v>
       </c>
       <c r="G80" t="n">
-        <v>167.8</v>
+        <v>191.4</v>
       </c>
       <c r="H80" t="n">
-        <v>68.2</v>
+        <v>62.4</v>
       </c>
       <c r="I80" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>42.34</v>
+        <v>66.78</v>
       </c>
       <c r="K80" t="n">
-        <v>-80.11</v>
+        <v>67.87</v>
       </c>
       <c r="L80" t="n">
-        <v>90.61</v>
+        <v>95.20999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:46:51</t>
+          <t>10:45:37</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="F81" t="n">
-        <v>7.93</v>
+        <v>7.23</v>
       </c>
       <c r="G81" t="n">
-        <v>163.7</v>
+        <v>176</v>
       </c>
       <c r="H81" t="n">
-        <v>28.8</v>
+        <v>57.1</v>
       </c>
       <c r="I81" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>-54.56</v>
+        <v>-45.87</v>
       </c>
       <c r="K81" t="n">
-        <v>-17</v>
+        <v>-72.66</v>
       </c>
       <c r="L81" t="n">
-        <v>57.15</v>
+        <v>85.93000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:48:20</t>
+          <t>10:46:53</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="F82" t="n">
-        <v>6.95</v>
+        <v>6.79</v>
       </c>
       <c r="G82" t="n">
-        <v>183.5</v>
+        <v>185.8</v>
       </c>
       <c r="H82" t="n">
-        <v>42</v>
+        <v>39.3</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-26.2</v>
+        <v>-121.51</v>
       </c>
       <c r="K82" t="n">
-        <v>90.84999999999999</v>
+        <v>26.43</v>
       </c>
       <c r="L82" t="n">
-        <v>94.55</v>
+        <v>124.35</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:54:14</t>
+          <t>10:52:19</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.17</v>
+        <v>3.26</v>
       </c>
       <c r="F83" t="n">
         <v>7.93</v>
       </c>
       <c r="G83" t="n">
-        <v>193.3</v>
+        <v>162.9</v>
       </c>
       <c r="H83" t="n">
-        <v>43.1</v>
+        <v>63.4</v>
       </c>
       <c r="I83" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J83" t="n">
-        <v>-169.92</v>
+        <v>-2.71</v>
       </c>
       <c r="K83" t="n">
-        <v>-157.76</v>
+        <v>-181.36</v>
       </c>
       <c r="L83" t="n">
-        <v>231.86</v>
+        <v>181.38</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:55:37</t>
+          <t>10:53:09</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.66</v>
+        <v>3.36</v>
       </c>
       <c r="F84" t="n">
         <v>7.93</v>
       </c>
       <c r="G84" t="n">
-        <v>176.2</v>
+        <v>159.3</v>
       </c>
       <c r="H84" t="n">
-        <v>71.8</v>
+        <v>24.8</v>
       </c>
       <c r="I84" t="n">
         <v>31</v>
       </c>
       <c r="J84" t="n">
-        <v>75.62</v>
+        <v>170.61</v>
       </c>
       <c r="K84" t="n">
-        <v>-49.05</v>
+        <v>19.68</v>
       </c>
       <c r="L84" t="n">
-        <v>90.13</v>
+        <v>171.74</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:56:28</t>
+          <t>10:55:26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="F85" t="n">
         <v>7.93</v>
       </c>
       <c r="G85" t="n">
-        <v>179.4</v>
+        <v>184.2</v>
       </c>
       <c r="H85" t="n">
-        <v>43.2</v>
+        <v>56.4</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>152.71</v>
+        <v>-121.87</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.17</v>
+        <v>32.78</v>
       </c>
       <c r="L85" t="n">
-        <v>152.71</v>
+        <v>126.2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:02:22</t>
+          <t>10:58:54</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="F86" t="n">
-        <v>7.93</v>
+        <v>6.01</v>
       </c>
       <c r="G86" t="n">
-        <v>157.8</v>
+        <v>178.7</v>
       </c>
       <c r="H86" t="n">
-        <v>43.4</v>
+        <v>44.5</v>
       </c>
       <c r="I86" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-98.90000000000001</v>
+        <v>-155.43</v>
       </c>
       <c r="K86" t="n">
-        <v>121.12</v>
+        <v>-104.91</v>
       </c>
       <c r="L86" t="n">
-        <v>156.37</v>
+        <v>187.52</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:03:04</t>
+          <t>11:00:45</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="F87" t="n">
         <v>7.93</v>
       </c>
       <c r="G87" t="n">
-        <v>184.4</v>
+        <v>170.2</v>
       </c>
       <c r="H87" t="n">
-        <v>78.7</v>
+        <v>41.7</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J87" t="n">
-        <v>179.88</v>
+        <v>163.49</v>
       </c>
       <c r="K87" t="n">
-        <v>-25.68</v>
+        <v>-22.21</v>
       </c>
       <c r="L87" t="n">
-        <v>181.7</v>
+        <v>165</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:05:31</t>
+          <t>11:01:49</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.89</v>
+        <v>3.33</v>
       </c>
       <c r="F88" t="n">
-        <v>7.71</v>
+        <v>7.39</v>
       </c>
       <c r="G88" t="n">
-        <v>170.2</v>
+        <v>188.4</v>
       </c>
       <c r="H88" t="n">
-        <v>45.9</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>198.28</v>
+        <v>169.5</v>
       </c>
       <c r="K88" t="n">
-        <v>69.01000000000001</v>
+        <v>-157.63</v>
       </c>
       <c r="L88" t="n">
-        <v>209.94</v>
+        <v>231.47</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-03.xlsx
+++ b/output/2024-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-58.94</v>
+        <v>-62.69</v>
       </c>
       <c r="K14" t="n">
-        <v>27.8</v>
+        <v>29.57</v>
       </c>
       <c r="L14" t="n">
-        <v>65.17</v>
+        <v>69.31</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.77</v>
+        <v>-3.12</v>
       </c>
       <c r="L15" t="n">
-        <v>3.47</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>21.77</v>
+        <v>22.44</v>
       </c>
       <c r="K16" t="n">
-        <v>74.27</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>77.39</v>
+        <v>79.79000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>103.98</v>
+        <v>107.5</v>
       </c>
       <c r="K17" t="n">
-        <v>-29.44</v>
+        <v>-30.44</v>
       </c>
       <c r="L17" t="n">
-        <v>108.07</v>
+        <v>111.72</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-46.03</v>
+        <v>-53.01</v>
       </c>
       <c r="K18" t="n">
-        <v>54.09</v>
+        <v>62.29</v>
       </c>
       <c r="L18" t="n">
-        <v>71.02</v>
+        <v>81.79000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-62.55</v>
+        <v>-74.06999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>14.53</v>
+        <v>17.21</v>
       </c>
       <c r="L19" t="n">
-        <v>64.22</v>
+        <v>76.05</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>71.86</v>
+        <v>89.11</v>
       </c>
       <c r="K20" t="n">
-        <v>64.15000000000001</v>
+        <v>79.55</v>
       </c>
       <c r="L20" t="n">
-        <v>96.33</v>
+        <v>119.46</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>96.69</v>
+        <v>117.49</v>
       </c>
       <c r="K21" t="n">
-        <v>28.85</v>
+        <v>35.06</v>
       </c>
       <c r="L21" t="n">
-        <v>100.9</v>
+        <v>122.6</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>124.98</v>
+        <v>133.63</v>
       </c>
       <c r="K22" t="n">
-        <v>-135.12</v>
+        <v>-144.47</v>
       </c>
       <c r="L22" t="n">
-        <v>184.06</v>
+        <v>196.79</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-87</v>
+        <v>-101.11</v>
       </c>
       <c r="K23" t="n">
-        <v>-171.89</v>
+        <v>-199.76</v>
       </c>
       <c r="L23" t="n">
-        <v>192.65</v>
+        <v>223.89</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-98.69</v>
+        <v>-130.73</v>
       </c>
       <c r="K24" t="n">
-        <v>56.38</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>113.66</v>
+        <v>150.56</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-41.21</v>
+        <v>-53.38</v>
       </c>
       <c r="K25" t="n">
-        <v>-108.98</v>
+        <v>-141.17</v>
       </c>
       <c r="L25" t="n">
-        <v>116.51</v>
+        <v>150.92</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-56.84</v>
+        <v>-78.53</v>
       </c>
       <c r="K26" t="n">
-        <v>-111.81</v>
+        <v>-154.46</v>
       </c>
       <c r="L26" t="n">
-        <v>125.43</v>
+        <v>173.28</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>140.75</v>
+        <v>179.73</v>
       </c>
       <c r="K27" t="n">
-        <v>-178.36</v>
+        <v>-227.76</v>
       </c>
       <c r="L27" t="n">
-        <v>227.21</v>
+        <v>290.13</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>214.38</v>
+        <v>281.54</v>
       </c>
       <c r="K28" t="n">
-        <v>-31.26</v>
+        <v>-41.05</v>
       </c>
       <c r="L28" t="n">
-        <v>216.65</v>
+        <v>284.52</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>14.79</v>
+        <v>16.14</v>
       </c>
       <c r="K29" t="n">
-        <v>57.14</v>
+        <v>62.38</v>
       </c>
       <c r="L29" t="n">
-        <v>59.02</v>
+        <v>64.43000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-70.69</v>
+        <v>-75.34999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="L30" t="n">
-        <v>70.69</v>
+        <v>75.36</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>43.13</v>
+        <v>46.96</v>
       </c>
       <c r="K31" t="n">
-        <v>-79.93000000000001</v>
+        <v>-87.04000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>90.83</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>38.02</v>
+        <v>40.74</v>
       </c>
       <c r="K32" t="n">
-        <v>100.84</v>
+        <v>108.06</v>
       </c>
       <c r="L32" t="n">
-        <v>107.77</v>
+        <v>115.48</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>52.87</v>
+        <v>64.69</v>
       </c>
       <c r="K33" t="n">
-        <v>-41.26</v>
+        <v>-50.48</v>
       </c>
       <c r="L33" t="n">
-        <v>67.06</v>
+        <v>82.05</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>38</v>
+        <v>47.04</v>
       </c>
       <c r="K34" t="n">
-        <v>55.85</v>
+        <v>69.14</v>
       </c>
       <c r="L34" t="n">
-        <v>67.55</v>
+        <v>83.63</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>32.85</v>
+        <v>37.69</v>
       </c>
       <c r="K35" t="n">
-        <v>112.55</v>
+        <v>129.13</v>
       </c>
       <c r="L35" t="n">
-        <v>117.24</v>
+        <v>134.52</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.19</v>
+        <v>-4.03</v>
       </c>
       <c r="K36" t="n">
-        <v>99.18000000000001</v>
+        <v>125.24</v>
       </c>
       <c r="L36" t="n">
-        <v>99.23</v>
+        <v>125.31</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>146.73</v>
+        <v>158.08</v>
       </c>
       <c r="K37" t="n">
-        <v>-66.29000000000001</v>
+        <v>-71.42</v>
       </c>
       <c r="L37" t="n">
-        <v>161.01</v>
+        <v>173.46</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-197.04</v>
+        <v>-216.19</v>
       </c>
       <c r="K38" t="n">
-        <v>-184.99</v>
+        <v>-202.97</v>
       </c>
       <c r="L38" t="n">
-        <v>270.27</v>
+        <v>296.54</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-97.84999999999999</v>
+        <v>-129.97</v>
       </c>
       <c r="K39" t="n">
-        <v>-56.46</v>
+        <v>-74.98999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>112.97</v>
+        <v>150.05</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>14.93</v>
+        <v>18.65</v>
       </c>
       <c r="K40" t="n">
-        <v>-145.87</v>
+        <v>-182.17</v>
       </c>
       <c r="L40" t="n">
-        <v>146.63</v>
+        <v>183.12</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>20.21</v>
+        <v>26.49</v>
       </c>
       <c r="K41" t="n">
-        <v>174.84</v>
+        <v>229.11</v>
       </c>
       <c r="L41" t="n">
-        <v>176.01</v>
+        <v>230.64</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-194.12</v>
+        <v>-244</v>
       </c>
       <c r="K42" t="n">
-        <v>138.77</v>
+        <v>174.44</v>
       </c>
       <c r="L42" t="n">
-        <v>238.62</v>
+        <v>299.94</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>66.51000000000001</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>-260.69</v>
+        <v>-312.84</v>
       </c>
       <c r="L43" t="n">
-        <v>269.04</v>
+        <v>322.86</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>-30.06</v>
+        <v>-35.82</v>
       </c>
       <c r="K44" t="n">
-        <v>6.14</v>
+        <v>7.32</v>
       </c>
       <c r="L44" t="n">
-        <v>30.68</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>37.35</v>
+        <v>40.92</v>
       </c>
       <c r="K45" t="n">
-        <v>-66.31999999999999</v>
+        <v>-72.66</v>
       </c>
       <c r="L45" t="n">
-        <v>76.11</v>
+        <v>83.39</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>9.77</v>
+        <v>10.62</v>
       </c>
       <c r="K46" t="n">
-        <v>67.25</v>
+        <v>73.12</v>
       </c>
       <c r="L46" t="n">
-        <v>67.95999999999999</v>
+        <v>73.89</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-60.4</v>
+        <v>-67.20999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-64.59</v>
+        <v>-71.86</v>
       </c>
       <c r="L47" t="n">
-        <v>88.43000000000001</v>
+        <v>98.39</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>73.29000000000001</v>
+        <v>78.83</v>
       </c>
       <c r="K48" t="n">
-        <v>-67.65000000000001</v>
+        <v>-72.77</v>
       </c>
       <c r="L48" t="n">
-        <v>99.73999999999999</v>
+        <v>107.29</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-76.03</v>
+        <v>-81.59999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>65.43000000000001</v>
+        <v>70.22</v>
       </c>
       <c r="L49" t="n">
-        <v>100.31</v>
+        <v>107.66</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>114.6</v>
+        <v>129.99</v>
       </c>
       <c r="K50" t="n">
-        <v>-92.22</v>
+        <v>-104.6</v>
       </c>
       <c r="L50" t="n">
-        <v>147.1</v>
+        <v>166.85</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-38.2</v>
+        <v>-43.27</v>
       </c>
       <c r="K51" t="n">
-        <v>-127.55</v>
+        <v>-144.46</v>
       </c>
       <c r="L51" t="n">
-        <v>133.15</v>
+        <v>150.8</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>24.24</v>
+        <v>29.4</v>
       </c>
       <c r="K52" t="n">
-        <v>-96.7</v>
+        <v>-117.27</v>
       </c>
       <c r="L52" t="n">
-        <v>99.69</v>
+        <v>120.9</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>147.2</v>
+        <v>169.46</v>
       </c>
       <c r="K53" t="n">
-        <v>-124.63</v>
+        <v>-143.48</v>
       </c>
       <c r="L53" t="n">
-        <v>192.87</v>
+        <v>222.04</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>5.08</v>
+        <v>6.71</v>
       </c>
       <c r="K54" t="n">
-        <v>-67.73</v>
+        <v>-89.39</v>
       </c>
       <c r="L54" t="n">
-        <v>67.92</v>
+        <v>89.64</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>174.88</v>
+        <v>200.93</v>
       </c>
       <c r="K55" t="n">
-        <v>55.41</v>
+        <v>63.66</v>
       </c>
       <c r="L55" t="n">
-        <v>183.44</v>
+        <v>210.77</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-131.1</v>
+        <v>-177.92</v>
       </c>
       <c r="K56" t="n">
-        <v>120.31</v>
+        <v>163.29</v>
       </c>
       <c r="L56" t="n">
-        <v>177.94</v>
+        <v>241.5</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>205.38</v>
+        <v>249.41</v>
       </c>
       <c r="K57" t="n">
-        <v>-160.29</v>
+        <v>-194.65</v>
       </c>
       <c r="L57" t="n">
-        <v>260.53</v>
+        <v>316.38</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>152.62</v>
+        <v>187.81</v>
       </c>
       <c r="K58" t="n">
-        <v>-241.53</v>
+        <v>-297.23</v>
       </c>
       <c r="L58" t="n">
-        <v>285.71</v>
+        <v>351.6</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>67.59</v>
+        <v>72.42</v>
       </c>
       <c r="K59" t="n">
-        <v>-9.210000000000001</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>68.22</v>
+        <v>73.09</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>90.11</v>
+        <v>91.78</v>
       </c>
       <c r="K60" t="n">
-        <v>88.72</v>
+        <v>90.37</v>
       </c>
       <c r="L60" t="n">
-        <v>126.46</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-93.25</v>
+        <v>-95.98</v>
       </c>
       <c r="K61" t="n">
-        <v>6.01</v>
+        <v>6.19</v>
       </c>
       <c r="L61" t="n">
-        <v>93.45</v>
+        <v>96.18000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-66.59</v>
+        <v>-76.61</v>
       </c>
       <c r="K62" t="n">
-        <v>12.73</v>
+        <v>14.65</v>
       </c>
       <c r="L62" t="n">
-        <v>67.79000000000001</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-62.34</v>
+        <v>-73.43000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>18.98</v>
+        <v>22.36</v>
       </c>
       <c r="L63" t="n">
-        <v>65.17</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-65.41</v>
+        <v>-79.45</v>
       </c>
       <c r="K64" t="n">
-        <v>18.18</v>
+        <v>22.08</v>
       </c>
       <c r="L64" t="n">
-        <v>67.89</v>
+        <v>82.45999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-78.90000000000001</v>
+        <v>-88.16</v>
       </c>
       <c r="K65" t="n">
-        <v>132.54</v>
+        <v>148.11</v>
       </c>
       <c r="L65" t="n">
-        <v>154.25</v>
+        <v>172.36</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-51</v>
+        <v>-60.39</v>
       </c>
       <c r="K66" t="n">
-        <v>115.83</v>
+        <v>137.17</v>
       </c>
       <c r="L66" t="n">
-        <v>126.56</v>
+        <v>149.87</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>106.71</v>
+        <v>131.68</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.88</v>
+        <v>-4.78</v>
       </c>
       <c r="L67" t="n">
-        <v>106.78</v>
+        <v>131.77</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-115.1</v>
+        <v>-148.19</v>
       </c>
       <c r="K68" t="n">
-        <v>-42.64</v>
+        <v>-54.91</v>
       </c>
       <c r="L68" t="n">
-        <v>122.74</v>
+        <v>158.04</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-73.62</v>
+        <v>-93.09999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>-119.16</v>
+        <v>-150.68</v>
       </c>
       <c r="L69" t="n">
-        <v>140.07</v>
+        <v>177.12</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-145.02</v>
+        <v>-181.64</v>
       </c>
       <c r="K70" t="n">
-        <v>-14.9</v>
+        <v>-18.66</v>
       </c>
       <c r="L70" t="n">
-        <v>145.78</v>
+        <v>182.6</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>198.5</v>
+        <v>245.03</v>
       </c>
       <c r="K71" t="n">
-        <v>-79.59999999999999</v>
+        <v>-98.26000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>213.86</v>
+        <v>264</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-25.38</v>
+        <v>-35.56</v>
       </c>
       <c r="K72" t="n">
-        <v>150.23</v>
+        <v>210.51</v>
       </c>
       <c r="L72" t="n">
-        <v>152.35</v>
+        <v>213.49</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>183.81</v>
+        <v>235.36</v>
       </c>
       <c r="K73" t="n">
-        <v>-144.28</v>
+        <v>-184.73</v>
       </c>
       <c r="L73" t="n">
-        <v>233.68</v>
+        <v>299.2</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-63.58</v>
+        <v>-73.56</v>
       </c>
       <c r="K74" t="n">
-        <v>6.63</v>
+        <v>7.68</v>
       </c>
       <c r="L74" t="n">
-        <v>63.92</v>
+        <v>73.95999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-98.14</v>
+        <v>-100.66</v>
       </c>
       <c r="K75" t="n">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="L75" t="n">
-        <v>98.17</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>69.41</v>
+        <v>77.27</v>
       </c>
       <c r="K76" t="n">
-        <v>15.34</v>
+        <v>17.07</v>
       </c>
       <c r="L76" t="n">
-        <v>71.08</v>
+        <v>79.14</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>61.84</v>
+        <v>77.22</v>
       </c>
       <c r="K77" t="n">
-        <v>-17.7</v>
+        <v>-22.1</v>
       </c>
       <c r="L77" t="n">
-        <v>64.31999999999999</v>
+        <v>80.31999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-31.03</v>
+        <v>-34.18</v>
       </c>
       <c r="K78" t="n">
-        <v>103.24</v>
+        <v>113.73</v>
       </c>
       <c r="L78" t="n">
-        <v>107.8</v>
+        <v>118.76</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-20.02</v>
+        <v>-22.08</v>
       </c>
       <c r="K79" t="n">
-        <v>-78.83</v>
+        <v>-86.95</v>
       </c>
       <c r="L79" t="n">
-        <v>81.33</v>
+        <v>89.70999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>110.86</v>
+        <v>135.19</v>
       </c>
       <c r="K80" t="n">
-        <v>4.25</v>
+        <v>5.19</v>
       </c>
       <c r="L80" t="n">
-        <v>110.94</v>
+        <v>135.29</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>48.23</v>
+        <v>54.92</v>
       </c>
       <c r="K81" t="n">
-        <v>144.46</v>
+        <v>164.49</v>
       </c>
       <c r="L81" t="n">
-        <v>152.3</v>
+        <v>173.42</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-143</v>
+        <v>-161.18</v>
       </c>
       <c r="K82" t="n">
-        <v>14.83</v>
+        <v>16.71</v>
       </c>
       <c r="L82" t="n">
-        <v>143.77</v>
+        <v>162.04</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>132.37</v>
+        <v>163.44</v>
       </c>
       <c r="K83" t="n">
-        <v>114.39</v>
+        <v>141.24</v>
       </c>
       <c r="L83" t="n">
-        <v>174.95</v>
+        <v>216.01</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>120.72</v>
+        <v>140.13</v>
       </c>
       <c r="K84" t="n">
-        <v>130.8</v>
+        <v>151.84</v>
       </c>
       <c r="L84" t="n">
-        <v>177.99</v>
+        <v>206.62</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>128.94</v>
+        <v>158.77</v>
       </c>
       <c r="K85" t="n">
-        <v>-58.71</v>
+        <v>-72.29000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>141.68</v>
+        <v>174.45</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>308.41</v>
+        <v>363.57</v>
       </c>
       <c r="K86" t="n">
-        <v>-144.39</v>
+        <v>-170.21</v>
       </c>
       <c r="L86" t="n">
-        <v>340.54</v>
+        <v>401.44</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-90.75</v>
+        <v>-111.62</v>
       </c>
       <c r="K87" t="n">
-        <v>264.9</v>
+        <v>325.81</v>
       </c>
       <c r="L87" t="n">
-        <v>280.01</v>
+        <v>344.4</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-144.21</v>
+        <v>-181.17</v>
       </c>
       <c r="K88" t="n">
-        <v>-177.6</v>
+        <v>-223.11</v>
       </c>
       <c r="L88" t="n">
-        <v>228.77</v>
+        <v>287.4</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-03.xlsx
+++ b/output/2024-10-03.xlsx
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>46.96</v>
+        <v>48.97</v>
       </c>
       <c r="K31" t="n">
-        <v>-87.04000000000001</v>
+        <v>-90.76000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>98.90000000000001</v>
+        <v>103.13</v>
       </c>
     </row>
     <row r="32">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>47.04</v>
+        <v>48.61</v>
       </c>
       <c r="K34" t="n">
-        <v>69.14</v>
+        <v>71.45</v>
       </c>
       <c r="L34" t="n">
-        <v>83.63</v>
+        <v>86.41</v>
       </c>
     </row>
     <row r="35">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>77.22</v>
+        <v>80.77</v>
       </c>
       <c r="K77" t="n">
-        <v>-22.1</v>
+        <v>-23.11</v>
       </c>
       <c r="L77" t="n">
-        <v>80.31999999999999</v>
+        <v>84.01000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-34.18</v>
+        <v>-36.42</v>
       </c>
       <c r="K78" t="n">
-        <v>113.73</v>
+        <v>121.18</v>
       </c>
       <c r="L78" t="n">
-        <v>118.76</v>
+        <v>126.54</v>
       </c>
     </row>
     <row r="79">
